--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$70</definedName>
@@ -8045,38 +8045,38 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Stašėnai</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Dirvaliai, Šveicarijos sen., Jonavos r. sav.</t>
+          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
-        <v>55.033</v>
+        <v>54.6493094</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>24.183</v>
+        <v>25.3107972</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus adreso taškas pagal geokodavimą</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Stašėnai Plant</t>
+          <t>Vilnius Ušos g. Plant</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
+          <t>Nissbau Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U67" s="5" t="n">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-07T09:56:29.575140+00:00</t>
+          <t>2026-09-14T04:36:38.879321+00:00</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:56:29.575852+00:00</t>
+          <t>2026-09-14T04:36:38.880373+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -513,7 +513,7 @@
     <col width="40" customWidth="1" min="16" max="16"/>
     <col width="32" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="42" customWidth="1" min="22" max="22"/>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>Ponas betonas betono mazgas</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="S70" s="4" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>2 matomi oficialioje nuotraukoje</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Mazgo gamintojas, maišyklė, našumas ir silosų skaičius viešai nenurodyti.</t>
+          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
         </is>
       </c>
       <c r="U70" s="5" t="n">
@@ -8507,17 +8507,17 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
+          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14T04:36:38.879321+00:00</t>
+          <t>2026-09-14T04:47:15.098822+00:00</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14T04:36:38.880373+00:00</t>
+          <t>2026-09-14T04:47:15.100829+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$70</definedName>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14T04:47:15.098822+00:00</t>
+          <t>2026-09-14T10:18:58.753253+00:00</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14T04:47:15.100829+00:00</t>
+          <t>2026-09-14T10:18:58.753936+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-14T10:18:58.753253+00:00</t>
+          <t>2026-09-21T10:23:24.887386+00:00</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14T10:18:58.753936+00:00</t>
+          <t>2026-09-21T10:23:24.888084+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$70</definedName>
@@ -510,7 +510,7 @@
     <col width="42" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="16" max="16"/>
     <col width="32" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
@@ -1777,38 +1777,38 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Glaudėnai</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Šiaurės g. 2, Vilnius</t>
+          <t>Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>54.6921358</v>
+        <v>55.774886</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>25.3937728</v>
+        <v>21.160809</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas; adresas patikslintas reverse-geokodavimu</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus betono gamykla, Šiaurės g.</t>
+          <t>Heidelberg Materials betono gamykla, Glaudėnai</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Vilniuje.</t>
+          <t>Heidelberg Materials betono gamyklų tinklo taškas perkeltas iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="U11" s="5" t="n">
@@ -1849,17 +1849,17 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
+          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+          <t>Perkelta iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją. Google Maps nuoroda išsisprendė į koordinates 55.774886, 21.160809; vietovė patikslinta reverse-geokodavimu kaip Glaudėnų k., Sendvario sen., Klaipėdos r. sav. Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis paliktas kaip įmonės šaltinis.</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21T10:23:24.887386+00:00</t>
+          <t>2026-09-23T07:20:42.186376+00:00</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21T10:23:24.888084+00:00</t>
+          <t>2026-09-23T07:20:42.187391+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -902,7 +902,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-rudningai</t>
+          <t>betono-centras-vilnius-metalo</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -927,38 +927,38 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Rūdningai</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Šalčininkų r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Rūdningai</t>
+          <t>Metalo g. 19B, Vilnius</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>54.43883333333333</v>
+        <v>54.633332907517</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>25.081</v>
+        <v>25.265130105086</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktas koordinačių taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos koordinatės</t>
+          <t>ArcGIS World Geocoding Service</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -973,31 +973,19 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>SBM3000 (Schwenk)</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3,0 m³</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>80 m³/h</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>3x85 t</t>
-        </is>
-      </c>
+          <t>Būsima Betono centro gamykla</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>Betono centro betono mazgas Rūdninguose.</t>
+          <t>Būsima Betono centro betono gamykla Metalo g. 19B, Vilniuje.</t>
         </is>
       </c>
       <c r="U4" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1006,29 +994,25 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>https://betonocentras.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
-        </is>
-      </c>
+          <t>https://betonocentras.lt/</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos DMS formatu: 54°26'19.8"N 25°04'51.6"E.</t>
+          <t>Būsimas Betono centro taškas įtrauktas pagal naudotojo pateiktą informaciją. Techniniai mazgo duomenys dar nepateikti.</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-rudninkai</t>
+          <t>betono-centras-rudningai</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1053,7 +1037,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Rūdninkai</t>
+          <t>Rūdningai</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1063,14 +1047,14 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Rūdninkai</t>
+          <t>Rūdningai</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>54.43924548406194</v>
+        <v>54.43883333333333</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>25.08098427100702</v>
+        <v>25.081</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1084,7 +1068,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
+          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1099,12 +1083,12 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>SBM3300</t>
+          <t>SBM3000 (Schwenk)</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>3,3 m³</t>
+          <t>3,0 m³</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
@@ -1119,7 +1103,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>Betono centro betono mazgas Rūdninkuose.</t>
+          <t>Betono centro betono mazgas Rūdninguose.</t>
         </is>
       </c>
       <c r="U5" s="5" t="n">
@@ -1137,12 +1121,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
+          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos dešimtainiu formatu.</t>
+          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos DMS formatu: 54°26'19.8"N 25°04'51.6"E.</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1154,7 +1138,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-kaunas</t>
+          <t>betono-centras-rudninkai</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1179,38 +1163,38 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Rūdninkai</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Šalčininkų r. sav.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Raudondvario pl. 157, Kaunas</t>
+          <t>Rūdninkai</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>54.9128359</v>
+        <v>54.43924548406194</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>23.8412662</v>
+        <v>25.08098427100702</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Naudotojo pateiktas koordinačių taškas</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Naudotojo pateiktos koordinatės</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1225,23 +1209,27 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Wiggert</t>
+          <t>SBM3300</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2,0 m³ ir 3,0 m³</t>
+          <t>3,3 m³</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S6" s="4" t="inlineStr"/>
+          <t>80 m³/h</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>3x85 t</t>
+        </is>
+      </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Kaune.</t>
+          <t>Betono centro betono mazgas Rūdninkuose.</t>
         </is>
       </c>
       <c r="U6" s="5" t="n">
@@ -1259,24 +1247,24 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>https://betonocentras.lt/kontaktai/</t>
+          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>Kauno betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos dešimtainiu formatu.</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-klaipeda</t>
+          <t>betono-centras-kaunas</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1301,24 +1289,24 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Liepų g. 87N, Klaipėda</t>
+          <t>Raudondvario pl. 157, Kaunas</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>55.7290357</v>
+        <v>54.9128359</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.1544709</v>
+        <v>23.8412662</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1347,23 +1335,23 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>LIEBHERR MOBILMIX</t>
+          <t>Wiggert</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2,25 m³</t>
+          <t>2,0 m³ ir 3,0 m³</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>60 m³/h</t>
+          <t>60-80 m³/h</t>
         </is>
       </c>
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Klaipėdoje.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Kaune.</t>
         </is>
       </c>
       <c r="U7" s="5" t="n">
@@ -1386,7 +1374,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame Betono centro kontaktų puslapyje patvirtintas Klaipėdos padalinys. Mazgo techniniai duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
+          <t>Kauno betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1398,7 +1386,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-siauliai</t>
+          <t>betono-centras-klaipeda</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1423,24 +1411,24 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Šiauliai</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių m. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Daubos g. 7A, Šiauliai</t>
+          <t>Liepų g. 87N, Klaipėda</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>55.9056327</v>
+        <v>55.7290357</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>23.3141873</v>
+        <v>21.1544709</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1485,7 +1473,7 @@
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Šiauliuose.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Klaipėdoje.</t>
         </is>
       </c>
       <c r="U8" s="5" t="n">
@@ -1508,7 +1496,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialiame Betono centro kontaktų puslapyje patvirtintas Klaipėdos padalinys. Mazgo techniniai duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1520,7 +1508,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-mazeikiai</t>
+          <t>betono-centras-siauliai</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1545,24 +1533,24 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Mažeikiai</t>
+          <t>Šiauliai</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių r. sav.</t>
+          <t>Šiaulių m. sav.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Troškučių g. 1, Mažeikiai</t>
+          <t>Daubos g. 7A, Šiauliai</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>56.3189055</v>
+        <v>55.9056327</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>22.2967774</v>
+        <v>23.3141873</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1591,15 +1579,23 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių betono mazgas</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
+          <t>LIEBHERR MOBILMIX</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2,25 m³</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/h</t>
+        </is>
+      </c>
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Mažeikiuose.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Šiauliuose.</t>
         </is>
       </c>
       <c r="U9" s="5" t="n">
@@ -1620,17 +1616,21 @@
           <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>Šiaulių betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+        </is>
+      </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-panevezys</t>
+          <t>betono-centras-mazeikiai</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1655,24 +1655,24 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Mažeikiai</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Mažeikių r. sav.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52A, Panevėžys</t>
+          <t>Troškučių g. 1, Mažeikiai</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>55.7423854</v>
+        <v>56.3189055</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>24.3777723</v>
+        <v>22.2967774</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1701,23 +1701,15 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>LIEBHERR Betomix</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2,25 m³</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/h</t>
-        </is>
-      </c>
+          <t>Mažeikių betono mazgas</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Panevėžyje.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Mažeikiuose.</t>
         </is>
       </c>
       <c r="U10" s="5" t="n">
@@ -1738,77 +1730,73 @@
           <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>Panevėžio betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
-        </is>
-      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-vilnius-siaures</t>
+          <t>betono-centras-panevezys</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>304102190</t>
+          <t>123018186</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>UAB Heidelberg Materials Lietuva Betonas</t>
+          <t>UAB Betono centras</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials</t>
+          <t>Betono centras</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Konkurentas</t>
+          <t>Mūsų įmonė</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Glaudėnai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
+          <t>S. Kerbedžio g. 52A, Panevėžys</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>55.774886</v>
+        <v>55.7423854</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>21.160809</v>
+        <v>24.3777723</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas; adresas patikslintas reverse-geokodavimu</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1823,50 +1811,58 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials betono gamykla, Glaudėnai</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
+          <t>LIEBHERR Betomix</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2,25 m³</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/h</t>
+        </is>
+      </c>
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials betono gamyklų tinklo taškas perkeltas iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Panevėžyje.</t>
         </is>
       </c>
       <c r="U11" s="5" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt</t>
+          <t>https://betonocentras.lt/</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
+          <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
+          <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>Perkelta iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją. Google Maps nuoroda išsisprendė į koordinates 55.774886, 21.160809; vietovė patikslinta reverse-geokodavimu kaip Glaudėnų k., Sendvario sen., Klaipėdos r. sav. Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis paliktas kaip įmonės šaltinis.</t>
+          <t>Panevėžio betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-vilnius-sandeliu</t>
+          <t>heidelberg-vilnius-siaures</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1891,38 +1887,38 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Glaudėnai</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Sandėlių g. 16, Vilnius</t>
+          <t>Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>54.6535114</v>
+        <v>55.774886</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>25.1242965</v>
+        <v>21.160809</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas; adresas patikslintas reverse-geokodavimu</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1937,7 +1933,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus betono gamykla, Sandėlių g.</t>
+          <t>Heidelberg Materials betono gamykla, Glaudėnai</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -1945,7 +1941,7 @@
       <c r="S12" s="4" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Vilniuje.</t>
+          <t>Heidelberg Materials betono gamyklų tinklo taškas perkeltas iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="U12" s="5" t="n">
@@ -1963,24 +1959,24 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
+          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+          <t>Perkelta iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją. Google Maps nuoroda išsisprendė į koordinates 55.774886, 21.160809; vietovė patikslinta reverse-geokodavimu kaip Glaudėnų k., Sendvario sen., Klaipėdos r. sav. Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis paliktas kaip įmonės šaltinis.</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-kaunas</t>
+          <t>heidelberg-vilnius-sandeliu</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2005,24 +2001,24 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Technikos g. 7K, Kaunas</t>
+          <t>Sandėlių g. 16, Vilnius</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>54.9093181</v>
+        <v>54.6535114</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>24.0122104</v>
+        <v>25.1242965</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -2051,7 +2047,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Kauno betono gamykla</t>
+          <t>Vilniaus betono gamykla, Sandėlių g.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -2059,7 +2055,7 @@
       <c r="S13" s="4" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Kaune.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Vilniuje.</t>
         </is>
       </c>
       <c r="U13" s="5" t="n">
@@ -2094,7 +2090,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-klaipeda</t>
+          <t>heidelberg-avizieniai-klevu</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2119,24 +2115,24 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Avižieniai</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Švepelių g. 5, Klaipėda</t>
+          <t>Klevų g. 2, Avižieniai, Vilniaus r.</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>55.6744503</v>
+        <v>54.760788043384</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>21.2165993</v>
+        <v>25.179476693822</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -2145,12 +2141,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>ArcGIS World Geocoding Service</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2165,7 +2161,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Wiggert</t>
+          <t>Ammann Elba</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2175,19 +2171,21 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S14" s="4" t="n">
-        <v>2</v>
+          <t>60 m³/val.</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>3x85 t</t>
+        </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Klaipėdoje.</t>
+          <t>Heidelberg Materials betono mazgas Klevų g. 2, Avižieniuose.</t>
         </is>
       </c>
       <c r="U14" s="5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
@@ -2206,19 +2204,19 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje. Klaipėdos mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina Klevų g. 2, Avižieniai, betono užsakymų tašką. Mazgo gamintojas, maišyklės tūris, realus našumas ir silosų duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-alytus</t>
+          <t>heidelberg-kaunas</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2243,24 +2241,24 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Alytus</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Alytaus m. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Kalniškės g. 2, Alytus</t>
+          <t>Technikos g. 7K, Kaunas</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>54.4113266</v>
+        <v>54.9093181</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>24.0081029</v>
+        <v>24.0122104</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -2289,7 +2287,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Alytaus betono gamykla</t>
+          <t>Kauno betono gamykla</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -2297,7 +2295,7 @@
       <c r="S15" s="4" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Alytuje.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Kaune.</t>
         </is>
       </c>
       <c r="U15" s="5" t="n">
@@ -2332,7 +2330,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-pasvalys</t>
+          <t>heidelberg-klaipeda</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2357,28 +2355,28 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Pasvalys</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Pasvalio r. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Beržų g. 8C, Pasvalys</t>
+          <t>Švepelių g. 5, Klaipėda</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>56.0647646</v>
+        <v>55.6744503</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>24.3860079</v>
+        <v>21.2165993</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Gatvės lygio taškas; reikia tikslesnio adreso taško</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2403,19 +2401,29 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Pasvalio betono gamykla</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
+          <t>Wiggert</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Pasvalyje.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Klaipėdoje.</t>
         </is>
       </c>
       <c r="U16" s="5" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2434,34 +2442,34 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje. Klaipėdos mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>palmusta-vilnius</t>
+          <t>heidelberg-alytus</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>122619426</t>
+          <t>304102190</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>UAB Palmusta</t>
+          <t>UAB Heidelberg Materials Lietuva Betonas</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Palmusta</t>
+          <t>Heidelberg Materials</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2471,24 +2479,24 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Alytus</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Alytaus m. sav.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Sudervės kel. 1A, Avižieniai, Vilniaus r.</t>
+          <t>Kalniškės g. 2, Alytus</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>54.7136351</v>
+        <v>54.4113266</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>25.2359209</v>
+        <v>24.0081029</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2517,7 +2525,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Palmusta betono mazgas</t>
+          <t>Alytaus betono gamykla</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -2525,28 +2533,32 @@
       <c r="S17" s="4" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas Vilniaus regione.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Alytuje.</t>
         </is>
       </c>
       <c r="U17" s="5" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>https://www.palmusta.lt/</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>https://www.palmusta.lt/</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>https://www.palmusta.lt/</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr"/>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+        </is>
+      </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -2556,18 +2568,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>gkg3-vilnius</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr"/>
+          <t>heidelberg-pasvalys</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>304102190</t>
+        </is>
+      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>UAB Vilniaus gelžbetoninių konstrukcijų gamykla Nr. 3</t>
+          <t>UAB Heidelberg Materials Lietuva Betonas</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>GKG-3</t>
+          <t>Heidelberg Materials</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2577,53 +2593,53 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Pasvalys</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Pasvalio r. sav.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Šaltupio g. 11, Vilnius</t>
+          <t>Beržų g. 8C, Pasvalys</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>54.6471731</v>
+        <v>56.0647646</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>25.1918488</v>
+        <v>24.3860079</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Oficialios Google Maps nuorodos taškas</t>
+          <t>Gatvės lygio taškas; reikia tikslesnio adreso taško</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>GKG3 kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>https://gkg3.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>GKG-3 gelžbetonio gamykla</t>
+          <t>Pasvalio betono gamykla</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -2631,30 +2647,30 @@
       <c r="S18" s="4" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninių konstrukcijų gamyba Vilniuje.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Pasvalyje.</t>
         </is>
       </c>
       <c r="U18" s="5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>https://www.gkg3.lt/</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>https://gkg3.lt/kontaktai/</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>https://gkg3.lt/kontaktai/</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>Koordinatės patikslintos pagal oficialaus GKG3 kontaktų puslapio Google Maps nuorodą.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2666,18 +2682,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>perdanga-vilnius</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr"/>
+          <t>palmusta-vilnius</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>122619426</t>
+        </is>
+      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>UAB Perdanga</t>
+          <t>UAB Palmusta</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Perdanga</t>
+          <t>Palmusta</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2692,19 +2712,19 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Lentvario g. 16, Vilnius</t>
+          <t>Sudervės kel. 1A, Avižieniai, Vilniaus r.</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>54.642372</v>
+        <v>54.7136351</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>25.1441455</v>
+        <v>25.2359209</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2723,47 +2743,43 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Perdanga Vilniaus gamykla</t>
+          <t>Palmusta betono mazgas</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>150 m³/val.</t>
-        </is>
-      </c>
+      <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="4" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>Viešai nurodoma nauja gelžbetonio elementų gamybos linija, kurios našumas 150 m³/val.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Vilniaus regione.</t>
         </is>
       </c>
       <c r="U19" s="5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
+          <t>https://www.palmusta.lt/</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
+          <t>https://www.palmusta.lt/</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
+          <t>https://www.palmusta.lt/</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr"/>
@@ -2776,18 +2792,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>perdanga-klaipeda</t>
+          <t>gkg3-vilnius</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UAB Perdanga</t>
+          <t>UAB Vilniaus gelžbetoninių konstrukcijų gamykla Nr. 3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Perdanga</t>
+          <t>GKG-3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2797,38 +2813,38 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Dubysos g. 27, Klaipėda</t>
+          <t>Šaltupio g. 11, Vilnius</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>55.6923067</v>
+        <v>54.6471731</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>21.1631559</v>
+        <v>25.1918488</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialios Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>GKG3 kontaktų puslapis</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://gkg3.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2843,69 +2859,61 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Stetter</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2x1,5 m³</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>40-50 m³/h</t>
-        </is>
-      </c>
+          <t>GKG-3 gelžbetonio gamykla</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="4" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Perdangos padalinys Klaipėdoje.</t>
+          <t>Gelžbetoninių konstrukcijų gamyba Vilniuje.</t>
         </is>
       </c>
       <c r="U20" s="5" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
+          <t>https://www.gkg3.lt/</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
+          <t>https://gkg3.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/lt/produkcija/betono-misiniai/gamyba-transportavimas</t>
+          <t>https://gkg3.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Perdangos puslapis nurodo, kad Klaipėdoje betono mišiniai gaminami STETTER technologinėmis linijomis. Maišyklės ir našumo duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
+          <t>Koordinatės patikslintos pagal oficialaus GKG3 kontaktų puslapio Google Maps nuorodą.</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>kauno-gelzbetonis-kaunas</t>
+          <t>perdanga-vilnius</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>UAB Kauno gelžbetonis</t>
+          <t>UAB Perdanga</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Kauno gelžbetonis</t>
+          <t>Perdanga</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2915,24 +2923,24 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Pramonės pr. 8, Kaunas</t>
+          <t>Lentvario g. 16, Vilnius</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>54.9122829</v>
+        <v>54.642372</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>23.9864942</v>
+        <v>25.1441455</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2961,40 +2969,40 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Kauno gelžbetonio gamykla</t>
+          <t>Perdanga Vilniaus gamykla</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>150 m³/val.</t>
+        </is>
+      </c>
       <c r="S21" s="4" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas gelžbetonio gamintojas Kaune.</t>
+          <t>Viešai nurodoma nauja gelžbetonio elementų gamybos linija, kurios našumas 150 m³/val.</t>
         </is>
       </c>
       <c r="U21" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaunogelzbetonis.lt/</t>
+          <t>https://www.perdanga.lt/</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
+          <t>https://www.perdanga.lt/</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t>Oficialus Kauno gelžbetonio kontaktų puslapis patvirtina Pramonės pr. 8 adresą.</t>
-        </is>
-      </c>
+          <t>https://www.perdanga.lt/</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -3004,18 +3012,18 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ukmerges-gelzbetonis-ukmerge</t>
+          <t>perdanga-klaipeda</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>UAB Ukmergės gelžbetonis</t>
+          <t>UAB Perdanga</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Ukmergės gelžbetonis</t>
+          <t>Perdanga</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3025,24 +3033,24 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Ukmergė</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Ukmergės r. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Antakalnio g. 60, Ukmergė</t>
+          <t>Dubysos g. 27, Klaipėda</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>55.2419448</v>
+        <v>55.6923067</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>24.7875927</v>
+        <v>21.1631559</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -3071,61 +3079,69 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Ukmergės gelžbetonio gamykla</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
+          <t>Stetter</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2x1,5 m³</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>40-50 m³/h</t>
+        </is>
+      </c>
       <c r="S22" s="4" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas gelžbetonio gamintojas Ukmergėje.</t>
+          <t>Viešai skelbiamas Perdangos padalinys Klaipėdoje.</t>
         </is>
       </c>
       <c r="U22" s="5" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>https://ukmergesgelzbetonis.lt/</t>
+          <t>https://www.perdanga.lt/</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>https://ukmergesgelzbetonis.lt/</t>
+          <t>https://www.perdanga.lt/</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>https://ukmergesgelzbetonis.lt/</t>
+          <t>https://www.perdanga.lt/lt/produkcija/betono-misiniai/gamyba-transportavimas</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Ukmergės gelžbetonio svetainė palikta kaip pagrindinis šaltinis; naujų patikimų koordinačių nerasta.</t>
+          <t>Oficialus Perdangos puslapis nurodo, kad Klaipėdoje betono mišiniai gaminami STETTER technologinėmis linijomis. Maišyklės ir našumo duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>gelzbetonines-konstrukcijos-siauliai</t>
+          <t>kauno-gelzbetonis-kaunas</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelžbetoninės konstrukcijos</t>
+          <t>UAB Kauno gelžbetonis</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninės konstrukcijos</t>
+          <t>Kauno gelžbetonis</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3135,38 +3151,38 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Šiauliai</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių m. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Sodo g. 20A, Šiauliai</t>
+          <t>Pramonės pr. 8, Kaunas</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>55.9495824</v>
+        <v>54.9122829</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>23.3105291</v>
+        <v>23.9864942</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Oficialios žemėlapio nuorodos taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninės konstrukcijos kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3181,7 +3197,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninių konstrukcijų gamykla</t>
+          <t>Kauno gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -3189,7 +3205,7 @@
       <c r="S23" s="4" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas gelžbetonio gamintojas Šiauliuose.</t>
+          <t>Viešai skelbiamas gelžbetonio gamintojas Kaune.</t>
         </is>
       </c>
       <c r="U23" s="5" t="n">
@@ -3197,22 +3213,22 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/</t>
+          <t>https://www.kaunogelzbetonis.lt/</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>Koordinatės patikslintos pagal oficialaus kontaktų puslapio žemėlapio tašką.</t>
+          <t>Oficialus Kauno gelžbetonio kontaktų puslapis patvirtina Pramonės pr. 8 adresą.</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3224,18 +3240,18 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>inhus-senieji-trakai</t>
+          <t>ukmerges-gelzbetonis-ukmerge</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>UAB INHUS Lietuva</t>
+          <t>UAB Ukmergės gelžbetonis</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>INHUS</t>
+          <t>Ukmergės gelžbetonis</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3245,24 +3261,24 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Senieji Trakai</t>
+          <t>Ukmergė</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Trakų r. sav.</t>
+          <t>Ukmergės r. sav.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Plačioji g. 27, Senieji Trakai</t>
+          <t>Antakalnio g. 60, Ukmergė</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>54.6140174</v>
+        <v>55.2419448</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>24.980818</v>
+        <v>24.7875927</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -3286,12 +3302,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Surenkamas gelžbetonis</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>INHUS gelžbetonio gamykla</t>
+          <t>Ukmergės gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -3299,7 +3315,7 @@
       <c r="S24" s="4" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas surenkamojo gelžbetonio konstrukcijų gamintojas.</t>
+          <t>Viešai skelbiamas gelžbetonio gamintojas Ukmergėje.</t>
         </is>
       </c>
       <c r="U24" s="5" t="n">
@@ -3307,20 +3323,24 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
+          <t>https://ukmergesgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
+          <t>https://ukmergesgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr"/>
+          <t>https://ukmergesgelzbetonis.lt/</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>Oficiali Ukmergės gelžbetonio svetainė palikta kaip pagrindinis šaltinis; naujų patikimų koordinačių nerasta.</t>
+        </is>
+      </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -3330,18 +3350,18 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>gelmesta-vievis</t>
+          <t>gelzbetonines-konstrukcijos-siauliai</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelmesta</t>
+          <t>UAB Gelžbetoninės konstrukcijos</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Gelmesta</t>
+          <t>Gelžbetoninės konstrukcijos</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3351,53 +3371,53 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Vievis</t>
+          <t>Šiauliai</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Elektrėnų sav.</t>
+          <t>Šiaulių m. sav.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Statybininkų g. 1B, Vievis</t>
+          <t>Sodo g. 20A, Šiauliai</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>54.7782794</v>
+        <v>55.9495824</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>24.8280365</v>
+        <v>23.3105291</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialios žemėlapio nuorodos taškas</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Gelžbetoninės konstrukcijos kontaktų puslapis</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Gelmesta betono mazgas</t>
+          <t>Gelžbetoninių konstrukcijų gamykla</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -3405,28 +3425,32 @@
       <c r="S25" s="4" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas.</t>
+          <t>Viešai skelbiamas gelžbetonio gamintojas Šiauliuose.</t>
         </is>
       </c>
       <c r="U25" s="5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>https://gelmesta.lt/</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>https://gelmesta.lt/</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>https://gelmesta.lt/</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr"/>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>Koordinatės patikslintos pagal oficialaus kontaktų puslapio žemėlapio tašką.</t>
+        </is>
+      </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -3436,22 +3460,18 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>suduvos-betonas-marijampole</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>302330957</t>
-        </is>
-      </c>
+          <t>inhus-senieji-trakai</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>UAB Surenkamos statybos konstrukcijos</t>
+          <t>UAB INHUS Lietuva</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Sūduvos betonas</t>
+          <t>INHUS</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3461,24 +3481,24 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Senieji Trakai</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Trakų r. sav.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Sporto g. 9H, LT-68108 Marijampolė</t>
+          <t>Plačioji g. 27, Senieji Trakai</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>54.5702553</v>
+        <v>54.6140174</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>23.3803405</v>
+        <v>24.980818</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3497,87 +3517,67 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Surenkamas gelžbetonis</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Sūduvos betono mazgas</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>iki 200 m³ per darbo pamainą</t>
-        </is>
-      </c>
-      <c r="S26" s="4" t="inlineStr">
-        <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
+          <t>INHUS gelžbetonio gamykla</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje nurodoma betono mišinių gamyba ir pristatymas; Marijampolėje esantis 130 arų betono mazgas gali pagaminti iki 200 m³ betono per darbo pamainą.</t>
+          <t>Viešai skelbiamas surenkamojo gelžbetonio konstrukcijų gamintojas.</t>
         </is>
       </c>
       <c r="U26" s="5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>https://www.suduvos-betonas.lt/</t>
+          <t>https://inhus.eu/</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>https://www.suduvos-betonas.lt/kontaktai/</t>
+          <t>https://inhus.eu/</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>https://www.suduvos-betonas.lt/betono-misiniai/</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t>Atnaujinta pagal oficialų suduvos-betonas.lt kontaktų, pradinį ir betono mišinių puslapius: juridinis pavadinimas, įmonės kodas, adresas, betono mišinių veikla ir viešas mazgo aprašymas.</t>
-        </is>
-      </c>
+          <t>https://inhus.eu/</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>statkasta-kaunas</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>185607978</t>
-        </is>
-      </c>
+          <t>gelmesta-vievis</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>UAB Statkasta</t>
+          <t>UAB Gelmesta</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Statkasta</t>
+          <t>Gelmesta</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3587,38 +3587,38 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Serdokai</t>
+          <t>Vievis</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Vilkaviškio r. sav.</t>
+          <t>Elektrėnų sav.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Gėlių g. 34, Serdokų k., Vilkaviškio r., LT-70201</t>
+          <t>Statybininkų g. 1B, Vievis</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>54.6279368</v>
+        <v>54.7782794</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>23.0871345</v>
+        <v>24.8280365</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Vietovės lygio taškas; reikia tikslesnio adreso taško</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS geokodavimas pagal oficialų Statkasta adresą</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3633,23 +3633,15 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Statkasta betono mazgas</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>Ammann Elba CBT60SL, 1 m³</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>iki 60 m³/h</t>
-        </is>
-      </c>
+          <t>Gelmesta betono mazgas</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
       <c r="S27" s="4" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgo gamintojas Ammann Elba; modelis CBT60SL; maišyklė 1 m³; našumas iki 60 m³/h.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas.</t>
         </is>
       </c>
       <c r="U27" s="5" t="n">
@@ -3657,45 +3649,45 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/</t>
+          <t>https://gelmesta.lt/</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/kontaktai/</t>
+          <t>https://gelmesta.lt/</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t>Oficialiame Statkasta kontaktų puslapyje nurodytas adresas Gėlių g. 34, Serdokų k.; koordinatės geokoduotos iki vietovės lygio. Rankiniu būdu papildyta techninė informacija: gamintojas Ammann Elba, modelis CBT60SL, maišyklė 1 m³, našumas iki 60 m³/h.</t>
-        </is>
-      </c>
+          <t>https://gelmesta.lt/</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>autokausta-kaunas</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr"/>
+          <t>suduvos-betonas-marijampole</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>302330957</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>UAB Autokausta</t>
+          <t>UAB Surenkamos statybos konstrukcijos</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Autokausta</t>
+          <t>Sūduvos betonas</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3705,24 +3697,24 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Marvelės g. 199B, Kaunas</t>
+          <t>Sporto g. 9H, LT-68108 Marijampolė</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>54.9007881</v>
+        <v>54.5702553</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>23.8489377</v>
+        <v>23.3803405</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3749,63 +3741,79 @@
           <t>Betono mišiniai</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Sūduvos betono mazgas</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>iki 200 m³ per darbo pamainą</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo pavadinimą reikia patikslinti.</t>
+          <t>Oficialiame puslapyje nurodoma betono mišinių gamyba ir pristatymas; Marijampolėje esantis 130 arų betono mazgas gali pagaminti iki 200 m³ betono per darbo pamainą.</t>
         </is>
       </c>
       <c r="U28" s="5" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>https://autokausta.lt/</t>
+          <t>https://www.suduvos-betonas.lt/</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
+          <t>https://www.suduvos-betonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
+          <t>https://www.suduvos-betonas.lt/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Autokausta betono puslapis patvirtina betono veiklą ir Marvelės g. 199B kontaktą.</t>
+          <t>Atnaujinta pagal oficialų suduvos-betonas.lt kontaktų, pradinį ir betono mišinių puslapius: juridinis pavadinimas, įmonės kodas, adresas, betono mišinių veikla ir viešas mazgo aprašymas.</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>betono-baze-visaginas</t>
+          <t>statkasta-kaunas</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>302725961</t>
+          <t>185607978</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono bazė</t>
+          <t>UAB Statkasta</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Betono bazė</t>
+          <t>Statkasta</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3815,38 +3823,38 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Visaginas</t>
+          <t>Serdokai</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Visagino sav.</t>
+          <t>Vilkaviškio r. sav.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Elektrinės g. 11, Drūkšinių k., Visagino sav.</t>
+          <t>Gėlių g. 34, Serdokų k., Vilkaviškio r., LT-70201</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>55.5963685</v>
+        <v>54.6279368</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>26.5817201</v>
+        <v>23.0871345</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Vietovės lygio taškas; reikia tikslesnio adreso taško</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>ArcGIS geokodavimas pagal oficialų Statkasta adresą</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://statkasta.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3861,61 +3869,69 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Betono bazė</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
+          <t>Statkasta betono mazgas</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Ammann Elba CBT60SL, 1 m³</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>iki 60 m³/h</t>
+        </is>
+      </c>
       <c r="S29" s="4" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo adresą reikia patikslinti.</t>
+          <t>Betono mazgo gamintojas Ammann Elba; modelis CBT60SL; maišyklė 1 m³; našumas iki 60 m³/h.</t>
         </is>
       </c>
       <c r="U29" s="5" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonobaze.lt/</t>
+          <t>https://statkasta.lt/</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonobaze.lt/kontaktai</t>
+          <t>https://statkasta.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonobaze.lt/kontaktai</t>
+          <t>https://statkasta.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Elektrinės g. 11 adresą ir betono bazės veiklą.</t>
+          <t>Oficialiame Statkasta kontaktų puslapyje nurodytas adresas Gėlių g. 34, Serdokų k.; koordinatės geokoduotos iki vietovės lygio. Rankiniu būdu papildyta techninė informacija: gamintojas Ammann Elba, modelis CBT60SL, maišyklė 1 m³, našumas iki 60 m³/h.</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>transdosa-druskininkai</t>
+          <t>autokausta-kaunas</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UAB Transdosa</t>
+          <t>UAB Autokausta</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Transdosa</t>
+          <t>Autokausta</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3925,24 +3941,24 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Druskininkai</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Druskininkų sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Žvyro g. 2A, Margų k., Druskininkų sav.</t>
+          <t>Marvelės g. 199B, Kaunas</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>54.146785</v>
+        <v>54.9007881</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>23.9291769</v>
+        <v>23.8489377</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3969,100 +3985,90 @@
           <t>Betono mišiniai</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>Elkomix-90 quick master</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1,5 m³</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>40 m³/h</t>
-        </is>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="4" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas Druskininkų regione.</t>
+          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo pavadinimą reikia patikslinti.</t>
         </is>
       </c>
       <c r="U30" s="5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>https://transdosa.lt/</t>
+          <t>https://autokausta.lt/</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>https://www.transdosa.lt/kontaktai/</t>
+          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>https://www.transdosa.lt/betonas/</t>
+          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>Oficialūs Transdosa kontaktų ir betono puslapiai patvirtina Margų karjero betono gamybą adresu Žvyro g. 2A. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialus Autokausta betono puslapis patvirtina betono veiklą ir Marvelės g. 199B kontaktą.</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>sodbeta-siauliai</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr"/>
+          <t>betono-baze-visaginas</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>302725961</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>UAB Sodbeta</t>
+          <t>UAB Betono bazė</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Sodbeta</t>
+          <t>Betono bazė</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Šiauliai</t>
+          <t>Visaginas</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių m. sav.</t>
+          <t>Visagino sav.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Sodo g. 20, Šiauliai</t>
+          <t>Elektrinės g. 11, Drūkšinių k., Visagino sav.</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>55.949032</v>
+        <v>55.5963685</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>23.3125879</v>
+        <v>26.5817201</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -4081,17 +4087,17 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Sodbeta betono gaminių gamykla</t>
+          <t>Betono bazė</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
@@ -4099,98 +4105,94 @@
       <c r="S31" s="4" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama gelžbetonio ir betono gaminių gamyba Šiauliuose.</t>
+          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo adresą reikia patikslinti.</t>
         </is>
       </c>
       <c r="U31" s="5" t="n">
-        <v>0.82</v>
+        <v>0.65</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>https://sodbeta.lt/</t>
+          <t>https://www.betonobaze.lt/</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>https://sodbeta.lt/</t>
+          <t>https://www.betonobaze.lt/kontaktai</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>https://sodbeta.lt/betonas/betono-misiniai/</t>
+          <t>https://www.betonobaze.lt/kontaktai</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Sodbeta svetainė patvirtina Sodo g. 20 adresą ir betono mišinių puslapį.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Elektrinės g. 11 adresą ir betono bazės veiklą.</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>alytaus-gelzbetonis-alytus</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>149720232</t>
-        </is>
-      </c>
+          <t>transdosa-druskininkai</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>AB Alytaus gelžbetonis</t>
+          <t>UAB Transdosa</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Alytaus gelžbetonis</t>
+          <t>Transdosa</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Alytus</t>
+          <t>Druskininkai</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Alytaus m. sav.</t>
+          <t>Druskininkų sav.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Pramonės g. 15, Alytus</t>
+          <t>Žvyro g. 2A, Margų k., Druskininkų sav.</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>54.426129</v>
+        <v>54.146785</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>24.016482</v>
+        <v>23.9291769</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Oficialaus kontaktų puslapio žemėlapio taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Alytaus gelžbetonis kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4205,61 +4207,71 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Alytaus gelžbetonio gamykla</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr"/>
+          <t>Elkomix-90 quick master</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1,5 m³</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>40 m³/h</t>
+        </is>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Druskininkų regione.</t>
         </is>
       </c>
       <c r="U32" s="5" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/</t>
+          <t>https://transdosa.lt/</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
+          <t>https://www.transdosa.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
+          <t>https://www.transdosa.lt/betonas/</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>Patikslinta pagal oficialų kontaktų puslapį.</t>
+          <t>Oficialūs Transdosa kontaktų ir betono puslapiai patvirtina Margų karjero betono gamybą adresu Žvyro g. 2A. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>gernora-marijampole</t>
+          <t>sodbeta-siauliai</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>UAB Gernora</t>
+          <t>UAB Sodbeta</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Gernora</t>
+          <t>Sodbeta</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4269,53 +4281,53 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Šiauliai</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Šiaulių m. sav.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Vingio g. 2M, LT-68131 Marijampolė</t>
+          <t>Sodo g. 20, Šiauliai</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>54.5356806</v>
+        <v>55.949032</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>23.3349754</v>
+        <v>23.3125879</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Oficialios Google Maps nuorodos taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Gernora kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Gernora betono mazgas</t>
+          <t>Sodbeta betono gaminių gamykla</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
@@ -4323,30 +4335,30 @@
       <c r="S33" s="4" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas Marijampolėje.</t>
+          <t>Viešai skelbiama gelžbetonio ir betono gaminių gamyba Šiauliuose.</t>
         </is>
       </c>
       <c r="U33" s="5" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/</t>
+          <t>https://sodbeta.lt/</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/kontaktai/</t>
+          <t>https://sodbeta.lt/</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/kontaktai/</t>
+          <t>https://sodbeta.lt/betonas/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>Koordinatės patikslintos pagal oficialaus Gernora kontaktų puslapio Google Maps nuorodą.</t>
+          <t>Oficiali Sodbeta svetainė patvirtina Sodo g. 20 adresą ir betono mišinių puslapį.</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4358,18 +4370,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>re-betono-konstrukcijos-kretinga</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr"/>
+          <t>alytaus-gelzbetonis-alytus</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>149720232</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>UAB RE Betono konstrukcijos</t>
+          <t>AB Alytaus gelžbetonis</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>RE Betono konstrukcijos</t>
+          <t>Alytaus gelžbetonis</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4379,53 +4395,53 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Kretinga</t>
+          <t>Alytus</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Kretingos r. sav.</t>
+          <t>Alytaus m. sav.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiekėjų g. 27B, Kretinga</t>
+          <t>Pramonės g. 15, Alytus</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>55.87963</v>
+        <v>54.426129</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>21.220888</v>
+        <v>24.016482</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialaus kontaktų puslapio žemėlapio taškas</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Alytaus gelžbetonis kontaktų puslapis</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>RE Betono konstrukcijų gamyba</t>
+          <t>Alytaus gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -4433,26 +4449,30 @@
       <c r="S34" s="4" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, cemento gaminiai, betono siurblys ir pamatų blokai Kretingoje.</t>
+          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U34" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>https://alytausgelzbetonis.lt/</t>
+        </is>
+      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
+          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
+          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>Katalogo šaltinis, reikia patikslinti gamybos apimtį.</t>
+          <t>Patikslinta pagal oficialų kontaktų puslapį.</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4464,18 +4484,18 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>silales-statyba-vingininkai</t>
+          <t>gernora-marijampole</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilalės statyba</t>
+          <t>UAB Gernora</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Šilalės statyba</t>
+          <t>Gernora</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4485,53 +4505,53 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Vingininkai</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Šilalės r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Lauryno Ivinskio g. 7, Vingininkai, Šilalės r.</t>
+          <t>Vingio g. 2M, LT-68131 Marijampolė</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>55.4808479</v>
+        <v>54.5356806</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>22.1937399</v>
+        <v>23.3349754</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialios Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Gernora kontaktų puslapis</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://gernora.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Šilalės statybos betono gaminių gamyba</t>
+          <t>Gernora betono mazgas</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -4539,30 +4559,30 @@
       <c r="S35" s="4" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių ir statybinių konstrukcijų veikla Šilalės rajone.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Marijampolėje.</t>
         </is>
       </c>
       <c r="U35" s="5" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>https://www.silalesstatyba.lt/</t>
+          <t>https://gernora.lt/</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>https://www.silalesstatyba.lt/</t>
+          <t>https://gernora.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>https://www.silalesstatyba.lt/</t>
+          <t>https://gernora.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti tikslų gaminių asortimentą.</t>
+          <t>Koordinatės patikslintos pagal oficialaus Gernora kontaktų puslapio Google Maps nuorodą.</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4574,18 +4594,18 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>panevezio-gelzbetonis-panevezys</t>
+          <t>re-betono-konstrukcijos-kretinga</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>UAB Panevėžio gelžbetonis</t>
+          <t>UAB RE Betono konstrukcijos</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio gelžbetonis</t>
+          <t>RE Betono konstrukcijos</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4595,24 +4615,24 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kretinga</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Kretingos r. sav.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Tiekėjų g. 27B, Kretinga</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.87963</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>24.3803541</v>
+        <v>21.220888</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -4636,12 +4656,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio gelžbetonio gamykla</t>
+          <t>RE Betono konstrukcijų gamyba</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -4649,7 +4669,7 @@
       <c r="S36" s="4" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>Viešame įmonių kataloge nurodomas gelžbetonio gaminių profilis Panevėžyje.</t>
+          <t>Viešame kataloge nurodomi betonas, cemento gaminiai, betono siurblys ir pamatų blokai Kretingoje.</t>
         </is>
       </c>
       <c r="U36" s="5" t="n">
@@ -4658,17 +4678,17 @@
       <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
+          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
+          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikrinti veiklos aktyvumą ir produkcijos apimtį.</t>
+          <t>Katalogo šaltinis, reikia patikslinti gamybos apimtį.</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4680,18 +4700,18 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>pamatas-telsiai</t>
+          <t>silales-statyba-vingininkai</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>UAB Pamatas</t>
+          <t>UAB Šilalės statyba</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Pamatas</t>
+          <t>Šilalės statyba</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4701,24 +4721,24 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Vingininkai</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Šilalės r. sav.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Tryškių g. 46, Dimaičių k., Telšių r.</t>
+          <t>Lauryno Ivinskio g. 7, Vingininkai, Šilalės r.</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>55.9874536</v>
+        <v>55.4808479</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>22.287162</v>
+        <v>22.1937399</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4747,7 +4767,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Pamatas betono gaminių gamyba</t>
+          <t>Šilalės statybos betono gaminių gamyba</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -4755,7 +4775,7 @@
       <c r="S37" s="4" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiami pamatų ir kiti betono gaminiai Telšių rajone.</t>
+          <t>Viešai skelbiama betono gaminių ir statybinių konstrukcijų veikla Šilalės rajone.</t>
         </is>
       </c>
       <c r="U37" s="5" t="n">
@@ -4763,22 +4783,22 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://www.silalesstatyba.lt/</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://www.silalesstatyba.lt/</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://www.silalesstatyba.lt/</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>Adresas patikslintas pagal lietuvišką įmonės puslapį; koordinatės nustatytos Lietuvos geolokatoriumi.</t>
+          <t>Reikia patikslinti tikslų gaminių asortimentą.</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4790,18 +4810,18 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>vilniaus-betono-gaminiai-vilnius</t>
+          <t>panevezio-gelzbetonis-panevezys</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>UAB Vilniaus betono gaminiai</t>
+          <t>UAB Panevėžio gelžbetonis</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>HAUS / Vilniaus betono gaminiai</t>
+          <t>Panevėžio gelžbetonis</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4811,24 +4831,24 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>A. Jakšto g. 5, Vilnius</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>54.6888177</v>
+        <v>55.7409491</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>25.2756813</v>
+        <v>24.3803541</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4852,12 +4872,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus betono gaminiai</t>
+          <t>Panevėžio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -4865,30 +4885,26 @@
       <c r="S38" s="4" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas HAUS blokelių ir betono gaminių gamintojas.</t>
+          <t>Viešame įmonių kataloge nurodomas gelžbetonio gaminių profilis Panevėžyje.</t>
         </is>
       </c>
       <c r="U38" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vbg.lt/</t>
-        </is>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>Žemėlapyje naudotas viešai skelbiamas įmonės adresas; gamybos vietą reikia patikslinti.</t>
+          <t>Reikia patikrinti veiklos aktyvumą ir produkcijos apimtį.</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4900,18 +4916,18 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>pamario-grupe-kalnuvenai</t>
+          <t>pamatas-telsiai</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>UAB Pamario grupė</t>
+          <t>UAB Pamatas</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupė</t>
+          <t>Pamatas</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4921,24 +4937,24 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Kalnuvėnai</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Kaukėnų g. 12, Kalnuvėnai, Klaipėdos r.</t>
+          <t>Tryškių g. 46, Dimaičių k., Telšių r.</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.7905468</v>
+        <v>55.9874536</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>21.1471136</v>
+        <v>22.287162</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4957,17 +4973,17 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupės betono mazgas</t>
+          <t>Pamatas betono gaminių gamyba</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -4975,30 +4991,30 @@
       <c r="S39" s="4" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Klaipėdos rajone.</t>
+          <t>Viešai skelbiami pamatų ir kiti betono gaminiai Telšių rajone.</t>
         </is>
       </c>
       <c r="U39" s="5" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą ir gamybos režimą.</t>
+          <t>Adresas patikslintas pagal lietuvišką įmonės puslapį; koordinatės nustatytos Lietuvos geolokatoriumi.</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5010,18 +5026,18 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>betono-zona-klaipeda</t>
+          <t>vilniaus-betono-gaminiai-vilnius</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono zona</t>
+          <t>UAB Vilniaus betono gaminiai</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>HAUS / Vilniaus betono gaminiai</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5031,24 +5047,24 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g. 6, Klaipėda</t>
+          <t>A. Jakšto g. 5, Vilnius</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>55.7549809</v>
+        <v>54.6888177</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>21.150509</v>
+        <v>25.2756813</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -5077,7 +5093,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Vilniaus betono gaminiai</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -5085,30 +5101,30 @@
       <c r="S40" s="4" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
+          <t>Viešai skelbiamas HAUS blokelių ir betono gaminių gamintojas.</t>
         </is>
       </c>
       <c r="U40" s="5" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://www.vbg.lt/</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://www.vbg.lt/</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://www.vbg.lt/</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
+          <t>Žemėlapyje naudotas viešai skelbiamas įmonės adresas; gamybos vietą reikia patikslinti.</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5120,22 +5136,18 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>topbeton-panevezys</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>307083610</t>
-        </is>
-      </c>
+          <t>pamario-grupe-kalnuvenai</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>UAB Topbeton</t>
+          <t>UAB Pamario grupė</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Topbeton</t>
+          <t>Pamario grupė</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5145,24 +5157,24 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kalnuvėnai</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Beržų g. 5C, Panevėžys</t>
+          <t>Kaukėnų g. 12, Kalnuvėnai, Klaipėdos r.</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>55.7168572</v>
+        <v>55.7905468</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>24.3617863</v>
+        <v>21.1471136</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -5191,7 +5203,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Topbeton betono mazgas</t>
+          <t>Pamario grupės betono mazgas</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -5199,30 +5211,30 @@
       <c r="S41" s="4" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U41" s="5" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>https://topbeton.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
+          <t>Reikia patikslinti našumą ir gamybos režimą.</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5234,18 +5246,18 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>gelzbetonio-gamyba-panevezys</t>
+          <t>betono-zona-klaipeda</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>MB Gelžbetonio gamyba</t>
+          <t>UAB Betono zona</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5255,24 +5267,24 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Dvaro g. 6, Klaipėda</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.7549809</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>24.3803541</v>
+        <v>21.150509</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -5296,12 +5308,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba Panevėžyje</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -5309,30 +5321,30 @@
       <c r="S42" s="4" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
         </is>
       </c>
       <c r="U42" s="5" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
+          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5344,18 +5356,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>inroma-pakruojis</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr"/>
+          <t>topbeton-panevezys</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>307083610</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>UAB Inroma</t>
+          <t>UAB Topbeton</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Inroma</t>
+          <t>Topbeton</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5365,24 +5381,24 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Pakruojis</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Pakruojo r. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Pramonės g. 5B, Pakruojis</t>
+          <t>Beržų g. 5C, Panevėžys</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>55.9763263</v>
+        <v>55.7168572</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>23.8584712</v>
+        <v>24.3617863</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -5411,7 +5427,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Inroma betono mazgas</t>
+          <t>Topbeton betono mazgas</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -5419,30 +5435,30 @@
       <c r="S43" s="4" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
+          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U43" s="5" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://topbeton.lt/</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5454,18 +5470,18 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>seldra-vilnius</t>
+          <t>gelzbetonio-gamyba-panevezys</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>UAB Seldra</t>
+          <t>MB Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Seldra</t>
+          <t>Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5475,24 +5491,24 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>O. Miciūtės g. 7, Vilnius</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>54.7424422</v>
+        <v>55.7409491</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>25.2535408</v>
+        <v>24.3803541</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -5511,17 +5527,17 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Seldra prekinio betono gamyba</t>
+          <t>Gelžbetonio gamyba Panevėžyje</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -5529,26 +5545,30 @@
       <c r="S44" s="4" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodoma prekinio betono gamyba ir prekyba Vilniuje.</t>
+          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U44" s="5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr"/>
+        <v>0.72</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>https://gelzbetoniogamyba.lt/</t>
+        </is>
+      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/seldra-uab-prekinio-betono-gamyba-ir-prekyba-vilniuje-219193/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/seldra-uab-prekinio-betono-gamyba-ir-prekyba-vilniuje-219193/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>Koordinatė apytikslė pagal adresą; reikia patikslinti gamybos tašką.</t>
+          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5560,22 +5580,18 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>utenos-betonas-utena</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>300904691</t>
-        </is>
-      </c>
+          <t>inroma-pakruojis</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>UAB Utenos betonas</t>
+          <t>UAB Inroma</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Utenos betonas</t>
+          <t>Inroma</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5585,24 +5601,24 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Pakruojis</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Utenos r. sav.</t>
+          <t>Pakruojo r. sav.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Metalo g. 9B, Utena</t>
+          <t>Pramonės g. 5B, Pakruojis</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>55.4947607</v>
+        <v>55.9763263</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>25.6225075</v>
+        <v>23.8584712</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -5631,7 +5647,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Utenos betono mazgas</t>
+          <t>Inroma betono mazgas</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -5639,30 +5655,30 @@
       <c r="S45" s="4" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
         </is>
       </c>
       <c r="U45" s="5" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>https://utenosbetonas.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
+          <t>Reikia patikslinti našumą.</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5674,22 +5690,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>sbetonas-jonava</t>
+          <t>utenos-betonas-utena</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>300902683</t>
+          <t>300904691</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>UAB Sbetonas</t>
+          <t>UAB Utenos betonas</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas</t>
+          <t>Utenos betonas</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5699,24 +5715,24 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Jonava</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Utenos r. sav.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Skarulių g. 58, Jonava</t>
+          <t>Metalo g. 9B, Utena</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>55.0786452</v>
+        <v>55.4947607</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>24.3199072</v>
+        <v>25.6225075</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5745,7 +5761,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas betono mazgas</t>
+          <t>Utenos betono mazgas</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -5753,7 +5769,7 @@
       <c r="S46" s="4" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
         </is>
       </c>
       <c r="U46" s="5" t="n">
@@ -5761,22 +5777,22 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://utenosbetonas.lt/</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta pagal prekinio betono požymį.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5788,18 +5804,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>kalcitas-naujoji-akmene</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr"/>
+          <t>sbetonas-jonava</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>300902683</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>AB Kalcitas</t>
+          <t>UAB Sbetonas</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas</t>
+          <t>Sbetonas</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5809,24 +5829,24 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Jonava</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Skarulių g. 58, Jonava</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>56.3143832</v>
+        <v>55.0786452</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>22.9130704</v>
+        <v>24.3199072</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5855,7 +5875,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas betono mišinių gamybos linija</t>
+          <t>Sbetonas betono mazgas</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -5863,26 +5883,30 @@
       <c r="S47" s="4" t="inlineStr"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
+          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
         </is>
       </c>
       <c r="U47" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="V47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>https://sbetonas.lt/</t>
+        </is>
+      </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
+          <t>Papildomai rasta pagal prekinio betono požymį.</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -5894,18 +5918,18 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
+          <t>kalcitas-naujoji-akmene</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelgaudiškio gelžbetonis</t>
+          <t>AB Kalcitas</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonis</t>
+          <t>Kalcitas</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5915,24 +5939,24 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškis</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Šakių r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>55.07067</v>
+        <v>56.3143832</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>22.976723</v>
+        <v>22.9130704</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5941,27 +5965,27 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>GLG kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai ir gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonio gamykla</t>
+          <t>Kalcitas betono mišinių gamybos linija</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -5969,30 +5993,26 @@
       <c r="S48" s="4" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
+          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
         </is>
       </c>
       <c r="U48" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/</t>
-        </is>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr"/>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/betonas/betono-misiniai/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
+          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6004,22 +6024,18 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>sausta-trakai</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>145744638</t>
-        </is>
-      </c>
+          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>UAB Sausta</t>
+          <t>UAB Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Sausta</t>
+          <t>Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -6029,24 +6045,24 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Gelgaudiškis</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Trakų r. sav.</t>
+          <t>Šakių r. sav.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Karaimų g. 73, Trakai</t>
+          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>54.6523614</v>
+        <v>55.07067</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>24.9221724</v>
+        <v>22.976723</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -6055,27 +6071,27 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>GLG kontaktų puslapis</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono mišiniai ir gelžbetonis</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Sausta betono mišinių veikla</t>
+          <t>Gelgaudiškio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -6083,26 +6099,30 @@
       <c r="S49" s="4" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge įmonė siejama su betono mišinių veikla.</t>
+          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
         </is>
       </c>
       <c r="U49" s="5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>https://glg.lt/</t>
+        </is>
+      </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/sausta-uab-240915/</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/sausta-uab-240915/</t>
+          <t>https://glg.lt/betonas/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>Žemos pasitikėjimo įrašas; reikia patikslinti, ar gamyba vykdoma šiame taške.</t>
+          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6114,49 +6134,49 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ginfa-kutiskiai</t>
+          <t>sausta-trakai</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>302680943</t>
+          <t>145744638</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>UAB GinFa</t>
+          <t>UAB Sausta</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>GinFa</t>
+          <t>Sausta</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai rasta</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Kutiškiai</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Trakų r. sav.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
+          <t>Karaimų g. 73, Trakai</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>55.8326273</v>
+        <v>54.6523614</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>23.4995317</v>
+        <v>24.9221724</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -6185,7 +6205,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>GinFa betono gamyba</t>
+          <t>Sausta betono mišinių veikla</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -6193,22 +6213,26 @@
       <c r="S50" s="4" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Viešame kataloge įmonė siejama su betono mišinių veikla.</t>
         </is>
       </c>
       <c r="U50" s="5" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X50" s="2" t="inlineStr"/>
+          <t>https://www.1551.lt/sausta-uab-240915/</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.1551.lt/sausta-uab-240915/</t>
+        </is>
+      </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Žemos pasitikėjimo įrašas; reikia patikslinti, ar gamyba vykdoma šiame taške.</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6220,22 +6244,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>antano-gribino-imone-prienai</t>
+          <t>ginfa-kutiskiai</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>170687267</t>
+          <t>302680943</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
+          <t>UAB GinFa</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonė</t>
+          <t>GinFa</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6245,24 +6269,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Prienai</t>
+          <t>Kutiškiai</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Prienų r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Kęstučio g. 95A, Prienai</t>
+          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>54.6523184</v>
+        <v>55.8326273</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>23.9696591</v>
+        <v>23.4995317</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -6291,7 +6315,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonės betono gamyba</t>
+          <t>GinFa betono gamyba</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -6326,22 +6350,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>kelsera-anavilis</t>
+          <t>antano-gribino-imone-prienai</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>304642165</t>
+          <t>170687267</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>UAB Kelsera</t>
+          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Kelsera</t>
+          <t>Antano Gribino įmonė</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6351,24 +6375,24 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Anavilis</t>
+          <t>Prienai</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Prienų r. sav.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Bitininkų g. 13, Anavilis, Vilniaus r.</t>
+          <t>Kęstučio g. 95A, Prienai</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>54.9463928</v>
+        <v>54.6523184</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>25.216796</v>
+        <v>23.9696591</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -6397,7 +6421,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Kelsera betono gamyba</t>
+          <t>Antano Gribino įmonės betono gamyba</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -6432,22 +6456,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>altimas-avizieniai</t>
+          <t>kelsera-anavilis</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>301699702</t>
+          <t>304642165</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>UAB Altimas</t>
+          <t>UAB Kelsera</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Altimas</t>
+          <t>Kelsera</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6457,7 +6481,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Avižieniai</t>
+          <t>Anavilis</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6467,14 +6491,14 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Vaikystės g. 10, Avižieniai, Vilniaus r.</t>
+          <t>Bitininkų g. 13, Anavilis, Vilniaus r.</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>54.7579388</v>
+        <v>54.9463928</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>25.1878461</v>
+        <v>25.216796</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -6503,7 +6527,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Altimas betono gamyba</t>
+          <t>Kelsera betono gamyba</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -8611,7 +8635,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T07:20:42.186376+00:00</t>
+          <t>2026-09-23T07:39:37.605548+00:00</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8690,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T07:20:42.187391+00:00</t>
+          <t>2026-09-23T07:39:37.605548+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z70" headerRowCount="1">
-  <autoFilter ref="A1:Z70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z68" headerRowCount="1">
+  <autoFilter ref="A1:Z68"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Įrašo ID"/>
     <tableColumn id="2" name="Įmonės kodas"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z70"/>
+  <dimension ref="A1:Z68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -6134,49 +6134,49 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>sausta-trakai</t>
+          <t>ginfa-kutiskiai</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>145744638</t>
+          <t>302680943</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>UAB Sausta</t>
+          <t>UAB GinFa</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Sausta</t>
+          <t>GinFa</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta</t>
+          <t>Papildomai rasta EVRK 23.63</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kutiškiai</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Trakų r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Karaimų g. 73, Trakai</t>
+          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>54.6523614</v>
+        <v>55.8326273</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>24.9221724</v>
+        <v>23.4995317</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Sausta betono mišinių veikla</t>
+          <t>GinFa betono gamyba</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -6213,26 +6213,22 @@
       <c r="S50" s="4" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge įmonė siejama su betono mišinių veikla.</t>
+          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U50" s="5" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/sausta-uab-240915/</t>
-        </is>
-      </c>
-      <c r="X50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.1551.lt/sausta-uab-240915/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr"/>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>Žemos pasitikėjimo įrašas; reikia patikslinti, ar gamyba vykdoma šiame taške.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6244,22 +6240,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ginfa-kutiskiai</t>
+          <t>antano-gribino-imone-prienai</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>302680943</t>
+          <t>170687267</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>UAB GinFa</t>
+          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>GinFa</t>
+          <t>Antano Gribino įmonė</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6269,24 +6265,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Kutiškiai</t>
+          <t>Prienai</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Prienų r. sav.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
+          <t>Kęstučio g. 95A, Prienai</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>55.8326273</v>
+        <v>54.6523184</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>23.4995317</v>
+        <v>23.9696591</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -6315,7 +6311,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>GinFa betono gamyba</t>
+          <t>Antano Gribino įmonės betono gamyba</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -6350,22 +6346,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>antano-gribino-imone-prienai</t>
+          <t>kelsera-anavilis</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>170687267</t>
+          <t>304642165</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
+          <t>UAB Kelsera</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonė</t>
+          <t>Kelsera</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6375,24 +6371,24 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Prienai</t>
+          <t>Anavilis</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Prienų r. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Kęstučio g. 95A, Prienai</t>
+          <t>Bitininkų g. 13, Anavilis, Vilniaus r.</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>54.6523184</v>
+        <v>54.9463928</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>23.9696591</v>
+        <v>25.216796</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6417,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonės betono gamyba</t>
+          <t>Kelsera betono gamyba</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -6456,22 +6452,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>kelsera-anavilis</t>
+          <t>vinido-taurage</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>304642165</t>
+          <t>306258220</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>UAB Kelsera</t>
+          <t>UAB Vinido</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Kelsera</t>
+          <t>Vinido</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6481,24 +6477,24 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Anavilis</t>
+          <t>Tauragė</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Tauragės r. sav.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Bitininkų g. 13, Anavilis, Vilniaus r.</t>
+          <t>Gaurės g. 32, Tauragė</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>54.9463928</v>
+        <v>55.2492204</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>25.216796</v>
+        <v>22.3185845</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6523,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Kelsera betono gamyba</t>
+          <t>Vinido betono gamyba</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -6541,16 +6537,24 @@
       <c r="U53" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/</t>
+        </is>
+      </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X53" s="2" t="inlineStr"/>
+          <t>https://betonastaurageje.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/betonas/</t>
+        </is>
+      </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Oficiali Vinido svetainė patvirtina Gaurės g. 32 adresą, betono gamybą ir betono mazgą.</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6562,22 +6566,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>vinido-taurage</t>
+          <t>santvara-kedainiai</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>306258220</t>
+          <t>304915297</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>UAB Vinido</t>
+          <t>UAB Santvara</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Vinido</t>
+          <t>Santvara</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6587,24 +6591,24 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Tauragė</t>
+          <t>Kėdainiai</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Tauragės r. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Gaurės g. 32, Tauragė</t>
+          <t>Aruodų g. 34, Kėdainiai</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>55.2492204</v>
+        <v>55.2634747</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>22.3185845</v>
+        <v>23.9440384</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6637,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Vinido betono gamyba</t>
+          <t>Santvara betono gamyba</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -6649,22 +6653,22 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/kontaktai/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/betonas/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Vinido svetainė patvirtina Gaurės g. 32 adresą, betono gamybą ir betono mazgą.</t>
+          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6676,22 +6680,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>santvara-kedainiai</t>
+          <t>medis-ir-betonas-naujoji-akmene</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>304915297</t>
+          <t>153074073</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>UAB Santvara</t>
+          <t>AB Medis ir betonas</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Santvara</t>
+          <t>Medis ir betonas</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6701,24 +6705,24 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Kėdainiai</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Kėdainių r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Aruodų g. 34, Kėdainiai</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>55.2634747</v>
+        <v>56.3143832</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>23.9440384</v>
+        <v>22.9130704</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -6747,7 +6751,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Santvara betono gamyba</t>
+          <t>Medis ir betonas gamyba</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -6761,24 +6765,16 @@
       <c r="U55" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
+      <c r="V55" s="2" t="inlineStr"/>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
-      <c r="X55" s="2" t="inlineStr">
-        <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr"/>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6790,22 +6786,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>eurobetonas-visaginas</t>
+          <t>ekobetonas-marijampole</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>305191384</t>
+          <t>300636364</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UAB Eurobetonas</t>
+          <t>UAB Ekobetonas</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Eurobetonas</t>
+          <t>Ekobetonas</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6815,24 +6811,24 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Visaginas</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Visagino sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Sandėlių g. 1, Karlų k., Visagino sav.</t>
+          <t>Gamyklų g. 3, Marijampolė</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>55.5732062</v>
+        <v>54.5750142</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>26.4787145</v>
+        <v>23.3796805</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -6861,7 +6857,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Eurobetonas betono gamyba</t>
+          <t>Ekobetonas betono gamyba</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -6873,18 +6869,26 @@
         </is>
       </c>
       <c r="U56" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr"/>
+        <v>0.82</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>https://ekobetonas.lt/</t>
+        </is>
+      </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X56" s="2" t="inlineStr"/>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+        </is>
+      </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Visagino miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
+          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -6896,22 +6900,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>medis-ir-betonas-naujoji-akmene</t>
+          <t>rokbetonis-rokiskis</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>153074073</t>
+          <t>304184091</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>AB Medis ir betonas</t>
+          <t>MB Rokbetonis</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas</t>
+          <t>Rokbetonis</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6921,24 +6925,24 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Rokiškis</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Rokiškio r. sav.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>56.3143832</v>
+        <v>55.9525796</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>22.9130704</v>
+        <v>25.5624197</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6967,7 +6971,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas gamyba</t>
+          <t>Rokbetonis betono gamyba</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -6979,7 +6983,7 @@
         </is>
       </c>
       <c r="U57" s="5" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="V57" s="2" t="inlineStr"/>
       <c r="W57" s="2" t="inlineStr">
@@ -6990,7 +6994,7 @@
       <c r="X57" s="2" t="inlineStr"/>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7002,22 +7006,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ekobetonas-marijampole</t>
+          <t>beton-eura-dovainonys</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>300636364</t>
+          <t>302745280</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>UAB Ekobetonas</t>
+          <t>UAB Beton Eura</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas</t>
+          <t>Beton Eura</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -7027,24 +7031,24 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Dovainonys</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Kaišiadorių r. sav.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Gamyklų g. 3, Marijampolė</t>
+          <t>Žilvičių g. 2, Dovainonys, Kaišiadorių r.</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>54.5750142</v>
+        <v>54.8395918</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>23.3796805</v>
+        <v>24.2360193</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -7073,7 +7077,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas betono gamyba</t>
+          <t>Beton Eura betono gamyba</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -7089,22 +7093,22 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>https://ekobetonas.lt/</t>
+          <t>https://www.betoneura.lt/</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+          <t>https://www.betoneura.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+          <t>https://www.betoneura.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
+          <t>Oficialus Beton Eura kontaktų puslapis patvirtina Žilvičių g. 2 adresą ir rekvizitus.</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7116,22 +7120,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>rokbetonis-rokiskis</t>
+          <t>silutes-betonas-silute</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>304184091</t>
+          <t>177392928</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>MB Rokbetonis</t>
+          <t>UAB Šilutės betonas</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis</t>
+          <t>Šilutės betonas</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -7141,24 +7145,24 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Rokiškis</t>
+          <t>Šilutė</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Rokiškio r. sav.</t>
+          <t>Šilutės r. sav.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
+          <t>Ramučių g. 1, Šilutė</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>55.9525796</v>
+        <v>55.3538641</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>25.5624197</v>
+        <v>21.4796635</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -7187,7 +7191,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis betono gamyba</t>
+          <t>Šilutės betono gamyba</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -7199,7 +7203,7 @@
         </is>
       </c>
       <c r="U59" s="5" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="V59" s="2" t="inlineStr"/>
       <c r="W59" s="2" t="inlineStr">
@@ -7207,10 +7211,14 @@
           <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
         </is>
       </c>
-      <c r="X59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
+        </is>
+      </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7222,22 +7230,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>beton-eura-dovainonys</t>
+          <t>kruszbet-lithuania-jure</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>302745280</t>
+          <t>305173596</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>UAB Beton Eura</t>
+          <t>UAB KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Beton Eura</t>
+          <t>KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7247,24 +7255,24 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Dovainonys</t>
+          <t>Jūrė</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Kaišiadorių r. sav.</t>
+          <t>Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Žilvičių g. 2, Dovainonys, Kaišiadorių r.</t>
+          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>54.8395918</v>
+        <v>54.7706307</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>24.2360193</v>
+        <v>23.4998409</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -7293,7 +7301,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Beton Eura betono gamyba</t>
+          <t>KRUSZBET Lithuania betono gamyba</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
@@ -7307,24 +7315,16 @@
       <c r="U60" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.betoneura.lt/</t>
-        </is>
-      </c>
+      <c r="V60" s="2" t="inlineStr"/>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>https://www.betoneura.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="X60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.betoneura.lt/kontaktai/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr"/>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Beton Eura kontaktų puslapis patvirtina Žilvičių g. 2 adresą ir rekvizitus.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7336,49 +7336,49 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>silutes-betonas-silute</t>
+          <t>telsiu-keliai-telsiai</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>177392928</t>
+          <t>180200843</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilutės betonas</t>
+          <t>UAB Telšių keliai</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betonas</t>
+          <t>Telšių keliai</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Šilutė</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Šilutės r. sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Ramučių g. 1, Šilutė</t>
+          <t>Mažeikių g. 18, Telšiai</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>55.3538641</v>
+        <v>56.0004158</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>21.4796635</v>
+        <v>22.2581129</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -7407,102 +7407,108 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betono gamyba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="2" t="inlineStr"/>
-      <c r="S61" s="4" t="inlineStr"/>
+      <c r="S61" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
         </is>
       </c>
       <c r="U61" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr"/>
+        <v>0.86</v>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/</t>
+        </is>
+      </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>kruszbet-lithuania-jure</t>
+          <t>vpa-laistai</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>305173596</t>
+          <t>110185819</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>UAB KRUSZBET Lithuania</t>
+          <t>UAB V. Paulius &amp; Associates</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania</t>
+          <t>VPA</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Jūrė</t>
+          <t>Laistai</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Kazlų Rūdos sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
+          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>54.7706307</v>
+        <v>55.636908</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>23.4998409</v>
+        <v>21.209254</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7517,98 +7523,116 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania betono gamyba</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr"/>
-      <c r="S62" s="4" t="inlineStr"/>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
+      <c r="S62" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>VPA betono mazgas Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U62" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V62" s="2" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vpa.lt/</t>
+        </is>
+      </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X62" s="2" t="inlineStr"/>
+          <t>https://www.vpa.lt/?Kontaktai=</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+        </is>
+      </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>telsiu-keliai-telsiai</t>
+          <t>c3-beton-baisogala</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>180200843</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>UAB Telšių keliai</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Telšių keliai</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Baisogala</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių g. 18, Telšiai</t>
+          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>56.0004158</v>
+        <v>55.6372</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>22.2581129</v>
+        <v>23.7183</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7623,108 +7647,118 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="inlineStr"/>
-      <c r="S63" s="4" t="n">
-        <v>2</v>
+          <t>Baisiogala Plant</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="S63" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
+          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
         </is>
       </c>
       <c r="U63" s="5" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/</t>
+          <t>https://c3beton.com/</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>vpa-laistai</t>
+          <t>c3-beton-martiniskis</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>110185819</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>UAB V. Paulius &amp; Associates</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>VPA</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Laistai</t>
+          <t>Martiniškis</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
+          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>55.636908</v>
+        <v>55.1441659</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>21.209254</v>
+        <v>24.1869636</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Google Maps nuoroda</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7739,60 +7773,62 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Liebherr</t>
+          <t>Martiniškis Plant</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>3 m³</t>
+          <t>Ammann Elba Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S64" s="4" t="n">
-        <v>2</v>
+          <t>60–80 m³/val.</t>
+        </is>
+      </c>
+      <c r="S64" s="4" t="inlineStr">
+        <is>
+          <t>2x85 t</t>
+        </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>VPA betono mazgas Klaipėdos rajone.</t>
+          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U64" s="5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/</t>
+          <t>https://c3beton.com/</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/?Kontaktai=</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-baisogala</t>
+          <t>c3-beton-stasenai</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -7817,38 +7853,38 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Baisogala</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
+          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>55.6372</v>
+        <v>54.6493094</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>23.7183</v>
+        <v>25.3107972</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus adreso taškas pagal geokodavimą</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7863,27 +7899,27 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Baisiogala Plant</t>
+          <t>Vilnius Ušos g. Plant</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>Nissbau Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>60–80 m³/val.</t>
         </is>
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>2x85 t</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
+          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U65" s="5" t="n">
@@ -7906,7 +7942,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
+          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -7918,7 +7954,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-martiniskis</t>
+          <t>c3-beton-runeikiai</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -7943,24 +7979,24 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis</t>
+          <t>Runeikiai</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
+          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>55.1441659</v>
+        <v>55.3327393</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>24.1869636</v>
+        <v>24.3501308</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -7989,7 +8025,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis Plant</t>
+          <t>Runeikiai Plant</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8044,22 +8080,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-stasenai</t>
+          <t>reljef-rukla</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>301731961</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>UAB Reljef</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>Reljef</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8069,38 +8105,38 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Rukla</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
+          <t>Rukla, Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
-        <v>54.6493094</v>
+        <v>55.05225</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>25.3107972</v>
+        <v>24.4064167</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas pagal geokodavimą</t>
+          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
+          <t>Naudotojo pateiktos koordinatės</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8115,438 +8151,186 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Vilnius Ušos g. Plant</t>
+          <t>Ammann Elba</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Nissbau Euromix C120, 3 m³</t>
+          <t>Nenustatyta</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>60–80 m³/val.</t>
+          <t>Nenustatytas</t>
         </is>
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2x85 t</t>
+          <t>2x65 t</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
         </is>
       </c>
       <c r="U67" s="5" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
+          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-runeikiai</t>
+          <t>ponas-betonas-paraudondvariai</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
+          <t>306676006</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>UAB Ponas betonas</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Ponas betonas</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Konkurentas</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Paraudondvariai</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus r. sav.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>54.8321418</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>25.2755596</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Elkon</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
           <t>Nenurodyta viešai</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>C3 Betonas</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>C3 Betonas</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Runeikiai</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Kėdainių r. sav.</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>55.3327393</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>24.3501308</v>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>C3 Betonas oficialus puslapis</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>https://c3beton.com/lt/betonas</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>Runeikiai Plant</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
-        </is>
-      </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>60–80 m³/val.</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="S68" s="4" t="inlineStr">
         <is>
-          <t>2x85 t</t>
+          <t>2 matomi oficialioje nuotraukoje</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
         </is>
       </c>
       <c r="U68" s="5" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.ponasbetonas.lt/#Apiemus</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>reljef-rukla</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>301731961</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>UAB Reljef</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Reljef</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Rukla</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Jonavos r. sav.</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Rukla, Jonavos r. sav.</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>55.05225</v>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>24.4064167</v>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>Naudotojo pateiktos koordinatės</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>Ammann Elba</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>Nenustatyta</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>Nenustatytas</t>
-        </is>
-      </c>
-      <c r="S69" s="4" t="inlineStr">
-        <is>
-          <t>2x65 t</t>
-        </is>
-      </c>
-      <c r="T69" s="2" t="inlineStr">
-        <is>
-          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
-        </is>
-      </c>
-      <c r="U69" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reljef.lt/</t>
-        </is>
-      </c>
-      <c r="W69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.reljef.lt/</t>
-        </is>
-      </c>
-      <c r="X69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
-        </is>
-      </c>
-      <c r="Y69" s="2" t="inlineStr">
-        <is>
-          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
-        </is>
-      </c>
-      <c r="Z69" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>ponas-betonas-paraudondvariai</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>306676006</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>UAB Ponas betonas</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Ponas betonas</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Paraudondvariai</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Vilniaus r. sav.</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>54.8321418</v>
-      </c>
-      <c r="J70" s="3" t="n">
-        <v>25.2755596</v>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
-      <c r="S70" s="4" t="inlineStr">
-        <is>
-          <t>2 matomi oficialioje nuotraukoje</t>
-        </is>
-      </c>
-      <c r="T70" s="2" t="inlineStr">
-        <is>
-          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
-        </is>
-      </c>
-      <c r="U70" s="5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="V70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ponasbetonas.lt/</t>
-        </is>
-      </c>
-      <c r="W70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ponasbetonas.lt/#Apiemus</t>
-        </is>
-      </c>
-      <c r="X70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ponasbetonas.lt/</t>
-        </is>
-      </c>
-      <c r="Y70" s="2" t="inlineStr">
-        <is>
-          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
-        </is>
-      </c>
-      <c r="Z70" s="2" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z70"/>
+  <autoFilter ref="A1:Z68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8635,7 +8419,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T07:39:37.605548+00:00</t>
+          <t>2026-09-23T08:39:21.239190+00:00</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T07:39:37.605548+00:00</t>
+          <t>2026-09-23T08:39:21.239190+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8704,7 +8488,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -495,7 +495,7 @@
   <dimension ref="A1:Z68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
@@ -1012,7 +1012,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-rudningai</t>
+          <t>betono-centras-vilnius-sirvintu-kryptis</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1032,43 +1032,43 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mūsų įmonė</t>
+          <t>Mūsų įmonė – planavimo taškas</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Rūdningai</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Šalčininkų r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Rūdningai</t>
+          <t>Vakarinis aplinkkelis, Vilnius (15 km keliais nuo Riovonių)</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>54.43883333333333</v>
+        <v>54.759939539351</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>25.081</v>
+        <v>25.203320952262</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktas koordinačių taškas</t>
+          <t>Apskaičiuotas 15 km važiavimo taškas</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos koordinatės</t>
+          <t>Valhalla / OpenStreetMap maršrutas</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
+          <t>https://valhalla.github.io/valhalla/api/turn-by-turn/overview/</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1083,31 +1083,19 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>SBM3000 (Schwenk)</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>3,0 m³</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>80 m³/h</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>3x85 t</t>
-        </is>
-      </c>
+          <t>Orientacinė gamyklos vieta – Širvintų kryptis</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>Betono centro betono mazgas Rūdninguose.</t>
+          <t>Orientacinis gamyklos planavimo taškas ties Riovonių gamyklos 15 km važiavimo keliais riba, Širvintų kryptimi.</t>
         </is>
       </c>
       <c r="U5" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1116,29 +1104,25 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>https://betonocentras.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
-        </is>
-      </c>
+          <t>https://valhalla.github.io/valhalla/api/turn-by-turn/overview/</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos DMS formatu: 54°26'19.8"N 25°04'51.6"E.</t>
+          <t>Taškas apskaičiuotas Valhalla maršrutu nuo Naujosios Riovonių g. 11 iki Širvintų centro. Tai orientacinis 15,00 km važiavimo ribos taškas Vakarinio aplinkkelio trasoje, o ne patvirtintas statybos sklypas.</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-rudninkai</t>
+          <t>betono-centras-rudningai</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1163,7 +1147,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Rūdninkai</t>
+          <t>Rūdningai</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1173,14 +1157,14 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Rūdninkai</t>
+          <t>Rūdningai</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>54.43924548406194</v>
+        <v>54.43883333333333</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>25.08098427100702</v>
+        <v>25.081</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1194,7 +1178,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
+          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1209,12 +1193,12 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>SBM3300</t>
+          <t>SBM3000 (Schwenk)</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>3,3 m³</t>
+          <t>3,0 m³</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -1229,7 +1213,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>Betono centro betono mazgas Rūdninkuose.</t>
+          <t>Betono centro betono mazgas Rūdninguose.</t>
         </is>
       </c>
       <c r="U6" s="5" t="n">
@@ -1247,12 +1231,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
+          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos dešimtainiu formatu.</t>
+          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos DMS formatu: 54°26'19.8"N 25°04'51.6"E.</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1264,7 +1248,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-kaunas</t>
+          <t>betono-centras-rudninkai</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1289,38 +1273,38 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Rūdninkai</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Šalčininkų r. sav.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Raudondvario pl. 157, Kaunas</t>
+          <t>Rūdninkai</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>54.9128359</v>
+        <v>54.43924548406194</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>23.8412662</v>
+        <v>25.08098427100702</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Naudotojo pateiktas koordinačių taškas</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Naudotojo pateiktos koordinatės</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1335,23 +1319,27 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Wiggert</t>
+          <t>SBM3300</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2,0 m³ ir 3,0 m³</t>
+          <t>3,3 m³</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S7" s="4" t="inlineStr"/>
+          <t>80 m³/h</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>3x85 t</t>
+        </is>
+      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Kaune.</t>
+          <t>Betono centro betono mazgas Rūdninkuose.</t>
         </is>
       </c>
       <c r="U7" s="5" t="n">
@@ -1369,24 +1357,24 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>https://betonocentras.lt/kontaktai/</t>
+          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>Kauno betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos dešimtainiu formatu.</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-klaipeda</t>
+          <t>betono-centras-kaunas</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1411,24 +1399,24 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Liepų g. 87N, Klaipėda</t>
+          <t>Raudondvario pl. 157, Kaunas</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>55.7290357</v>
+        <v>54.9128359</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>21.1544709</v>
+        <v>23.8412662</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1457,23 +1445,23 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>LIEBHERR MOBILMIX</t>
+          <t>Wiggert</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2,25 m³</t>
+          <t>2,0 m³ ir 3,0 m³</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>60 m³/h</t>
+          <t>60-80 m³/h</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Klaipėdoje.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Kaune.</t>
         </is>
       </c>
       <c r="U8" s="5" t="n">
@@ -1496,7 +1484,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame Betono centro kontaktų puslapyje patvirtintas Klaipėdos padalinys. Mazgo techniniai duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
+          <t>Kauno betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1508,7 +1496,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-siauliai</t>
+          <t>betono-centras-klaipeda</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1533,24 +1521,24 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Šiauliai</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių m. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Daubos g. 7A, Šiauliai</t>
+          <t>Liepų g. 87N, Klaipėda</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>55.9056327</v>
+        <v>55.7290357</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>23.3141873</v>
+        <v>21.1544709</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1595,7 +1583,7 @@
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Šiauliuose.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Klaipėdoje.</t>
         </is>
       </c>
       <c r="U9" s="5" t="n">
@@ -1618,7 +1606,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialiame Betono centro kontaktų puslapyje patvirtintas Klaipėdos padalinys. Mazgo techniniai duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1630,7 +1618,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-mazeikiai</t>
+          <t>betono-centras-siauliai</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1655,24 +1643,24 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Mažeikiai</t>
+          <t>Šiauliai</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių r. sav.</t>
+          <t>Šiaulių m. sav.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Troškučių g. 1, Mažeikiai</t>
+          <t>Daubos g. 7A, Šiauliai</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>56.3189055</v>
+        <v>55.9056327</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>22.2967774</v>
+        <v>23.3141873</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1701,15 +1689,23 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių betono mazgas</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
+          <t>LIEBHERR MOBILMIX</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2,25 m³</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/h</t>
+        </is>
+      </c>
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Mažeikiuose.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Šiauliuose.</t>
         </is>
       </c>
       <c r="U10" s="5" t="n">
@@ -1730,17 +1726,21 @@
           <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>Šiaulių betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+        </is>
+      </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-panevezys</t>
+          <t>betono-centras-mazeikiai</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1765,24 +1765,24 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Mažeikiai</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Mažeikių r. sav.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52A, Panevėžys</t>
+          <t>Troškučių g. 1, Mažeikiai</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>55.7423854</v>
+        <v>56.3189055</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>24.3777723</v>
+        <v>22.2967774</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1811,23 +1811,15 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>LIEBHERR Betomix</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2,25 m³</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/h</t>
-        </is>
-      </c>
+          <t>Mažeikių betono mazgas</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Panevėžyje.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Mažeikiuose.</t>
         </is>
       </c>
       <c r="U11" s="5" t="n">
@@ -1848,77 +1840,73 @@
           <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>Panevėžio betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
-        </is>
-      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-vilnius-siaures</t>
+          <t>betono-centras-panevezys</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>304102190</t>
+          <t>123018186</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>UAB Heidelberg Materials Lietuva Betonas</t>
+          <t>UAB Betono centras</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials</t>
+          <t>Betono centras</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Konkurentas</t>
+          <t>Mūsų įmonė</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Glaudėnai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
+          <t>S. Kerbedžio g. 52A, Panevėžys</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>55.774886</v>
+        <v>55.7423854</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>21.160809</v>
+        <v>24.3777723</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas; adresas patikslintas reverse-geokodavimu</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1933,50 +1921,58 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials betono gamykla, Glaudėnai</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
+          <t>LIEBHERR Betomix</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2,25 m³</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/h</t>
+        </is>
+      </c>
       <c r="S12" s="4" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials betono gamyklų tinklo taškas perkeltas iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Panevėžyje.</t>
         </is>
       </c>
       <c r="U12" s="5" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt</t>
+          <t>https://betonocentras.lt/</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
+          <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
+          <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>Perkelta iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją. Google Maps nuoroda išsisprendė į koordinates 55.774886, 21.160809; vietovė patikslinta reverse-geokodavimu kaip Glaudėnų k., Sendvario sen., Klaipėdos r. sav. Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis paliktas kaip įmonės šaltinis.</t>
+          <t>Panevėžio betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-vilnius-sandeliu</t>
+          <t>heidelberg-vilnius-siaures</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2001,38 +1997,38 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Glaudėnai</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Sandėlių g. 16, Vilnius</t>
+          <t>Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>54.6535114</v>
+        <v>55.774886</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>25.1242965</v>
+        <v>21.160809</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas; adresas patikslintas reverse-geokodavimu</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2047,7 +2043,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus betono gamykla, Sandėlių g.</t>
+          <t>Heidelberg Materials betono gamykla, Glaudėnai</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -2055,7 +2051,7 @@
       <c r="S13" s="4" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Vilniuje.</t>
+          <t>Heidelberg Materials betono gamyklų tinklo taškas perkeltas iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="U13" s="5" t="n">
@@ -2073,24 +2069,24 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
+          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+          <t>Perkelta iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją. Google Maps nuoroda išsisprendė į koordinates 55.774886, 21.160809; vietovė patikslinta reverse-geokodavimu kaip Glaudėnų k., Sendvario sen., Klaipėdos r. sav. Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis paliktas kaip įmonės šaltinis.</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-avizieniai-klevu</t>
+          <t>heidelberg-vilnius-sandeliu</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2115,24 +2111,24 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Avižieniai</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Klevų g. 2, Avižieniai, Vilniaus r.</t>
+          <t>Sandėlių g. 16, Vilnius</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>54.760788043384</v>
+        <v>54.6535114</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>25.179476693822</v>
+        <v>25.1242965</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -2141,12 +2137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS World Geocoding Service</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2161,31 +2157,19 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/val.</t>
-        </is>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>3x85 t</t>
-        </is>
-      </c>
+          <t>Vilniaus betono gamykla, Sandėlių g.</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials betono mazgas Klevų g. 2, Avižieniuose.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Vilniuje.</t>
         </is>
       </c>
       <c r="U14" s="5" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
@@ -2204,19 +2188,19 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina Klevų g. 2, Avižieniai, betono užsakymų tašką. Mazgo gamintojas, maišyklės tūris, realus našumas ir silosų duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-kaunas</t>
+          <t>heidelberg-avizieniai-klevu</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2241,24 +2225,24 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Avižieniai</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Technikos g. 7K, Kaunas</t>
+          <t>Klevų g. 2, Avižieniai, Vilniaus r.</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>54.9093181</v>
+        <v>54.760788043384</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>24.0122104</v>
+        <v>25.179476693822</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -2267,12 +2251,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>ArcGIS World Geocoding Service</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2287,19 +2271,31 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Kauno betono gamykla</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
+          <t>Ammann Elba</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/val.</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>3x85 t</t>
+        </is>
+      </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Kaune.</t>
+          <t>Heidelberg Materials betono mazgas Klevų g. 2, Avižieniuose.</t>
         </is>
       </c>
       <c r="U15" s="5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -2318,19 +2314,19 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina Klevų g. 2, Avižieniai, betono užsakymų tašką. Mazgo gamintojas, maišyklės tūris, realus našumas ir silosų duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-klaipeda</t>
+          <t>heidelberg-kaunas</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2355,24 +2351,24 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Švepelių g. 5, Klaipėda</t>
+          <t>Technikos g. 7K, Kaunas</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>55.6744503</v>
+        <v>54.9093181</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>21.2165993</v>
+        <v>24.0122104</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2401,25 +2397,15 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Wiggert</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S16" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>Kauno betono gamykla</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Klaipėdoje.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Kaune.</t>
         </is>
       </c>
       <c r="U16" s="5" t="n">
@@ -2442,19 +2428,19 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje. Klaipėdos mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-alytus</t>
+          <t>heidelberg-klaipeda</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2479,24 +2465,24 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Alytus</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Alytaus m. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Kalniškės g. 2, Alytus</t>
+          <t>Švepelių g. 5, Klaipėda</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>54.4113266</v>
+        <v>55.6744503</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>24.0081029</v>
+        <v>21.2165993</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2525,15 +2511,25 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Alytaus betono gamykla</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
+          <t>Wiggert</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Alytuje.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Klaipėdoje.</t>
         </is>
       </c>
       <c r="U17" s="5" t="n">
@@ -2556,19 +2552,19 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje. Klaipėdos mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-pasvalys</t>
+          <t>heidelberg-alytus</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2593,28 +2589,28 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Pasvalys</t>
+          <t>Alytus</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Pasvalio r. sav.</t>
+          <t>Alytaus m. sav.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Beržų g. 8C, Pasvalys</t>
+          <t>Kalniškės g. 2, Alytus</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>56.0647646</v>
+        <v>54.4113266</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>24.3860079</v>
+        <v>24.0081029</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Gatvės lygio taškas; reikia tikslesnio adreso taško</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2639,7 +2635,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Pasvalio betono gamykla</t>
+          <t>Alytaus betono gamykla</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -2647,11 +2643,11 @@
       <c r="S18" s="4" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Pasvalyje.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Alytuje.</t>
         </is>
       </c>
       <c r="U18" s="5" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2682,22 +2678,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>palmusta-vilnius</t>
+          <t>heidelberg-pasvalys</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>122619426</t>
+          <t>304102190</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>UAB Palmusta</t>
+          <t>UAB Heidelberg Materials Lietuva Betonas</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Palmusta</t>
+          <t>Heidelberg Materials</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2707,28 +2703,28 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Pasvalys</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Pasvalio r. sav.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Sudervės kel. 1A, Avižieniai, Vilniaus r.</t>
+          <t>Beržų g. 8C, Pasvalys</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>54.7136351</v>
+        <v>56.0647646</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>25.2359209</v>
+        <v>24.3860079</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Gatvės lygio taškas; reikia tikslesnio adreso taško</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2753,7 +2749,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Palmusta betono mazgas</t>
+          <t>Pasvalio betono gamykla</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -2761,7 +2757,7 @@
       <c r="S19" s="4" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas Vilniaus regione.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Pasvalyje.</t>
         </is>
       </c>
       <c r="U19" s="5" t="n">
@@ -2769,20 +2765,24 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>https://www.palmusta.lt/</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>https://www.palmusta.lt/</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>https://www.palmusta.lt/</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr"/>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+        </is>
+      </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -2792,18 +2792,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>gkg3-vilnius</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr"/>
+          <t>palmusta-vilnius</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>122619426</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UAB Vilniaus gelžbetoninių konstrukcijų gamykla Nr. 3</t>
+          <t>UAB Palmusta</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GKG-3</t>
+          <t>Palmusta</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2818,48 +2822,48 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Šaltupio g. 11, Vilnius</t>
+          <t>Sudervės kel. 1A, Avižieniai, Vilniaus r.</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>54.6471731</v>
+        <v>54.7136351</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>25.1918488</v>
+        <v>25.2359209</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Oficialios Google Maps nuorodos taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>GKG3 kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>https://gkg3.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>GKG-3 gelžbetonio gamykla</t>
+          <t>Palmusta betono mazgas</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -2867,32 +2871,28 @@
       <c r="S20" s="4" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninių konstrukcijų gamyba Vilniuje.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Vilniaus regione.</t>
         </is>
       </c>
       <c r="U20" s="5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>https://www.gkg3.lt/</t>
+          <t>https://www.palmusta.lt/</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>https://gkg3.lt/kontaktai/</t>
+          <t>https://www.palmusta.lt/</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>https://gkg3.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t>Koordinatės patikslintos pagal oficialaus GKG3 kontaktų puslapio Google Maps nuorodą.</t>
-        </is>
-      </c>
+          <t>https://www.palmusta.lt/</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -2902,18 +2902,18 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>perdanga-vilnius</t>
+          <t>gkg3-vilnius</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>UAB Perdanga</t>
+          <t>UAB Vilniaus gelžbetoninių konstrukcijų gamykla Nr. 3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Perdanga</t>
+          <t>GKG-3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2933,28 +2933,28 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Lentvario g. 16, Vilnius</t>
+          <t>Šaltupio g. 11, Vilnius</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>54.642372</v>
+        <v>54.6471731</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>25.1441455</v>
+        <v>25.1918488</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialios Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>GKG3 kontaktų puslapis</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://gkg3.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2969,19 +2969,15 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Perdanga Vilniaus gamykla</t>
+          <t>GKG-3 gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>150 m³/val.</t>
-        </is>
-      </c>
+      <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="4" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>Viešai nurodoma nauja gelžbetonio elementų gamybos linija, kurios našumas 150 m³/val.</t>
+          <t>Gelžbetoninių konstrukcijų gamyba Vilniuje.</t>
         </is>
       </c>
       <c r="U21" s="5" t="n">
@@ -2989,20 +2985,24 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
+          <t>https://www.gkg3.lt/</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
+          <t>https://gkg3.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr"/>
+          <t>https://gkg3.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>Koordinatės patikslintos pagal oficialaus GKG3 kontaktų puslapio Google Maps nuorodą.</t>
+        </is>
+      </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -3012,7 +3012,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>perdanga-klaipeda</t>
+          <t>perdanga-vilnius</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
@@ -3033,24 +3033,24 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Dubysos g. 27, Klaipėda</t>
+          <t>Lentvario g. 16, Vilnius</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>55.6923067</v>
+        <v>54.642372</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>21.1631559</v>
+        <v>25.1441455</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -3079,27 +3079,23 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Stetter</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2x1,5 m³</t>
-        </is>
-      </c>
+          <t>Perdanga Vilniaus gamykla</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>40-50 m³/h</t>
+          <t>150 m³/val.</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Perdangos padalinys Klaipėdoje.</t>
+          <t>Viešai nurodoma nauja gelžbetonio elementų gamybos linija, kurios našumas 150 m³/val.</t>
         </is>
       </c>
       <c r="U22" s="5" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -3113,35 +3109,31 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/lt/produkcija/betono-misiniai/gamyba-transportavimas</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t>Oficialus Perdangos puslapis nurodo, kad Klaipėdoje betono mišiniai gaminami STETTER technologinėmis linijomis. Maišyklės ir našumo duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
-        </is>
-      </c>
+          <t>https://www.perdanga.lt/</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>kauno-gelzbetonis-kaunas</t>
+          <t>perdanga-klaipeda</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>UAB Kauno gelžbetonis</t>
+          <t>UAB Perdanga</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Kauno gelžbetonis</t>
+          <t>Perdanga</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3151,24 +3143,24 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Pramonės pr. 8, Kaunas</t>
+          <t>Dubysos g. 27, Klaipėda</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>54.9122829</v>
+        <v>55.6923067</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>23.9864942</v>
+        <v>21.1631559</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -3197,61 +3189,69 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Kauno gelžbetonio gamykla</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
+          <t>Stetter</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2x1,5 m³</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>40-50 m³/h</t>
+        </is>
+      </c>
       <c r="S23" s="4" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas gelžbetonio gamintojas Kaune.</t>
+          <t>Viešai skelbiamas Perdangos padalinys Klaipėdoje.</t>
         </is>
       </c>
       <c r="U23" s="5" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaunogelzbetonis.lt/</t>
+          <t>https://www.perdanga.lt/</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
+          <t>https://www.perdanga.lt/</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
+          <t>https://www.perdanga.lt/lt/produkcija/betono-misiniai/gamyba-transportavimas</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Kauno gelžbetonio kontaktų puslapis patvirtina Pramonės pr. 8 adresą.</t>
+          <t>Oficialus Perdangos puslapis nurodo, kad Klaipėdoje betono mišiniai gaminami STETTER technologinėmis linijomis. Maišyklės ir našumo duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ukmerges-gelzbetonis-ukmerge</t>
+          <t>kauno-gelzbetonis-kaunas</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>UAB Ukmergės gelžbetonis</t>
+          <t>UAB Kauno gelžbetonis</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Ukmergės gelžbetonis</t>
+          <t>Kauno gelžbetonis</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Ukmergė</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Ukmergės r. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Antakalnio g. 60, Ukmergė</t>
+          <t>Pramonės pr. 8, Kaunas</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>55.2419448</v>
+        <v>54.9122829</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>24.7875927</v>
+        <v>23.9864942</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Ukmergės gelžbetonio gamykla</t>
+          <t>Kauno gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -3315,7 +3315,7 @@
       <c r="S24" s="4" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas gelžbetonio gamintojas Ukmergėje.</t>
+          <t>Viešai skelbiamas gelžbetonio gamintojas Kaune.</t>
         </is>
       </c>
       <c r="U24" s="5" t="n">
@@ -3323,22 +3323,22 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>https://ukmergesgelzbetonis.lt/</t>
+          <t>https://www.kaunogelzbetonis.lt/</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>https://ukmergesgelzbetonis.lt/</t>
+          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>https://ukmergesgelzbetonis.lt/</t>
+          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Ukmergės gelžbetonio svetainė palikta kaip pagrindinis šaltinis; naujų patikimų koordinačių nerasta.</t>
+          <t>Oficialus Kauno gelžbetonio kontaktų puslapis patvirtina Pramonės pr. 8 adresą.</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3350,18 +3350,18 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>gelzbetonines-konstrukcijos-siauliai</t>
+          <t>ukmerges-gelzbetonis-ukmerge</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelžbetoninės konstrukcijos</t>
+          <t>UAB Ukmergės gelžbetonis</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninės konstrukcijos</t>
+          <t>Ukmergės gelžbetonis</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Šiauliai</t>
+          <t>Ukmergė</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių m. sav.</t>
+          <t>Ukmergės r. sav.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Sodo g. 20A, Šiauliai</t>
+          <t>Antakalnio g. 60, Ukmergė</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>55.9495824</v>
+        <v>55.2419448</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>23.3105291</v>
+        <v>24.7875927</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Oficialios žemėlapio nuorodos taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninės konstrukcijos kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninių konstrukcijų gamykla</t>
+          <t>Ukmergės gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -3425,7 +3425,7 @@
       <c r="S25" s="4" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas gelžbetonio gamintojas Šiauliuose.</t>
+          <t>Viešai skelbiamas gelžbetonio gamintojas Ukmergėje.</t>
         </is>
       </c>
       <c r="U25" s="5" t="n">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/</t>
+          <t>https://ukmergesgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+          <t>https://ukmergesgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+          <t>https://ukmergesgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>Koordinatės patikslintos pagal oficialaus kontaktų puslapio žemėlapio tašką.</t>
+          <t>Oficiali Ukmergės gelžbetonio svetainė palikta kaip pagrindinis šaltinis; naujų patikimų koordinačių nerasta.</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3460,18 +3460,18 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>inhus-senieji-trakai</t>
+          <t>gelzbetonines-konstrukcijos-siauliai</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>UAB INHUS Lietuva</t>
+          <t>UAB Gelžbetoninės konstrukcijos</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>INHUS</t>
+          <t>Gelžbetoninės konstrukcijos</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3481,38 +3481,38 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Senieji Trakai</t>
+          <t>Šiauliai</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Trakų r. sav.</t>
+          <t>Šiaulių m. sav.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Plačioji g. 27, Senieji Trakai</t>
+          <t>Sodo g. 20A, Šiauliai</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>54.6140174</v>
+        <v>55.9495824</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>24.980818</v>
+        <v>23.3105291</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialios žemėlapio nuorodos taškas</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Gelžbetoninės konstrukcijos kontaktų puslapis</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Surenkamas gelžbetonis</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>INHUS gelžbetonio gamykla</t>
+          <t>Gelžbetoninių konstrukcijų gamykla</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -3535,7 +3535,7 @@
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas surenkamojo gelžbetonio konstrukcijų gamintojas.</t>
+          <t>Viešai skelbiamas gelžbetonio gamintojas Šiauliuose.</t>
         </is>
       </c>
       <c r="U26" s="5" t="n">
@@ -3543,20 +3543,24 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr"/>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>Koordinatės patikslintos pagal oficialaus kontaktų puslapio žemėlapio tašką.</t>
+        </is>
+      </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -3566,18 +3570,18 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>gelmesta-vievis</t>
+          <t>inhus-senieji-trakai</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelmesta</t>
+          <t>UAB INHUS Lietuva</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Gelmesta</t>
+          <t>INHUS</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3587,24 +3591,24 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Vievis</t>
+          <t>Senieji Trakai</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Elektrėnų sav.</t>
+          <t>Trakų r. sav.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Statybininkų g. 1B, Vievis</t>
+          <t>Plačioji g. 27, Senieji Trakai</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>54.7782794</v>
+        <v>54.6140174</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>24.8280365</v>
+        <v>24.980818</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3623,17 +3627,17 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Surenkamas gelžbetonis</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Gelmesta betono mazgas</t>
+          <t>INHUS gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -3641,25 +3645,25 @@
       <c r="S27" s="4" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas.</t>
+          <t>Viešai skelbiamas surenkamojo gelžbetonio konstrukcijų gamintojas.</t>
         </is>
       </c>
       <c r="U27" s="5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>https://gelmesta.lt/</t>
+          <t>https://inhus.eu/</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>https://gelmesta.lt/</t>
+          <t>https://inhus.eu/</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>https://gelmesta.lt/</t>
+          <t>https://inhus.eu/</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr"/>
@@ -3672,22 +3676,18 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>suduvos-betonas-marijampole</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>302330957</t>
-        </is>
-      </c>
+          <t>gelmesta-vievis</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>UAB Surenkamos statybos konstrukcijos</t>
+          <t>UAB Gelmesta</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Sūduvos betonas</t>
+          <t>Gelmesta</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3697,24 +3697,24 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Vievis</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Elektrėnų sav.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Sporto g. 9H, LT-68108 Marijampolė</t>
+          <t>Statybininkų g. 1B, Vievis</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>54.5702553</v>
+        <v>54.7782794</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>23.3803405</v>
+        <v>24.8280365</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3743,77 +3743,61 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Sūduvos betono mazgas</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>iki 200 m³ per darbo pamainą</t>
-        </is>
-      </c>
-      <c r="S28" s="4" t="inlineStr">
-        <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
+          <t>Gelmesta betono mazgas</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="4" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje nurodoma betono mišinių gamyba ir pristatymas; Marijampolėje esantis 130 arų betono mazgas gali pagaminti iki 200 m³ betono per darbo pamainą.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas.</t>
         </is>
       </c>
       <c r="U28" s="5" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>https://www.suduvos-betonas.lt/</t>
+          <t>https://gelmesta.lt/</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>https://www.suduvos-betonas.lt/kontaktai/</t>
+          <t>https://gelmesta.lt/</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>https://www.suduvos-betonas.lt/betono-misiniai/</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t>Atnaujinta pagal oficialų suduvos-betonas.lt kontaktų, pradinį ir betono mišinių puslapius: juridinis pavadinimas, įmonės kodas, adresas, betono mišinių veikla ir viešas mazgo aprašymas.</t>
-        </is>
-      </c>
+          <t>https://gelmesta.lt/</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>statkasta-kaunas</t>
+          <t>suduvos-betonas-marijampole</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>185607978</t>
+          <t>302330957</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>UAB Statkasta</t>
+          <t>UAB Surenkamos statybos konstrukcijos</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Statkasta</t>
+          <t>Sūduvos betonas</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3823,38 +3807,38 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Serdokai</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Vilkaviškio r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Gėlių g. 34, Serdokų k., Vilkaviškio r., LT-70201</t>
+          <t>Sporto g. 9H, LT-68108 Marijampolė</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>54.6279368</v>
+        <v>54.5702553</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>23.0871345</v>
+        <v>23.3803405</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Vietovės lygio taškas; reikia tikslesnio adreso taško</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS geokodavimas pagal oficialų Statkasta adresą</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3869,69 +3853,77 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Statkasta betono mazgas</t>
+          <t>Sūduvos betono mazgas</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba CBT60SL, 1 m³</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>iki 60 m³/h</t>
-        </is>
-      </c>
-      <c r="S29" s="4" t="inlineStr"/>
+          <t>iki 200 m³ per darbo pamainą</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgo gamintojas Ammann Elba; modelis CBT60SL; maišyklė 1 m³; našumas iki 60 m³/h.</t>
+          <t>Oficialiame puslapyje nurodoma betono mišinių gamyba ir pristatymas; Marijampolėje esantis 130 arų betono mazgas gali pagaminti iki 200 m³ betono per darbo pamainą.</t>
         </is>
       </c>
       <c r="U29" s="5" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/</t>
+          <t>https://www.suduvos-betonas.lt/</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/kontaktai/</t>
+          <t>https://www.suduvos-betonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/kontaktai/</t>
+          <t>https://www.suduvos-betonas.lt/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame Statkasta kontaktų puslapyje nurodytas adresas Gėlių g. 34, Serdokų k.; koordinatės geokoduotos iki vietovės lygio. Rankiniu būdu papildyta techninė informacija: gamintojas Ammann Elba, modelis CBT60SL, maišyklė 1 m³, našumas iki 60 m³/h.</t>
+          <t>Atnaujinta pagal oficialų suduvos-betonas.lt kontaktų, pradinį ir betono mišinių puslapius: juridinis pavadinimas, įmonės kodas, adresas, betono mišinių veikla ir viešas mazgo aprašymas.</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>autokausta-kaunas</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr"/>
+          <t>statkasta-kaunas</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>185607978</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UAB Autokausta</t>
+          <t>UAB Statkasta</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Autokausta</t>
+          <t>Statkasta</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3941,38 +3933,38 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Serdokai</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Vilkaviškio r. sav.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Marvelės g. 199B, Kaunas</t>
+          <t>Gėlių g. 34, Serdokų k., Vilkaviškio r., LT-70201</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>54.9007881</v>
+        <v>54.6279368</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>23.8489377</v>
+        <v>23.0871345</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Vietovės lygio taškas; reikia tikslesnio adreso taško</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>ArcGIS geokodavimas pagal oficialų Statkasta adresą</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://statkasta.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3985,63 +3977,71 @@
           <t>Betono mišiniai</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Statkasta betono mazgas</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Ammann Elba CBT60SL, 1 m³</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>iki 60 m³/h</t>
+        </is>
+      </c>
       <c r="S30" s="4" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo pavadinimą reikia patikslinti.</t>
+          <t>Betono mazgo gamintojas Ammann Elba; modelis CBT60SL; maišyklė 1 m³; našumas iki 60 m³/h.</t>
         </is>
       </c>
       <c r="U30" s="5" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>https://autokausta.lt/</t>
+          <t>https://statkasta.lt/</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
+          <t>https://statkasta.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
+          <t>https://statkasta.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Autokausta betono puslapis patvirtina betono veiklą ir Marvelės g. 199B kontaktą.</t>
+          <t>Oficialiame Statkasta kontaktų puslapyje nurodytas adresas Gėlių g. 34, Serdokų k.; koordinatės geokoduotos iki vietovės lygio. Rankiniu būdu papildyta techninė informacija: gamintojas Ammann Elba, modelis CBT60SL, maišyklė 1 m³, našumas iki 60 m³/h.</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>betono-baze-visaginas</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>302725961</t>
-        </is>
-      </c>
+          <t>autokausta-kaunas</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono bazė</t>
+          <t>UAB Autokausta</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Betono bazė</t>
+          <t>Autokausta</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Visaginas</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Visagino sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Elektrinės g. 11, Drūkšinių k., Visagino sav.</t>
+          <t>Marvelės g. 199B, Kaunas</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>55.5963685</v>
+        <v>54.9007881</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>26.5817201</v>
+        <v>23.8489377</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -4095,40 +4095,36 @@
           <t>Betono mišiniai</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Betono bazė</t>
-        </is>
-      </c>
+      <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr"/>
       <c r="S31" s="4" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo adresą reikia patikslinti.</t>
+          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo pavadinimą reikia patikslinti.</t>
         </is>
       </c>
       <c r="U31" s="5" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonobaze.lt/</t>
+          <t>https://autokausta.lt/</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonobaze.lt/kontaktai</t>
+          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonobaze.lt/kontaktai</t>
+          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Elektrinės g. 11 adresą ir betono bazės veiklą.</t>
+          <t>Oficialus Autokausta betono puslapis patvirtina betono veiklą ir Marvelės g. 199B kontaktą.</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4140,18 +4136,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>transdosa-druskininkai</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr"/>
+          <t>betono-baze-visaginas</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>302725961</t>
+        </is>
+      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>UAB Transdosa</t>
+          <t>UAB Betono bazė</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Transdosa</t>
+          <t>Betono bazė</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4161,24 +4161,24 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Druskininkai</t>
+          <t>Visaginas</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Druskininkų sav.</t>
+          <t>Visagino sav.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Žvyro g. 2A, Margų k., Druskininkų sav.</t>
+          <t>Elektrinės g. 11, Drūkšinių k., Visagino sav.</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>54.146785</v>
+        <v>55.5963685</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>23.9291769</v>
+        <v>26.5817201</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -4207,98 +4207,88 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Elkomix-90 quick master</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1,5 m³</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>40 m³/h</t>
-        </is>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>Betono bazė</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="4" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas Druskininkų regione.</t>
+          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo adresą reikia patikslinti.</t>
         </is>
       </c>
       <c r="U32" s="5" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>https://transdosa.lt/</t>
+          <t>https://www.betonobaze.lt/</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>https://www.transdosa.lt/kontaktai/</t>
+          <t>https://www.betonobaze.lt/kontaktai</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>https://www.transdosa.lt/betonas/</t>
+          <t>https://www.betonobaze.lt/kontaktai</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>Oficialūs Transdosa kontaktų ir betono puslapiai patvirtina Margų karjero betono gamybą adresu Žvyro g. 2A. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Elektrinės g. 11 adresą ir betono bazės veiklą.</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>sodbeta-siauliai</t>
+          <t>transdosa-druskininkai</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>UAB Sodbeta</t>
+          <t>UAB Transdosa</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Sodbeta</t>
+          <t>Transdosa</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Šiauliai</t>
+          <t>Druskininkai</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių m. sav.</t>
+          <t>Druskininkų sav.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Sodo g. 20, Šiauliai</t>
+          <t>Žvyro g. 2A, Margų k., Druskininkų sav.</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>55.949032</v>
+        <v>54.146785</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>23.3125879</v>
+        <v>23.9291769</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -4317,75 +4307,81 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Sodbeta betono gaminių gamykla</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr"/>
+          <t>Elkomix-90 quick master</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>1,5 m³</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>40 m³/h</t>
+        </is>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama gelžbetonio ir betono gaminių gamyba Šiauliuose.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Druskininkų regione.</t>
         </is>
       </c>
       <c r="U33" s="5" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>https://sodbeta.lt/</t>
+          <t>https://transdosa.lt/</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>https://sodbeta.lt/</t>
+          <t>https://www.transdosa.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>https://sodbeta.lt/betonas/betono-misiniai/</t>
+          <t>https://www.transdosa.lt/betonas/</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Sodbeta svetainė patvirtina Sodo g. 20 adresą ir betono mišinių puslapį.</t>
+          <t>Oficialūs Transdosa kontaktų ir betono puslapiai patvirtina Margų karjero betono gamybą adresu Žvyro g. 2A. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>alytaus-gelzbetonis-alytus</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>149720232</t>
-        </is>
-      </c>
+          <t>sodbeta-siauliai</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>AB Alytaus gelžbetonis</t>
+          <t>UAB Sodbeta</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Alytaus gelžbetonis</t>
+          <t>Sodbeta</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4395,53 +4391,53 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Alytus</t>
+          <t>Šiauliai</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Alytaus m. sav.</t>
+          <t>Šiaulių m. sav.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Pramonės g. 15, Alytus</t>
+          <t>Sodo g. 20, Šiauliai</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>54.426129</v>
+        <v>55.949032</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>24.016482</v>
+        <v>23.3125879</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Oficialaus kontaktų puslapio žemėlapio taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Alytaus gelžbetonis kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Alytaus gelžbetonio gamykla</t>
+          <t>Sodbeta betono gaminių gamykla</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -4449,30 +4445,30 @@
       <c r="S34" s="4" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Viešai skelbiama gelžbetonio ir betono gaminių gamyba Šiauliuose.</t>
         </is>
       </c>
       <c r="U34" s="5" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/</t>
+          <t>https://sodbeta.lt/</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
+          <t>https://sodbeta.lt/</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
+          <t>https://sodbeta.lt/betonas/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>Patikslinta pagal oficialų kontaktų puslapį.</t>
+          <t>Oficiali Sodbeta svetainė patvirtina Sodo g. 20 adresą ir betono mišinių puslapį.</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4484,18 +4480,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>gernora-marijampole</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr"/>
+          <t>alytaus-gelzbetonis-alytus</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>149720232</t>
+        </is>
+      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>UAB Gernora</t>
+          <t>AB Alytaus gelžbetonis</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Gernora</t>
+          <t>Alytaus gelžbetonis</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4505,38 +4505,38 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Alytus</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Alytaus m. sav.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Vingio g. 2M, LT-68131 Marijampolė</t>
+          <t>Pramonės g. 15, Alytus</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>54.5356806</v>
+        <v>54.426129</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>23.3349754</v>
+        <v>24.016482</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Oficialios Google Maps nuorodos taškas</t>
+          <t>Oficialaus kontaktų puslapio žemėlapio taškas</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Gernora kontaktų puslapis</t>
+          <t>Alytaus gelžbetonis kontaktų puslapis</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/kontaktai/</t>
+          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Gernora betono mazgas</t>
+          <t>Alytaus gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -4559,30 +4559,30 @@
       <c r="S35" s="4" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas Marijampolėje.</t>
+          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U35" s="5" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/</t>
+          <t>https://alytausgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/kontaktai/</t>
+          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/kontaktai/</t>
+          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>Koordinatės patikslintos pagal oficialaus Gernora kontaktų puslapio Google Maps nuorodą.</t>
+          <t>Patikslinta pagal oficialų kontaktų puslapį.</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4594,18 +4594,18 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>re-betono-konstrukcijos-kretinga</t>
+          <t>gernora-marijampole</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>UAB RE Betono konstrukcijos</t>
+          <t>UAB Gernora</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>RE Betono konstrukcijos</t>
+          <t>Gernora</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4615,53 +4615,53 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Kretinga</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Kretingos r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Tiekėjų g. 27B, Kretinga</t>
+          <t>Vingio g. 2M, LT-68131 Marijampolė</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>55.87963</v>
+        <v>54.5356806</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>21.220888</v>
+        <v>23.3349754</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialios Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Gernora kontaktų puslapis</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://gernora.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>RE Betono konstrukcijų gamyba</t>
+          <t>Gernora betono mazgas</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -4669,26 +4669,30 @@
       <c r="S36" s="4" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, cemento gaminiai, betono siurblys ir pamatų blokai Kretingoje.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Marijampolėje.</t>
         </is>
       </c>
       <c r="U36" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>https://gernora.lt/</t>
+        </is>
+      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
+          <t>https://gernora.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
+          <t>https://gernora.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>Katalogo šaltinis, reikia patikslinti gamybos apimtį.</t>
+          <t>Koordinatės patikslintos pagal oficialaus Gernora kontaktų puslapio Google Maps nuorodą.</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4700,18 +4704,18 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>silales-statyba-vingininkai</t>
+          <t>re-betono-konstrukcijos-kretinga</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilalės statyba</t>
+          <t>UAB RE Betono konstrukcijos</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Šilalės statyba</t>
+          <t>RE Betono konstrukcijos</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4721,24 +4725,24 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Vingininkai</t>
+          <t>Kretinga</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Šilalės r. sav.</t>
+          <t>Kretingos r. sav.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Lauryno Ivinskio g. 7, Vingininkai, Šilalės r.</t>
+          <t>Tiekėjų g. 27B, Kretinga</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>55.4808479</v>
+        <v>55.87963</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>22.1937399</v>
+        <v>21.220888</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4767,7 +4771,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Šilalės statybos betono gaminių gamyba</t>
+          <t>RE Betono konstrukcijų gamyba</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -4775,30 +4779,26 @@
       <c r="S37" s="4" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių ir statybinių konstrukcijų veikla Šilalės rajone.</t>
+          <t>Viešame kataloge nurodomi betonas, cemento gaminiai, betono siurblys ir pamatų blokai Kretingoje.</t>
         </is>
       </c>
       <c r="U37" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.silalesstatyba.lt/</t>
-        </is>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>https://www.silalesstatyba.lt/</t>
+          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>https://www.silalesstatyba.lt/</t>
+          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti tikslų gaminių asortimentą.</t>
+          <t>Katalogo šaltinis, reikia patikslinti gamybos apimtį.</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4810,18 +4810,18 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>panevezio-gelzbetonis-panevezys</t>
+          <t>silales-statyba-vingininkai</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>UAB Panevėžio gelžbetonis</t>
+          <t>UAB Šilalės statyba</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio gelžbetonis</t>
+          <t>Šilalės statyba</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4831,24 +4831,24 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vingininkai</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Šilalės r. sav.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Lauryno Ivinskio g. 7, Vingininkai, Šilalės r.</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.4808479</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>24.3803541</v>
+        <v>22.1937399</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio gelžbetonio gamykla</t>
+          <t>Šilalės statybos betono gaminių gamyba</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -4885,26 +4885,30 @@
       <c r="S38" s="4" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>Viešame įmonių kataloge nurodomas gelžbetonio gaminių profilis Panevėžyje.</t>
+          <t>Viešai skelbiama betono gaminių ir statybinių konstrukcijų veikla Šilalės rajone.</t>
         </is>
       </c>
       <c r="U38" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr"/>
+        <v>0.72</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.silalesstatyba.lt/</t>
+        </is>
+      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
+          <t>https://www.silalesstatyba.lt/</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
+          <t>https://www.silalesstatyba.lt/</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikrinti veiklos aktyvumą ir produkcijos apimtį.</t>
+          <t>Reikia patikslinti tikslų gaminių asortimentą.</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4916,18 +4920,18 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>pamatas-telsiai</t>
+          <t>panevezio-gelzbetonis-panevezys</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>UAB Pamatas</t>
+          <t>UAB Panevėžio gelžbetonis</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Pamatas</t>
+          <t>Panevėžio gelžbetonis</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4937,24 +4941,24 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Tryškių g. 46, Dimaičių k., Telšių r.</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.9874536</v>
+        <v>55.7409491</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>22.287162</v>
+        <v>24.3803541</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4978,12 +4982,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Pamatas betono gaminių gamyba</t>
+          <t>Panevėžio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -4991,30 +4995,26 @@
       <c r="S39" s="4" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiami pamatų ir kiti betono gaminiai Telšių rajone.</t>
+          <t>Viešame įmonių kataloge nurodomas gelžbetonio gaminių profilis Panevėžyje.</t>
         </is>
       </c>
       <c r="U39" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t>https://pamatas.lt/</t>
-        </is>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>Adresas patikslintas pagal lietuvišką įmonės puslapį; koordinatės nustatytos Lietuvos geolokatoriumi.</t>
+          <t>Reikia patikrinti veiklos aktyvumą ir produkcijos apimtį.</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5026,18 +5026,18 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>vilniaus-betono-gaminiai-vilnius</t>
+          <t>pamatas-telsiai</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>UAB Vilniaus betono gaminiai</t>
+          <t>UAB Pamatas</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>HAUS / Vilniaus betono gaminiai</t>
+          <t>Pamatas</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5047,24 +5047,24 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>A. Jakšto g. 5, Vilnius</t>
+          <t>Tryškių g. 46, Dimaičių k., Telšių r.</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>54.6888177</v>
+        <v>55.9874536</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>25.2756813</v>
+        <v>22.287162</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus betono gaminiai</t>
+          <t>Pamatas betono gaminių gamyba</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -5101,30 +5101,30 @@
       <c r="S40" s="4" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas HAUS blokelių ir betono gaminių gamintojas.</t>
+          <t>Viešai skelbiami pamatų ir kiti betono gaminiai Telšių rajone.</t>
         </is>
       </c>
       <c r="U40" s="5" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>Žemėlapyje naudotas viešai skelbiamas įmonės adresas; gamybos vietą reikia patikslinti.</t>
+          <t>Adresas patikslintas pagal lietuvišką įmonės puslapį; koordinatės nustatytos Lietuvos geolokatoriumi.</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5136,18 +5136,18 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>pamario-grupe-kalnuvenai</t>
+          <t>vilniaus-betono-gaminiai-vilnius</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>UAB Pamario grupė</t>
+          <t>UAB Vilniaus betono gaminiai</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupė</t>
+          <t>HAUS / Vilniaus betono gaminiai</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5157,24 +5157,24 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Kalnuvėnai</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Kaukėnų g. 12, Kalnuvėnai, Klaipėdos r.</t>
+          <t>A. Jakšto g. 5, Vilnius</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>55.7905468</v>
+        <v>54.6888177</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>21.1471136</v>
+        <v>25.2756813</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -5193,17 +5193,17 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupės betono mazgas</t>
+          <t>Vilniaus betono gaminiai</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -5211,30 +5211,30 @@
       <c r="S41" s="4" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Klaipėdos rajone.</t>
+          <t>Viešai skelbiamas HAUS blokelių ir betono gaminių gamintojas.</t>
         </is>
       </c>
       <c r="U41" s="5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://www.vbg.lt/</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://www.vbg.lt/</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://www.vbg.lt/</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą ir gamybos režimą.</t>
+          <t>Žemėlapyje naudotas viešai skelbiamas įmonės adresas; gamybos vietą reikia patikslinti.</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5246,18 +5246,18 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>betono-zona-klaipeda</t>
+          <t>pamario-grupe-kalnuvenai</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono zona</t>
+          <t>UAB Pamario grupė</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Pamario grupė</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5267,24 +5267,24 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Kalnuvėnai</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g. 6, Klaipėda</t>
+          <t>Kaukėnų g. 12, Kalnuvėnai, Klaipėdos r.</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>55.7549809</v>
+        <v>55.7905468</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>21.150509</v>
+        <v>21.1471136</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Pamario grupės betono mazgas</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -5321,30 +5321,30 @@
       <c r="S42" s="4" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U42" s="5" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
+          <t>Reikia patikslinti našumą ir gamybos režimą.</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5356,22 +5356,18 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>topbeton-panevezys</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>307083610</t>
-        </is>
-      </c>
+          <t>betono-zona-klaipeda</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>UAB Topbeton</t>
+          <t>UAB Betono zona</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Topbeton</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5381,24 +5377,24 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Beržų g. 5C, Panevėžys</t>
+          <t>Dvaro g. 6, Klaipėda</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>55.7168572</v>
+        <v>55.7549809</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>24.3617863</v>
+        <v>21.150509</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -5417,17 +5413,17 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Topbeton betono mazgas</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -5435,30 +5431,30 @@
       <c r="S43" s="4" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
         </is>
       </c>
       <c r="U43" s="5" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>https://topbeton.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
+          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5470,18 +5466,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>gelzbetonio-gamyba-panevezys</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr"/>
+          <t>topbeton-panevezys</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>307083610</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>MB Gelžbetonio gamyba</t>
+          <t>UAB Topbeton</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba</t>
+          <t>Topbeton</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Beržų g. 5C, Panevėžys</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.7168572</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>24.3803541</v>
+        <v>24.3617863</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -5527,17 +5527,17 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba Panevėžyje</t>
+          <t>Topbeton betono mazgas</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -5545,30 +5545,30 @@
       <c r="S44" s="4" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U44" s="5" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://topbeton.lt/</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5580,18 +5580,18 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>inroma-pakruojis</t>
+          <t>gelzbetonio-gamyba-panevezys</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>UAB Inroma</t>
+          <t>MB Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Inroma</t>
+          <t>Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5601,24 +5601,24 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Pakruojis</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Pakruojo r. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Pramonės g. 5B, Pakruojis</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>55.9763263</v>
+        <v>55.7409491</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>23.8584712</v>
+        <v>24.3803541</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -5637,17 +5637,17 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Inroma betono mazgas</t>
+          <t>Gelžbetonio gamyba Panevėžyje</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -5655,7 +5655,7 @@
       <c r="S45" s="4" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
+          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U45" s="5" t="n">
@@ -5663,22 +5663,22 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą.</t>
+          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5690,22 +5690,18 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>utenos-betonas-utena</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>300904691</t>
-        </is>
-      </c>
+          <t>inroma-pakruojis</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>UAB Utenos betonas</t>
+          <t>UAB Inroma</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Utenos betonas</t>
+          <t>Inroma</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5715,24 +5711,24 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Pakruojis</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Utenos r. sav.</t>
+          <t>Pakruojo r. sav.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Metalo g. 9B, Utena</t>
+          <t>Pramonės g. 5B, Pakruojis</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>55.4947607</v>
+        <v>55.9763263</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>25.6225075</v>
+        <v>23.8584712</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5761,7 +5757,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Utenos betono mazgas</t>
+          <t>Inroma betono mazgas</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -5769,30 +5765,30 @@
       <c r="S46" s="4" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
         </is>
       </c>
       <c r="U46" s="5" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>https://utenosbetonas.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
+          <t>Reikia patikslinti našumą.</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5804,22 +5800,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>sbetonas-jonava</t>
+          <t>utenos-betonas-utena</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>300902683</t>
+          <t>300904691</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>UAB Sbetonas</t>
+          <t>UAB Utenos betonas</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas</t>
+          <t>Utenos betonas</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5829,24 +5825,24 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Jonava</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Utenos r. sav.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Skarulių g. 58, Jonava</t>
+          <t>Metalo g. 9B, Utena</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>55.0786452</v>
+        <v>55.4947607</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>24.3199072</v>
+        <v>25.6225075</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5875,7 +5871,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas betono mazgas</t>
+          <t>Utenos betono mazgas</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -5883,7 +5879,7 @@
       <c r="S47" s="4" t="inlineStr"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
         </is>
       </c>
       <c r="U47" s="5" t="n">
@@ -5891,22 +5887,22 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://utenosbetonas.lt/</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta pagal prekinio betono požymį.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -5918,18 +5914,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>kalcitas-naujoji-akmene</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr"/>
+          <t>sbetonas-jonava</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>300902683</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>AB Kalcitas</t>
+          <t>UAB Sbetonas</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas</t>
+          <t>Sbetonas</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5939,24 +5939,24 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Jonava</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Skarulių g. 58, Jonava</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>56.3143832</v>
+        <v>55.0786452</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>22.9130704</v>
+        <v>24.3199072</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas betono mišinių gamybos linija</t>
+          <t>Sbetonas betono mazgas</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -5993,26 +5993,30 @@
       <c r="S48" s="4" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
+          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
         </is>
       </c>
       <c r="U48" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="V48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>https://sbetonas.lt/</t>
+        </is>
+      </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
+          <t>Papildomai rasta pagal prekinio betono požymį.</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6024,18 +6028,18 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
+          <t>kalcitas-naujoji-akmene</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelgaudiškio gelžbetonis</t>
+          <t>AB Kalcitas</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonis</t>
+          <t>Kalcitas</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -6045,24 +6049,24 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškis</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Šakių r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>55.07067</v>
+        <v>56.3143832</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>22.976723</v>
+        <v>22.9130704</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -6071,27 +6075,27 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>GLG kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai ir gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonio gamykla</t>
+          <t>Kalcitas betono mišinių gamybos linija</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -6099,30 +6103,26 @@
       <c r="S49" s="4" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
+          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
         </is>
       </c>
       <c r="U49" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/</t>
-        </is>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr"/>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/betonas/betono-misiniai/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
+          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6134,49 +6134,45 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ginfa-kutiskiai</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>302680943</t>
-        </is>
-      </c>
+          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>UAB GinFa</t>
+          <t>UAB Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>GinFa</t>
+          <t>Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai rasta</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Kutiškiai</t>
+          <t>Gelgaudiškis</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Šakių r. sav.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
+          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>55.8326273</v>
+        <v>55.07067</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>23.4995317</v>
+        <v>22.976723</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -6185,27 +6181,27 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>GLG kontaktų puslapis</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono mišiniai ir gelžbetonis</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>GinFa betono gamyba</t>
+          <t>Gelgaudiškio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -6213,22 +6209,30 @@
       <c r="S50" s="4" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
         </is>
       </c>
       <c r="U50" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V50" s="2" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>https://glg.lt/</t>
+        </is>
+      </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X50" s="2" t="inlineStr"/>
+          <t>https://glg.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>https://glg.lt/betonas/betono-misiniai/</t>
+        </is>
+      </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6240,22 +6244,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>antano-gribino-imone-prienai</t>
+          <t>ginfa-kutiskiai</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>170687267</t>
+          <t>302680943</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
+          <t>UAB GinFa</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonė</t>
+          <t>GinFa</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6265,24 +6269,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Prienai</t>
+          <t>Kutiškiai</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Prienų r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Kęstučio g. 95A, Prienai</t>
+          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>54.6523184</v>
+        <v>55.8326273</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>23.9696591</v>
+        <v>23.4995317</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -6311,7 +6315,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonės betono gamyba</t>
+          <t>GinFa betono gamyba</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -6346,22 +6350,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>kelsera-anavilis</t>
+          <t>antano-gribino-imone-prienai</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>304642165</t>
+          <t>170687267</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>UAB Kelsera</t>
+          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Kelsera</t>
+          <t>Antano Gribino įmonė</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6371,24 +6375,24 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Anavilis</t>
+          <t>Prienai</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Prienų r. sav.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Bitininkų g. 13, Anavilis, Vilniaus r.</t>
+          <t>Kęstučio g. 95A, Prienai</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>54.9463928</v>
+        <v>54.6523184</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>25.216796</v>
+        <v>23.9696591</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -6417,7 +6421,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Kelsera betono gamyba</t>
+          <t>Antano Gribino įmonės betono gamyba</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -8419,7 +8423,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T08:39:21.239190+00:00</t>
+          <t>2026-09-23T09:09:43.196745+00:00</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8478,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T08:39:21.239190+00:00</t>
+          <t>2026-09-23T09:09:43.197882+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z68" headerRowCount="1">
-  <autoFilter ref="A1:Z68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z67" headerRowCount="1">
+  <autoFilter ref="A1:Z67"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Įrašo ID"/>
     <tableColumn id="2" name="Įmonės kodas"/>
@@ -492,10 +492,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z68"/>
+  <dimension ref="A1:Z67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
@@ -1012,7 +1012,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-vilnius-sirvintu-kryptis</t>
+          <t>betono-centras-rudningai</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1032,43 +1032,43 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mūsų įmonė – planavimo taškas</t>
+          <t>Mūsų įmonė</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Rūdningai</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Šalčininkų r. sav.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Vakarinis aplinkkelis, Vilnius (15 km keliais nuo Riovonių)</t>
+          <t>Rūdningai</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>54.759939539351</v>
+        <v>54.43883333333333</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>25.203320952262</v>
+        <v>25.081</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Apskaičiuotas 15 km važiavimo taškas</t>
+          <t>Naudotojo pateiktas koordinačių taškas</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Valhalla / OpenStreetMap maršrutas</t>
+          <t>Naudotojo pateiktos koordinatės</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://valhalla.github.io/valhalla/api/turn-by-turn/overview/</t>
+          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1083,19 +1083,31 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Orientacinė gamyklos vieta – Širvintų kryptis</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
+          <t>SBM3000 (Schwenk)</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>3,0 m³</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>80 m³/h</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>3x85 t</t>
+        </is>
+      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>Orientacinis gamyklos planavimo taškas ties Riovonių gamyklos 15 km važiavimo keliais riba, Širvintų kryptimi.</t>
+          <t>Betono centro betono mazgas Rūdninguose.</t>
         </is>
       </c>
       <c r="U5" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1104,25 +1116,29 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>https://valhalla.github.io/valhalla/api/turn-by-turn/overview/</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr"/>
+          <t>https://betonocentras.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
+        </is>
+      </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>Taškas apskaičiuotas Valhalla maršrutu nuo Naujosios Riovonių g. 11 iki Širvintų centro. Tai orientacinis 15,00 km važiavimo ribos taškas Vakarinio aplinkkelio trasoje, o ne patvirtintas statybos sklypas.</t>
+          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos DMS formatu: 54°26'19.8"N 25°04'51.6"E.</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-rudningai</t>
+          <t>betono-centras-rudninkai</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1147,7 +1163,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Rūdningai</t>
+          <t>Rūdninkai</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1157,14 +1173,14 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Rūdningai</t>
+          <t>Rūdninkai</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>54.43883333333333</v>
+        <v>54.43924548406194</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>25.081</v>
+        <v>25.08098427100702</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1178,7 +1194,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
+          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1193,12 +1209,12 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>SBM3000 (Schwenk)</t>
+          <t>SBM3300</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>3,0 m³</t>
+          <t>3,3 m³</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -1213,7 +1229,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>Betono centro betono mazgas Rūdninguose.</t>
+          <t>Betono centro betono mazgas Rūdninkuose.</t>
         </is>
       </c>
       <c r="U6" s="5" t="n">
@@ -1231,12 +1247,12 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.43883333333333,25.081</t>
+          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos DMS formatu: 54°26'19.8"N 25°04'51.6"E.</t>
+          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos dešimtainiu formatu.</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1248,7 +1264,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-rudninkai</t>
+          <t>betono-centras-kaunas</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1273,38 +1289,38 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Rūdninkai</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Šalčininkų r. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Rūdninkai</t>
+          <t>Raudondvario pl. 157, Kaunas</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>54.43924548406194</v>
+        <v>54.9128359</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>25.08098427100702</v>
+        <v>23.8412662</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktas koordinačių taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos koordinatės</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1319,27 +1335,23 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>SBM3300</t>
+          <t>Wiggert</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>3,3 m³</t>
+          <t>2,0 m³ ir 3,0 m³</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>80 m³/h</t>
-        </is>
-      </c>
-      <c r="S7" s="4" t="inlineStr">
-        <is>
-          <t>3x85 t</t>
-        </is>
-      </c>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>Betono centro betono mazgas Rūdninkuose.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Kaune.</t>
         </is>
       </c>
       <c r="U7" s="5" t="n">
@@ -1357,24 +1369,24 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=54.439245484061935,25.080984271007022</t>
+          <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>Papildomas Betono centro mazgas įtrauktas pagal naudotojo pateiktą informaciją. Koordinatės pateiktos dešimtainiu formatu.</t>
+          <t>Kauno betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-kaunas</t>
+          <t>betono-centras-klaipeda</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1399,24 +1411,24 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Raudondvario pl. 157, Kaunas</t>
+          <t>Liepų g. 87N, Klaipėda</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>54.9128359</v>
+        <v>55.7290357</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>23.8412662</v>
+        <v>21.1544709</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1445,23 +1457,23 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Wiggert</t>
+          <t>LIEBHERR MOBILMIX</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2,0 m³ ir 3,0 m³</t>
+          <t>2,25 m³</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
+          <t>60 m³/h</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Kaune.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Klaipėdoje.</t>
         </is>
       </c>
       <c r="U8" s="5" t="n">
@@ -1484,7 +1496,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>Kauno betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialiame Betono centro kontaktų puslapyje patvirtintas Klaipėdos padalinys. Mazgo techniniai duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1496,7 +1508,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-klaipeda</t>
+          <t>betono-centras-siauliai</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1521,24 +1533,24 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Šiauliai</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Šiaulių m. sav.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Liepų g. 87N, Klaipėda</t>
+          <t>Daubos g. 7A, Šiauliai</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>55.7290357</v>
+        <v>55.9056327</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>21.1544709</v>
+        <v>23.3141873</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1583,7 +1595,7 @@
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Klaipėdoje.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Šiauliuose.</t>
         </is>
       </c>
       <c r="U9" s="5" t="n">
@@ -1606,7 +1618,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame Betono centro kontaktų puslapyje patvirtintas Klaipėdos padalinys. Mazgo techniniai duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
+          <t>Šiaulių betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1618,7 +1630,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-siauliai</t>
+          <t>betono-centras-mazeikiai</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1643,24 +1655,24 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Šiauliai</t>
+          <t>Mažeikiai</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių m. sav.</t>
+          <t>Mažeikių r. sav.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Daubos g. 7A, Šiauliai</t>
+          <t>Troškučių g. 1, Mažeikiai</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>55.9056327</v>
+        <v>56.3189055</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>23.3141873</v>
+        <v>22.2967774</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1689,23 +1701,15 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>LIEBHERR MOBILMIX</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2,25 m³</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/h</t>
-        </is>
-      </c>
+          <t>Mažeikių betono mazgas</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Šiauliuose.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Mažeikiuose.</t>
         </is>
       </c>
       <c r="U10" s="5" t="n">
@@ -1726,21 +1730,17 @@
           <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>Šiaulių betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
-        </is>
-      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-mazeikiai</t>
+          <t>betono-centras-panevezys</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1765,24 +1765,24 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Mažeikiai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių r. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Troškučių g. 1, Mažeikiai</t>
+          <t>S. Kerbedžio g. 52A, Panevėžys</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>56.3189055</v>
+        <v>55.7423854</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>22.2967774</v>
+        <v>24.3777723</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1811,15 +1811,23 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių betono mazgas</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
+          <t>LIEBHERR Betomix</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2,25 m³</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/h</t>
+        </is>
+      </c>
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Mažeikiuose.</t>
+          <t>Viešai skelbiamas Betono centro betono mazgas Panevėžyje.</t>
         </is>
       </c>
       <c r="U11" s="5" t="n">
@@ -1840,73 +1848,77 @@
           <t>https://betonocentras.lt/kontaktai/</t>
         </is>
       </c>
-      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>Panevėžio betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+        </is>
+      </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>betono-centras-panevezys</t>
+          <t>heidelberg-vilnius-siaures</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>123018186</t>
+          <t>304102190</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono centras</t>
+          <t>UAB Heidelberg Materials Lietuva Betonas</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Betono centras</t>
+          <t>Heidelberg Materials</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Mūsų įmonė</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Glaudėnai</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52A, Panevėžys</t>
+          <t>Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>55.7423854</v>
+        <v>55.774886</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>24.3777723</v>
+        <v>21.160809</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas; adresas patikslintas reverse-geokodavimu</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1921,58 +1933,50 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>LIEBHERR Betomix</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2,25 m³</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/h</t>
-        </is>
-      </c>
+          <t>Heidelberg Materials betono gamykla, Glaudėnai</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
       <c r="S12" s="4" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Betono centro betono mazgas Panevėžyje.</t>
+          <t>Heidelberg Materials betono gamyklų tinklo taškas perkeltas iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="U12" s="5" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>https://betonocentras.lt/</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>https://betonocentras.lt/kontaktai/</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>https://betonocentras.lt/kontaktai/</t>
+          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio betono mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Perkelta iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją. Google Maps nuoroda išsisprendė į koordinates 55.774886, 21.160809; vietovė patikslinta reverse-geokodavimu kaip Glaudėnų k., Sendvario sen., Klaipėdos r. sav. Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis paliktas kaip įmonės šaltinis.</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-vilnius-siaures</t>
+          <t>heidelberg-vilnius-sandeliu</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1997,38 +2001,38 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Glaudėnai</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
+          <t>Sandėlių g. 16, Vilnius</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>55.774886</v>
+        <v>54.6535114</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>21.160809</v>
+        <v>25.1242965</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas; adresas patikslintas reverse-geokodavimu</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2043,7 +2047,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials betono gamykla, Glaudėnai</t>
+          <t>Vilniaus betono gamykla, Sandėlių g.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -2051,7 +2055,7 @@
       <c r="S13" s="4" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials betono gamyklų tinklo taškas perkeltas iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją Glaudėnų k., Sendvario sen., Klaipėdos r. sav.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Vilniuje.</t>
         </is>
       </c>
       <c r="U13" s="5" t="n">
@@ -2069,24 +2073,24 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/WuHkJbkmPjqkPWgL8</t>
+          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>Perkelta iš Šiaurės g. 2, Vilnius į naudotojo pateiktą Google Maps lokaciją. Google Maps nuoroda išsisprendė į koordinates 55.774886, 21.160809; vietovė patikslinta reverse-geokodavimu kaip Glaudėnų k., Sendvario sen., Klaipėdos r. sav. Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis paliktas kaip įmonės šaltinis.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-vilnius-sandeliu</t>
+          <t>heidelberg-avizieniai-klevu</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2111,24 +2115,24 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Avižieniai</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Sandėlių g. 16, Vilnius</t>
+          <t>Klevų g. 2, Avižieniai, Vilniaus r.</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>54.6535114</v>
+        <v>54.760788043384</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>25.1242965</v>
+        <v>25.179476693822</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -2137,12 +2141,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>ArcGIS World Geocoding Service</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2157,19 +2161,31 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus betono gamykla, Sandėlių g.</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
+          <t>Ammann Elba</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/val.</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>3x85 t</t>
+        </is>
+      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Vilniuje.</t>
+          <t>Heidelberg Materials betono mazgas Klevų g. 2, Avižieniuose.</t>
         </is>
       </c>
       <c r="U14" s="5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
@@ -2188,19 +2204,19 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina Klevų g. 2, Avižieniai, betono užsakymų tašką. Mazgo gamintojas, maišyklės tūris, realus našumas ir silosų duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-avizieniai-klevu</t>
+          <t>heidelberg-kaunas</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2225,24 +2241,24 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Avižieniai</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Klevų g. 2, Avižieniai, Vilniaus r.</t>
+          <t>Technikos g. 7K, Kaunas</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>54.760788043384</v>
+        <v>54.9093181</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>25.179476693822</v>
+        <v>24.0122104</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -2251,12 +2267,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS World Geocoding Service</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2271,31 +2287,19 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/val.</t>
-        </is>
-      </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>3x85 t</t>
-        </is>
-      </c>
+          <t>Kauno betono gamykla</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials betono mazgas Klevų g. 2, Avižieniuose.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Kaune.</t>
         </is>
       </c>
       <c r="U15" s="5" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -2314,19 +2318,19 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina Klevų g. 2, Avižieniai, betono užsakymų tašką. Mazgo gamintojas, maišyklės tūris, realus našumas ir silosų duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-kaunas</t>
+          <t>heidelberg-klaipeda</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2351,24 +2355,24 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Technikos g. 7K, Kaunas</t>
+          <t>Švepelių g. 5, Klaipėda</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>54.9093181</v>
+        <v>55.6744503</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>24.0122104</v>
+        <v>21.2165993</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2397,15 +2401,25 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Kauno betono gamykla</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
+          <t>Wiggert</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Kaune.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Klaipėdoje.</t>
         </is>
       </c>
       <c r="U16" s="5" t="n">
@@ -2428,19 +2442,19 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje. Klaipėdos mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-klaipeda</t>
+          <t>heidelberg-alytus</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2465,24 +2479,24 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Alytus</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Alytaus m. sav.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Švepelių g. 5, Klaipėda</t>
+          <t>Kalniškės g. 2, Alytus</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>55.6744503</v>
+        <v>54.4113266</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>21.2165993</v>
+        <v>24.0081029</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2511,25 +2525,15 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Wiggert</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S17" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>Alytaus betono gamykla</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Klaipėdoje.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Alytuje.</t>
         </is>
       </c>
       <c r="U17" s="5" t="n">
@@ -2552,19 +2556,19 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje. Klaipėdos mazgo techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-alytus</t>
+          <t>heidelberg-pasvalys</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2589,28 +2593,28 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Alytus</t>
+          <t>Pasvalys</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Alytaus m. sav.</t>
+          <t>Pasvalio r. sav.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Kalniškės g. 2, Alytus</t>
+          <t>Beržų g. 8C, Pasvalys</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>54.4113266</v>
+        <v>56.0647646</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>24.0081029</v>
+        <v>24.3860079</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Gatvės lygio taškas; reikia tikslesnio adreso taško</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2635,7 +2639,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Alytaus betono gamykla</t>
+          <t>Pasvalio betono gamykla</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -2643,11 +2647,11 @@
       <c r="S18" s="4" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Alytuje.</t>
+          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Pasvalyje.</t>
         </is>
       </c>
       <c r="U18" s="5" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2678,22 +2682,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>heidelberg-pasvalys</t>
+          <t>palmusta-vilnius</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>304102190</t>
+          <t>122619426</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>UAB Heidelberg Materials Lietuva Betonas</t>
+          <t>UAB Palmusta</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Heidelberg Materials</t>
+          <t>Palmusta</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2703,28 +2707,28 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Pasvalys</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Pasvalio r. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Beržų g. 8C, Pasvalys</t>
+          <t>Sudervės kel. 1A, Avižieniai, Vilniaus r.</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>56.0647646</v>
+        <v>54.7136351</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>24.3860079</v>
+        <v>25.2359209</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Gatvės lygio taškas; reikia tikslesnio adreso taško</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2749,7 +2753,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Pasvalio betono gamykla</t>
+          <t>Palmusta betono mazgas</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -2757,7 +2761,7 @@
       <c r="S19" s="4" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Pasvalyje.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Vilniaus regione.</t>
         </is>
       </c>
       <c r="U19" s="5" t="n">
@@ -2765,24 +2769,20 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt</t>
+          <t>https://www.palmusta.lt/</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
+          <t>https://www.palmusta.lt/</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
-        </is>
-      </c>
-      <c r="Y19" s="2" t="inlineStr">
-        <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
-        </is>
-      </c>
+          <t>https://www.palmusta.lt/</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -2792,22 +2792,18 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>palmusta-vilnius</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>122619426</t>
-        </is>
-      </c>
+          <t>gkg3-vilnius</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UAB Palmusta</t>
+          <t>UAB Vilniaus gelžbetoninių konstrukcijų gamykla Nr. 3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Palmusta</t>
+          <t>GKG-3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2822,48 +2818,48 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Sudervės kel. 1A, Avižieniai, Vilniaus r.</t>
+          <t>Šaltupio g. 11, Vilnius</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>54.7136351</v>
+        <v>54.6471731</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>25.2359209</v>
+        <v>25.1918488</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialios Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>GKG3 kontaktų puslapis</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://gkg3.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Palmusta betono mazgas</t>
+          <t>GKG-3 gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -2871,28 +2867,32 @@
       <c r="S20" s="4" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas Vilniaus regione.</t>
+          <t>Gelžbetoninių konstrukcijų gamyba Vilniuje.</t>
         </is>
       </c>
       <c r="U20" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>https://www.palmusta.lt/</t>
+          <t>https://www.gkg3.lt/</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>https://www.palmusta.lt/</t>
+          <t>https://gkg3.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>https://www.palmusta.lt/</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr"/>
+          <t>https://gkg3.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>Koordinatės patikslintos pagal oficialaus GKG3 kontaktų puslapio Google Maps nuorodą.</t>
+        </is>
+      </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -2902,18 +2902,18 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>gkg3-vilnius</t>
+          <t>perdanga-vilnius</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>UAB Vilniaus gelžbetoninių konstrukcijų gamykla Nr. 3</t>
+          <t>UAB Perdanga</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>GKG-3</t>
+          <t>Perdanga</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2933,28 +2933,28 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Šaltupio g. 11, Vilnius</t>
+          <t>Lentvario g. 16, Vilnius</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>54.6471731</v>
+        <v>54.642372</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>25.1918488</v>
+        <v>25.1441455</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Oficialios Google Maps nuorodos taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>GKG3 kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>https://gkg3.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2969,15 +2969,19 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>GKG-3 gelžbetonio gamykla</t>
+          <t>Perdanga Vilniaus gamykla</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>150 m³/val.</t>
+        </is>
+      </c>
       <c r="S21" s="4" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninių konstrukcijų gamyba Vilniuje.</t>
+          <t>Viešai nurodoma nauja gelžbetonio elementų gamybos linija, kurios našumas 150 m³/val.</t>
         </is>
       </c>
       <c r="U21" s="5" t="n">
@@ -2985,24 +2989,20 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>https://www.gkg3.lt/</t>
+          <t>https://www.perdanga.lt/</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>https://gkg3.lt/kontaktai/</t>
+          <t>https://www.perdanga.lt/</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>https://gkg3.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t>Koordinatės patikslintos pagal oficialaus GKG3 kontaktų puslapio Google Maps nuorodą.</t>
-        </is>
-      </c>
+          <t>https://www.perdanga.lt/</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -3012,7 +3012,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>perdanga-vilnius</t>
+          <t>perdanga-klaipeda</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
@@ -3033,24 +3033,24 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Lentvario g. 16, Vilnius</t>
+          <t>Dubysos g. 27, Klaipėda</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>54.642372</v>
+        <v>55.6923067</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>25.1441455</v>
+        <v>21.1631559</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -3079,23 +3079,27 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Perdanga Vilniaus gamykla</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+          <t>Stetter</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2x1,5 m³</t>
+        </is>
+      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>150 m³/val.</t>
+          <t>40-50 m³/h</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>Viešai nurodoma nauja gelžbetonio elementų gamybos linija, kurios našumas 150 m³/val.</t>
+          <t>Viešai skelbiamas Perdangos padalinys Klaipėdoje.</t>
         </is>
       </c>
       <c r="U22" s="5" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -3109,31 +3113,35 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr"/>
+          <t>https://www.perdanga.lt/lt/produkcija/betono-misiniai/gamyba-transportavimas</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>Oficialus Perdangos puslapis nurodo, kad Klaipėdoje betono mišiniai gaminami STETTER technologinėmis linijomis. Maišyklės ir našumo duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
+        </is>
+      </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>perdanga-klaipeda</t>
+          <t>kauno-gelzbetonis-kaunas</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>UAB Perdanga</t>
+          <t>UAB Kauno gelžbetonis</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Perdanga</t>
+          <t>Kauno gelžbetonis</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3143,24 +3151,24 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Dubysos g. 27, Klaipėda</t>
+          <t>Pramonės pr. 8, Kaunas</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>55.6923067</v>
+        <v>54.9122829</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>21.1631559</v>
+        <v>23.9864942</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -3189,69 +3197,61 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Stetter</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2x1,5 m³</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>40-50 m³/h</t>
-        </is>
-      </c>
+          <t>Kauno gelžbetonio gamykla</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="4" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Perdangos padalinys Klaipėdoje.</t>
+          <t>Viešai skelbiamas gelžbetonio gamintojas Kaune.</t>
         </is>
       </c>
       <c r="U23" s="5" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
+          <t>https://www.kaunogelzbetonis.lt/</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/</t>
+          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>https://www.perdanga.lt/lt/produkcija/betono-misiniai/gamyba-transportavimas</t>
+          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Perdangos puslapis nurodo, kad Klaipėdoje betono mišiniai gaminami STETTER technologinėmis linijomis. Maišyklės ir našumo duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialus Kauno gelžbetonio kontaktų puslapis patvirtina Pramonės pr. 8 adresą.</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>kauno-gelzbetonis-kaunas</t>
+          <t>ukmerges-gelzbetonis-ukmerge</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>UAB Kauno gelžbetonis</t>
+          <t>UAB Ukmergės gelžbetonis</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Kauno gelžbetonis</t>
+          <t>Ukmergės gelžbetonis</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Ukmergė</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Ukmergės r. sav.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Pramonės pr. 8, Kaunas</t>
+          <t>Antakalnio g. 60, Ukmergė</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>54.9122829</v>
+        <v>55.2419448</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>23.9864942</v>
+        <v>24.7875927</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Kauno gelžbetonio gamykla</t>
+          <t>Ukmergės gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -3315,7 +3315,7 @@
       <c r="S24" s="4" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas gelžbetonio gamintojas Kaune.</t>
+          <t>Viešai skelbiamas gelžbetonio gamintojas Ukmergėje.</t>
         </is>
       </c>
       <c r="U24" s="5" t="n">
@@ -3323,22 +3323,22 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaunogelzbetonis.lt/</t>
+          <t>https://ukmergesgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
+          <t>https://ukmergesgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>https://www.kaunogelzbetonis.lt/kontaktai/</t>
+          <t>https://ukmergesgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Kauno gelžbetonio kontaktų puslapis patvirtina Pramonės pr. 8 adresą.</t>
+          <t>Oficiali Ukmergės gelžbetonio svetainė palikta kaip pagrindinis šaltinis; naujų patikimų koordinačių nerasta.</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3350,18 +3350,18 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ukmerges-gelzbetonis-ukmerge</t>
+          <t>gelzbetonines-konstrukcijos-siauliai</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>UAB Ukmergės gelžbetonis</t>
+          <t>UAB Gelžbetoninės konstrukcijos</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Ukmergės gelžbetonis</t>
+          <t>Gelžbetoninės konstrukcijos</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Ukmergė</t>
+          <t>Šiauliai</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Ukmergės r. sav.</t>
+          <t>Šiaulių m. sav.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Antakalnio g. 60, Ukmergė</t>
+          <t>Sodo g. 20A, Šiauliai</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>55.2419448</v>
+        <v>55.9495824</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>24.7875927</v>
+        <v>23.3105291</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialios žemėlapio nuorodos taškas</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Gelžbetoninės konstrukcijos kontaktų puslapis</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Ukmergės gelžbetonio gamykla</t>
+          <t>Gelžbetoninių konstrukcijų gamykla</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -3425,7 +3425,7 @@
       <c r="S25" s="4" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas gelžbetonio gamintojas Ukmergėje.</t>
+          <t>Viešai skelbiamas gelžbetonio gamintojas Šiauliuose.</t>
         </is>
       </c>
       <c r="U25" s="5" t="n">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>https://ukmergesgelzbetonis.lt/</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>https://ukmergesgelzbetonis.lt/</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>https://ukmergesgelzbetonis.lt/</t>
+          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Ukmergės gelžbetonio svetainė palikta kaip pagrindinis šaltinis; naujų patikimų koordinačių nerasta.</t>
+          <t>Koordinatės patikslintos pagal oficialaus kontaktų puslapio žemėlapio tašką.</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3460,18 +3460,18 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>gelzbetonines-konstrukcijos-siauliai</t>
+          <t>inhus-senieji-trakai</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelžbetoninės konstrukcijos</t>
+          <t>UAB INHUS Lietuva</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninės konstrukcijos</t>
+          <t>INHUS</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3481,38 +3481,38 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Šiauliai</t>
+          <t>Senieji Trakai</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių m. sav.</t>
+          <t>Trakų r. sav.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Sodo g. 20A, Šiauliai</t>
+          <t>Plačioji g. 27, Senieji Trakai</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>55.9495824</v>
+        <v>54.6140174</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>23.3105291</v>
+        <v>24.980818</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Oficialios žemėlapio nuorodos taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninės konstrukcijos kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Surenkamas gelžbetonis</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetoninių konstrukcijų gamykla</t>
+          <t>INHUS gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -3535,7 +3535,7 @@
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas gelžbetonio gamintojas Šiauliuose.</t>
+          <t>Viešai skelbiamas surenkamojo gelžbetonio konstrukcijų gamintojas.</t>
         </is>
       </c>
       <c r="U26" s="5" t="n">
@@ -3543,24 +3543,20 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/</t>
+          <t>https://inhus.eu/</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
+          <t>https://inhus.eu/</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>https://www.gelzbetonineskonstrukcijos.lt/contacts/</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t>Koordinatės patikslintos pagal oficialaus kontaktų puslapio žemėlapio tašką.</t>
-        </is>
-      </c>
+          <t>https://inhus.eu/</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>2026-06-29</t>
@@ -3570,18 +3566,18 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>inhus-senieji-trakai</t>
+          <t>gelmesta-vievis</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>UAB INHUS Lietuva</t>
+          <t>UAB Gelmesta</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>INHUS</t>
+          <t>Gelmesta</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3591,24 +3587,24 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Senieji Trakai</t>
+          <t>Vievis</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Trakų r. sav.</t>
+          <t>Elektrėnų sav.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Plačioji g. 27, Senieji Trakai</t>
+          <t>Statybininkų g. 1B, Vievis</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>54.6140174</v>
+        <v>54.7782794</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>24.980818</v>
+        <v>24.8280365</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3627,17 +3623,17 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Surenkamas gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>INHUS gelžbetonio gamykla</t>
+          <t>Gelmesta betono mazgas</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -3645,25 +3641,25 @@
       <c r="S27" s="4" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas surenkamojo gelžbetonio konstrukcijų gamintojas.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas.</t>
         </is>
       </c>
       <c r="U27" s="5" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
+          <t>https://gelmesta.lt/</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
+          <t>https://gelmesta.lt/</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
+          <t>https://gelmesta.lt/</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr"/>
@@ -3676,18 +3672,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>gelmesta-vievis</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr"/>
+          <t>suduvos-betonas-marijampole</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>302330957</t>
+        </is>
+      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelmesta</t>
+          <t>UAB Surenkamos statybos konstrukcijos</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Gelmesta</t>
+          <t>Sūduvos betonas</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3697,24 +3697,24 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Vievis</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Elektrėnų sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Statybininkų g. 1B, Vievis</t>
+          <t>Sporto g. 9H, LT-68108 Marijampolė</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>54.7782794</v>
+        <v>54.5702553</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>24.8280365</v>
+        <v>23.3803405</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3743,61 +3743,77 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Gelmesta betono mazgas</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr"/>
+          <t>Sūduvos betono mazgas</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>iki 200 m³ per darbo pamainą</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas.</t>
+          <t>Oficialiame puslapyje nurodoma betono mišinių gamyba ir pristatymas; Marijampolėje esantis 130 arų betono mazgas gali pagaminti iki 200 m³ betono per darbo pamainą.</t>
         </is>
       </c>
       <c r="U28" s="5" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>https://gelmesta.lt/</t>
+          <t>https://www.suduvos-betonas.lt/</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>https://gelmesta.lt/</t>
+          <t>https://www.suduvos-betonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>https://gelmesta.lt/</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr"/>
+          <t>https://www.suduvos-betonas.lt/betono-misiniai/</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>Atnaujinta pagal oficialų suduvos-betonas.lt kontaktų, pradinį ir betono mišinių puslapius: juridinis pavadinimas, įmonės kodas, adresas, betono mišinių veikla ir viešas mazgo aprašymas.</t>
+        </is>
+      </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>suduvos-betonas-marijampole</t>
+          <t>statkasta-kaunas</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>302330957</t>
+          <t>185607978</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>UAB Surenkamos statybos konstrukcijos</t>
+          <t>UAB Statkasta</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sūduvos betonas</t>
+          <t>Statkasta</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3807,38 +3823,38 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Serdokai</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Vilkaviškio r. sav.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Sporto g. 9H, LT-68108 Marijampolė</t>
+          <t>Gėlių g. 34, Serdokų k., Vilkaviškio r., LT-70201</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>54.5702553</v>
+        <v>54.6279368</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>23.3803405</v>
+        <v>23.0871345</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Vietovės lygio taškas; reikia tikslesnio adreso taško</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>ArcGIS geokodavimas pagal oficialų Statkasta adresą</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://statkasta.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3853,77 +3869,69 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Sūduvos betono mazgas</t>
+          <t>Statkasta betono mazgas</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>Ammann Elba CBT60SL, 1 m³</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>iki 200 m³ per darbo pamainą</t>
-        </is>
-      </c>
-      <c r="S29" s="4" t="inlineStr">
-        <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
+          <t>iki 60 m³/h</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje nurodoma betono mišinių gamyba ir pristatymas; Marijampolėje esantis 130 arų betono mazgas gali pagaminti iki 200 m³ betono per darbo pamainą.</t>
+          <t>Betono mazgo gamintojas Ammann Elba; modelis CBT60SL; maišyklė 1 m³; našumas iki 60 m³/h.</t>
         </is>
       </c>
       <c r="U29" s="5" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>https://www.suduvos-betonas.lt/</t>
+          <t>https://statkasta.lt/</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>https://www.suduvos-betonas.lt/kontaktai/</t>
+          <t>https://statkasta.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>https://www.suduvos-betonas.lt/betono-misiniai/</t>
+          <t>https://statkasta.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>Atnaujinta pagal oficialų suduvos-betonas.lt kontaktų, pradinį ir betono mišinių puslapius: juridinis pavadinimas, įmonės kodas, adresas, betono mišinių veikla ir viešas mazgo aprašymas.</t>
+          <t>Oficialiame Statkasta kontaktų puslapyje nurodytas adresas Gėlių g. 34, Serdokų k.; koordinatės geokoduotos iki vietovės lygio. Rankiniu būdu papildyta techninė informacija: gamintojas Ammann Elba, modelis CBT60SL, maišyklė 1 m³, našumas iki 60 m³/h.</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>statkasta-kaunas</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>185607978</t>
-        </is>
-      </c>
+          <t>autokausta-kaunas</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UAB Statkasta</t>
+          <t>UAB Autokausta</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Statkasta</t>
+          <t>Autokausta</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3933,38 +3941,38 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Serdokai</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Vilkaviškio r. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Gėlių g. 34, Serdokų k., Vilkaviškio r., LT-70201</t>
+          <t>Marvelės g. 199B, Kaunas</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>54.6279368</v>
+        <v>54.9007881</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>23.0871345</v>
+        <v>23.8489377</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Vietovės lygio taškas; reikia tikslesnio adreso taško</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS geokodavimas pagal oficialų Statkasta adresą</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3977,71 +3985,63 @@
           <t>Betono mišiniai</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>Statkasta betono mazgas</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>Ammann Elba CBT60SL, 1 m³</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>iki 60 m³/h</t>
-        </is>
-      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="4" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgo gamintojas Ammann Elba; modelis CBT60SL; maišyklė 1 m³; našumas iki 60 m³/h.</t>
+          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo pavadinimą reikia patikslinti.</t>
         </is>
       </c>
       <c r="U30" s="5" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/</t>
+          <t>https://autokausta.lt/</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/kontaktai/</t>
+          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>https://statkasta.lt/kontaktai/</t>
+          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame Statkasta kontaktų puslapyje nurodytas adresas Gėlių g. 34, Serdokų k.; koordinatės geokoduotos iki vietovės lygio. Rankiniu būdu papildyta techninė informacija: gamintojas Ammann Elba, modelis CBT60SL, maišyklė 1 m³, našumas iki 60 m³/h.</t>
+          <t>Oficialus Autokausta betono puslapis patvirtina betono veiklą ir Marvelės g. 199B kontaktą.</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>autokausta-kaunas</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr"/>
+          <t>betono-baze-visaginas</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>302725961</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>UAB Autokausta</t>
+          <t>UAB Betono bazė</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Autokausta</t>
+          <t>Betono bazė</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4051,24 +4051,24 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Kaunas</t>
+          <t>Visaginas</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Kauno m. sav.</t>
+          <t>Visagino sav.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Marvelės g. 199B, Kaunas</t>
+          <t>Elektrinės g. 11, Drūkšinių k., Visagino sav.</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>54.9007881</v>
+        <v>55.5963685</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>23.8489377</v>
+        <v>26.5817201</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -4095,36 +4095,40 @@
           <t>Betono mišiniai</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Betono bazė</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr"/>
       <c r="S31" s="4" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo pavadinimą reikia patikslinti.</t>
+          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo adresą reikia patikslinti.</t>
         </is>
       </c>
       <c r="U31" s="5" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>https://autokausta.lt/</t>
+          <t>https://www.betonobaze.lt/</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
+          <t>https://www.betonobaze.lt/kontaktai</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>https://www.autokausta.lt/apie-mus/betonas/</t>
+          <t>https://www.betonobaze.lt/kontaktai</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Autokausta betono puslapis patvirtina betono veiklą ir Marvelės g. 199B kontaktą.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Elektrinės g. 11 adresą ir betono bazės veiklą.</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4136,22 +4140,18 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>betono-baze-visaginas</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>302725961</t>
-        </is>
-      </c>
+          <t>transdosa-druskininkai</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono bazė</t>
+          <t>UAB Transdosa</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Betono bazė</t>
+          <t>Transdosa</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4161,24 +4161,24 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Visaginas</t>
+          <t>Druskininkai</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Visagino sav.</t>
+          <t>Druskininkų sav.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Elektrinės g. 11, Drūkšinių k., Visagino sav.</t>
+          <t>Žvyro g. 2A, Margų k., Druskininkų sav.</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>55.5963685</v>
+        <v>54.146785</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>26.5817201</v>
+        <v>23.9291769</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -4207,88 +4207,98 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Betono bazė</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr"/>
+          <t>Elkomix-90 quick master</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1,5 m³</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>40 m³/h</t>
+        </is>
+      </c>
+      <c r="S32" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo adresą reikia patikslinti.</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Druskininkų regione.</t>
         </is>
       </c>
       <c r="U32" s="5" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonobaze.lt/</t>
+          <t>https://transdosa.lt/</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonobaze.lt/kontaktai</t>
+          <t>https://www.transdosa.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonobaze.lt/kontaktai</t>
+          <t>https://www.transdosa.lt/betonas/</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Elektrinės g. 11 adresą ir betono bazės veiklą.</t>
+          <t>Oficialūs Transdosa kontaktų ir betono puslapiai patvirtina Margų karjero betono gamybą adresu Žvyro g. 2A. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>transdosa-druskininkai</t>
+          <t>sodbeta-siauliai</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>UAB Transdosa</t>
+          <t>UAB Sodbeta</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Transdosa</t>
+          <t>Sodbeta</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Konkurentas</t>
+          <t>Papildomai rasta</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Druskininkai</t>
+          <t>Šiauliai</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Druskininkų sav.</t>
+          <t>Šiaulių m. sav.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Žvyro g. 2A, Margų k., Druskininkų sav.</t>
+          <t>Sodo g. 20, Šiauliai</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>54.146785</v>
+        <v>55.949032</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>23.9291769</v>
+        <v>23.3125879</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -4307,81 +4317,75 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Elkomix-90 quick master</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>1,5 m³</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>40 m³/h</t>
-        </is>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>2</v>
-      </c>
+          <t>Sodbeta betono gaminių gamykla</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="4" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas Druskininkų regione.</t>
+          <t>Viešai skelbiama gelžbetonio ir betono gaminių gamyba Šiauliuose.</t>
         </is>
       </c>
       <c r="U33" s="5" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>https://transdosa.lt/</t>
+          <t>https://sodbeta.lt/</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>https://www.transdosa.lt/kontaktai/</t>
+          <t>https://sodbeta.lt/</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>https://www.transdosa.lt/betonas/</t>
+          <t>https://sodbeta.lt/betonas/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>Oficialūs Transdosa kontaktų ir betono puslapiai patvirtina Margų karjero betono gamybą adresu Žvyro g. 2A. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficiali Sodbeta svetainė patvirtina Sodo g. 20 adresą ir betono mišinių puslapį.</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>sodbeta-siauliai</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr"/>
+          <t>alytaus-gelzbetonis-alytus</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>149720232</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>UAB Sodbeta</t>
+          <t>AB Alytaus gelžbetonis</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Sodbeta</t>
+          <t>Alytaus gelžbetonis</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4391,53 +4395,53 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Šiauliai</t>
+          <t>Alytus</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Šiaulių m. sav.</t>
+          <t>Alytaus m. sav.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Sodo g. 20, Šiauliai</t>
+          <t>Pramonės g. 15, Alytus</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>55.949032</v>
+        <v>54.426129</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>23.3125879</v>
+        <v>24.016482</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialaus kontaktų puslapio žemėlapio taškas</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Alytaus gelžbetonis kontaktų puslapis</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Sodbeta betono gaminių gamykla</t>
+          <t>Alytaus gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -4445,30 +4449,30 @@
       <c r="S34" s="4" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama gelžbetonio ir betono gaminių gamyba Šiauliuose.</t>
+          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U34" s="5" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>https://sodbeta.lt/</t>
+          <t>https://alytausgelzbetonis.lt/</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>https://sodbeta.lt/</t>
+          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>https://sodbeta.lt/betonas/betono-misiniai/</t>
+          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Sodbeta svetainė patvirtina Sodo g. 20 adresą ir betono mišinių puslapį.</t>
+          <t>Patikslinta pagal oficialų kontaktų puslapį.</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4480,22 +4484,18 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>alytaus-gelzbetonis-alytus</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>149720232</t>
-        </is>
-      </c>
+          <t>gernora-marijampole</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>AB Alytaus gelžbetonis</t>
+          <t>UAB Gernora</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Alytaus gelžbetonis</t>
+          <t>Gernora</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4505,38 +4505,38 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Alytus</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Alytaus m. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Pramonės g. 15, Alytus</t>
+          <t>Vingio g. 2M, LT-68131 Marijampolė</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>54.426129</v>
+        <v>54.5356806</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>24.016482</v>
+        <v>23.3349754</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Oficialaus kontaktų puslapio žemėlapio taškas</t>
+          <t>Oficialios Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Alytaus gelžbetonis kontaktų puslapis</t>
+          <t>Gernora kontaktų puslapis</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
+          <t>https://gernora.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Alytaus gelžbetonio gamykla</t>
+          <t>Gernora betono mazgas</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -4559,30 +4559,30 @@
       <c r="S35" s="4" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Viešai skelbiamas betono mišinių tiekėjas Marijampolėje.</t>
         </is>
       </c>
       <c r="U35" s="5" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/</t>
+          <t>https://gernora.lt/</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
+          <t>https://gernora.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>https://alytausgelzbetonis.lt/kontaktai/</t>
+          <t>https://gernora.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>Patikslinta pagal oficialų kontaktų puslapį.</t>
+          <t>Koordinatės patikslintos pagal oficialaus Gernora kontaktų puslapio Google Maps nuorodą.</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4594,18 +4594,18 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>gernora-marijampole</t>
+          <t>re-betono-konstrukcijos-kretinga</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>UAB Gernora</t>
+          <t>UAB RE Betono konstrukcijos</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Gernora</t>
+          <t>RE Betono konstrukcijos</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4615,53 +4615,53 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Kretinga</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Kretingos r. sav.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Vingio g. 2M, LT-68131 Marijampolė</t>
+          <t>Tiekėjų g. 27B, Kretinga</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>54.5356806</v>
+        <v>55.87963</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>23.3349754</v>
+        <v>21.220888</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Oficialios Google Maps nuorodos taškas</t>
+          <t>Tikslus adreso taškas</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Gernora kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Gernora betono mazgas</t>
+          <t>RE Betono konstrukcijų gamyba</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -4669,30 +4669,26 @@
       <c r="S36" s="4" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas betono mišinių tiekėjas Marijampolėje.</t>
+          <t>Viešame kataloge nurodomi betonas, cemento gaminiai, betono siurblys ir pamatų blokai Kretingoje.</t>
         </is>
       </c>
       <c r="U36" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>https://gernora.lt/</t>
-        </is>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr"/>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/kontaktai/</t>
+          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>https://gernora.lt/kontaktai/</t>
+          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>Koordinatės patikslintos pagal oficialaus Gernora kontaktų puslapio Google Maps nuorodą.</t>
+          <t>Katalogo šaltinis, reikia patikslinti gamybos apimtį.</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4704,18 +4700,18 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>re-betono-konstrukcijos-kretinga</t>
+          <t>silales-statyba-vingininkai</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>UAB RE Betono konstrukcijos</t>
+          <t>UAB Šilalės statyba</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>RE Betono konstrukcijos</t>
+          <t>Šilalės statyba</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4725,24 +4721,24 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Kretinga</t>
+          <t>Vingininkai</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Kretingos r. sav.</t>
+          <t>Šilalės r. sav.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Tiekėjų g. 27B, Kretinga</t>
+          <t>Lauryno Ivinskio g. 7, Vingininkai, Šilalės r.</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>55.87963</v>
+        <v>55.4808479</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>21.220888</v>
+        <v>22.1937399</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4771,7 +4767,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>RE Betono konstrukcijų gamyba</t>
+          <t>Šilalės statybos betono gaminių gamyba</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -4779,26 +4775,30 @@
       <c r="S37" s="4" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, cemento gaminiai, betono siurblys ir pamatų blokai Kretingoje.</t>
+          <t>Viešai skelbiama betono gaminių ir statybinių konstrukcijų veikla Šilalės rajone.</t>
         </is>
       </c>
       <c r="U37" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr"/>
+        <v>0.72</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.silalesstatyba.lt/</t>
+        </is>
+      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
+          <t>https://www.silalesstatyba.lt/</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
+          <t>https://www.silalesstatyba.lt/</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>Katalogo šaltinis, reikia patikslinti gamybos apimtį.</t>
+          <t>Reikia patikslinti tikslų gaminių asortimentą.</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4810,18 +4810,18 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>silales-statyba-vingininkai</t>
+          <t>panevezio-gelzbetonis-panevezys</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilalės statyba</t>
+          <t>UAB Panevėžio gelžbetonis</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Šilalės statyba</t>
+          <t>Panevėžio gelžbetonis</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4831,24 +4831,24 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Vingininkai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Šilalės r. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Lauryno Ivinskio g. 7, Vingininkai, Šilalės r.</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>55.4808479</v>
+        <v>55.7409491</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>22.1937399</v>
+        <v>24.3803541</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Šilalės statybos betono gaminių gamyba</t>
+          <t>Panevėžio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -4885,30 +4885,26 @@
       <c r="S38" s="4" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių ir statybinių konstrukcijų veikla Šilalės rajone.</t>
+          <t>Viešame įmonių kataloge nurodomas gelžbetonio gaminių profilis Panevėžyje.</t>
         </is>
       </c>
       <c r="U38" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.silalesstatyba.lt/</t>
-        </is>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr"/>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>https://www.silalesstatyba.lt/</t>
+          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>https://www.silalesstatyba.lt/</t>
+          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti tikslų gaminių asortimentą.</t>
+          <t>Reikia patikrinti veiklos aktyvumą ir produkcijos apimtį.</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4920,18 +4916,18 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>panevezio-gelzbetonis-panevezys</t>
+          <t>pamatas-telsiai</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>UAB Panevėžio gelžbetonis</t>
+          <t>UAB Pamatas</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio gelžbetonis</t>
+          <t>Pamatas</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4941,24 +4937,24 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Tryškių g. 46, Dimaičių k., Telšių r.</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.9874536</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>24.3803541</v>
+        <v>22.287162</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4982,12 +4978,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio gelžbetonio gamykla</t>
+          <t>Pamatas betono gaminių gamyba</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -4995,26 +4991,30 @@
       <c r="S39" s="4" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>Viešame įmonių kataloge nurodomas gelžbetonio gaminių profilis Panevėžyje.</t>
+          <t>Viešai skelbiami pamatų ir kiti betono gaminiai Telšių rajone.</t>
         </is>
       </c>
       <c r="U39" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V39" s="2" t="inlineStr"/>
+        <v>0.72</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>https://pamatas.lt/</t>
+        </is>
+      </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikrinti veiklos aktyvumą ir produkcijos apimtį.</t>
+          <t>Adresas patikslintas pagal lietuvišką įmonės puslapį; koordinatės nustatytos Lietuvos geolokatoriumi.</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5026,18 +5026,18 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>pamatas-telsiai</t>
+          <t>vilniaus-betono-gaminiai-vilnius</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>UAB Pamatas</t>
+          <t>UAB Vilniaus betono gaminiai</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Pamatas</t>
+          <t>HAUS / Vilniaus betono gaminiai</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5047,24 +5047,24 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Tryškių g. 46, Dimaičių k., Telšių r.</t>
+          <t>A. Jakšto g. 5, Vilnius</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>55.9874536</v>
+        <v>54.6888177</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>22.287162</v>
+        <v>25.2756813</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Pamatas betono gaminių gamyba</t>
+          <t>Vilniaus betono gaminiai</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -5101,30 +5101,30 @@
       <c r="S40" s="4" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiami pamatų ir kiti betono gaminiai Telšių rajone.</t>
+          <t>Viešai skelbiamas HAUS blokelių ir betono gaminių gamintojas.</t>
         </is>
       </c>
       <c r="U40" s="5" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://www.vbg.lt/</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://www.vbg.lt/</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://www.vbg.lt/</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>Adresas patikslintas pagal lietuvišką įmonės puslapį; koordinatės nustatytos Lietuvos geolokatoriumi.</t>
+          <t>Žemėlapyje naudotas viešai skelbiamas įmonės adresas; gamybos vietą reikia patikslinti.</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5136,18 +5136,18 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>vilniaus-betono-gaminiai-vilnius</t>
+          <t>pamario-grupe-kalnuvenai</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>UAB Vilniaus betono gaminiai</t>
+          <t>UAB Pamario grupė</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>HAUS / Vilniaus betono gaminiai</t>
+          <t>Pamario grupė</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5157,24 +5157,24 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Kalnuvėnai</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>A. Jakšto g. 5, Vilnius</t>
+          <t>Kaukėnų g. 12, Kalnuvėnai, Klaipėdos r.</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>54.6888177</v>
+        <v>55.7905468</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>25.2756813</v>
+        <v>21.1471136</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -5193,17 +5193,17 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus betono gaminiai</t>
+          <t>Pamario grupės betono mazgas</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -5211,30 +5211,30 @@
       <c r="S41" s="4" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas HAUS blokelių ir betono gaminių gamintojas.</t>
+          <t>Viešai skelbiama betono mišinių veikla Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U41" s="5" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>Žemėlapyje naudotas viešai skelbiamas įmonės adresas; gamybos vietą reikia patikslinti.</t>
+          <t>Reikia patikslinti našumą ir gamybos režimą.</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5246,18 +5246,18 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>pamario-grupe-kalnuvenai</t>
+          <t>betono-zona-klaipeda</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>UAB Pamario grupė</t>
+          <t>UAB Betono zona</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupė</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5267,24 +5267,24 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Kalnuvėnai</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Kaukėnų g. 12, Kalnuvėnai, Klaipėdos r.</t>
+          <t>Dvaro g. 6, Klaipėda</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>55.7905468</v>
+        <v>55.7549809</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>21.1471136</v>
+        <v>21.150509</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupės betono mazgas</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -5321,30 +5321,30 @@
       <c r="S42" s="4" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Klaipėdos rajone.</t>
+          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
         </is>
       </c>
       <c r="U42" s="5" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą ir gamybos režimą.</t>
+          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5356,18 +5356,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>betono-zona-klaipeda</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr"/>
+          <t>topbeton-panevezys</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>307083610</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono zona</t>
+          <t>UAB Topbeton</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Topbeton</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5377,24 +5381,24 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g. 6, Klaipėda</t>
+          <t>Beržų g. 5C, Panevėžys</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>55.7549809</v>
+        <v>55.7168572</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>21.150509</v>
+        <v>24.3617863</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -5413,17 +5417,17 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Topbeton betono mazgas</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -5431,30 +5435,30 @@
       <c r="S43" s="4" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
+          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U43" s="5" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://topbeton.lt/</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5466,22 +5470,18 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>topbeton-panevezys</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>307083610</t>
-        </is>
-      </c>
+          <t>gelzbetonio-gamyba-panevezys</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>UAB Topbeton</t>
+          <t>MB Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Topbeton</t>
+          <t>Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Beržų g. 5C, Panevėžys</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>55.7168572</v>
+        <v>55.7409491</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>24.3617863</v>
+        <v>24.3803541</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -5527,17 +5527,17 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Topbeton betono mazgas</t>
+          <t>Gelžbetonio gamyba Panevėžyje</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -5545,30 +5545,30 @@
       <c r="S44" s="4" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U44" s="5" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>https://topbeton.lt/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
+          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5580,18 +5580,18 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>gelzbetonio-gamyba-panevezys</t>
+          <t>inroma-pakruojis</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>MB Gelžbetonio gamyba</t>
+          <t>UAB Inroma</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba</t>
+          <t>Inroma</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5601,24 +5601,24 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Pakruojis</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Pakruojo r. sav.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Pramonės g. 5B, Pakruojis</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.9763263</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>24.3803541</v>
+        <v>23.8584712</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -5637,17 +5637,17 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba Panevėžyje</t>
+          <t>Inroma betono mazgas</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -5655,7 +5655,7 @@
       <c r="S45" s="4" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
         </is>
       </c>
       <c r="U45" s="5" t="n">
@@ -5663,22 +5663,22 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
+          <t>Reikia patikslinti našumą.</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5690,18 +5690,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>inroma-pakruojis</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr"/>
+          <t>utenos-betonas-utena</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>300904691</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>UAB Inroma</t>
+          <t>UAB Utenos betonas</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Inroma</t>
+          <t>Utenos betonas</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5711,24 +5715,24 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Pakruojis</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Pakruojo r. sav.</t>
+          <t>Utenos r. sav.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Pramonės g. 5B, Pakruojis</t>
+          <t>Metalo g. 9B, Utena</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>55.9763263</v>
+        <v>55.4947607</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>23.8584712</v>
+        <v>25.6225075</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5757,7 +5761,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Inroma betono mazgas</t>
+          <t>Utenos betono mazgas</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -5765,30 +5769,30 @@
       <c r="S46" s="4" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
         </is>
       </c>
       <c r="U46" s="5" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://utenosbetonas.lt/</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5800,22 +5804,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>utenos-betonas-utena</t>
+          <t>sbetonas-jonava</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>300904691</t>
+          <t>300902683</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>UAB Utenos betonas</t>
+          <t>UAB Sbetonas</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Utenos betonas</t>
+          <t>Sbetonas</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5825,24 +5829,24 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Jonava</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Utenos r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Metalo g. 9B, Utena</t>
+          <t>Skarulių g. 58, Jonava</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>55.4947607</v>
+        <v>55.0786452</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>25.6225075</v>
+        <v>24.3199072</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5871,7 +5875,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Utenos betono mazgas</t>
+          <t>Sbetonas betono mazgas</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -5879,7 +5883,7 @@
       <c r="S47" s="4" t="inlineStr"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
+          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
         </is>
       </c>
       <c r="U47" s="5" t="n">
@@ -5887,22 +5891,22 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>https://utenosbetonas.lt/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
+          <t>Papildomai rasta pagal prekinio betono požymį.</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -5914,22 +5918,18 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>sbetonas-jonava</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>300902683</t>
-        </is>
-      </c>
+          <t>kalcitas-naujoji-akmene</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>UAB Sbetonas</t>
+          <t>AB Kalcitas</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas</t>
+          <t>Kalcitas</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5939,24 +5939,24 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Jonava</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Skarulių g. 58, Jonava</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>55.0786452</v>
+        <v>56.3143832</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>24.3199072</v>
+        <v>22.9130704</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas betono mazgas</t>
+          <t>Kalcitas betono mišinių gamybos linija</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -5993,30 +5993,26 @@
       <c r="S48" s="4" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
+          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
         </is>
       </c>
       <c r="U48" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>https://sbetonas.lt/</t>
-        </is>
-      </c>
+      <c r="V48" s="2" t="inlineStr"/>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta pagal prekinio betono požymį.</t>
+          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6028,18 +6024,18 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>kalcitas-naujoji-akmene</t>
+          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>AB Kalcitas</t>
+          <t>UAB Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas</t>
+          <t>Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -6049,24 +6045,24 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Gelgaudiškis</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Šakių r. sav.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>56.3143832</v>
+        <v>55.07067</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>22.9130704</v>
+        <v>22.976723</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -6075,27 +6071,27 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>GLG kontaktų puslapis</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono mišiniai ir gelžbetonis</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas betono mišinių gamybos linija</t>
+          <t>Gelgaudiškio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -6103,26 +6099,30 @@
       <c r="S49" s="4" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
+          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
         </is>
       </c>
       <c r="U49" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>https://glg.lt/</t>
+        </is>
+      </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://glg.lt/betonas/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
+          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6134,45 +6134,49 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr"/>
+          <t>ginfa-kutiskiai</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>302680943</t>
+        </is>
+      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelgaudiškio gelžbetonis</t>
+          <t>UAB GinFa</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonis</t>
+          <t>GinFa</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta</t>
+          <t>Papildomai rasta EVRK 23.63</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškis</t>
+          <t>Kutiškiai</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Šakių r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
+          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>55.07067</v>
+        <v>55.8326273</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>22.976723</v>
+        <v>23.4995317</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -6181,27 +6185,27 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>GLG kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai ir gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonio gamykla</t>
+          <t>GinFa betono gamyba</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -6209,30 +6213,22 @@
       <c r="S50" s="4" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
+          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U50" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/</t>
-        </is>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr"/>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="X50" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/betonas/betono-misiniai/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr"/>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6244,22 +6240,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ginfa-kutiskiai</t>
+          <t>antano-gribino-imone-prienai</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>302680943</t>
+          <t>170687267</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>UAB GinFa</t>
+          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>GinFa</t>
+          <t>Antano Gribino įmonė</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6269,24 +6265,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Kutiškiai</t>
+          <t>Prienai</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Prienų r. sav.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
+          <t>Kęstučio g. 95A, Prienai</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>55.8326273</v>
+        <v>54.6523184</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>23.4995317</v>
+        <v>23.9696591</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -6315,7 +6311,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>GinFa betono gamyba</t>
+          <t>Antano Gribino įmonės betono gamyba</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -6350,22 +6346,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>antano-gribino-imone-prienai</t>
+          <t>vinido-taurage</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>170687267</t>
+          <t>306258220</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
+          <t>UAB Vinido</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonė</t>
+          <t>Vinido</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6375,24 +6371,24 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Prienai</t>
+          <t>Tauragė</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Prienų r. sav.</t>
+          <t>Tauragės r. sav.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Kęstučio g. 95A, Prienai</t>
+          <t>Gaurės g. 32, Tauragė</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>54.6523184</v>
+        <v>55.2492204</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>23.9696591</v>
+        <v>22.3185845</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6417,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonės betono gamyba</t>
+          <t>Vinido betono gamyba</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -6435,16 +6431,24 @@
       <c r="U52" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/</t>
+        </is>
+      </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X52" s="2" t="inlineStr"/>
+          <t>https://betonastaurageje.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/betonas/</t>
+        </is>
+      </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Oficiali Vinido svetainė patvirtina Gaurės g. 32 adresą, betono gamybą ir betono mazgą.</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6456,22 +6460,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>vinido-taurage</t>
+          <t>santvara-kedainiai</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>306258220</t>
+          <t>304915297</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>UAB Vinido</t>
+          <t>UAB Santvara</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Vinido</t>
+          <t>Santvara</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6481,24 +6485,24 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Tauragė</t>
+          <t>Kėdainiai</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Tauragės r. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Gaurės g. 32, Tauragė</t>
+          <t>Aruodų g. 34, Kėdainiai</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>55.2492204</v>
+        <v>55.2634747</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>22.3185845</v>
+        <v>23.9440384</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6531,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Vinido betono gamyba</t>
+          <t>Santvara betono gamyba</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -6543,22 +6547,22 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/kontaktai/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/betonas/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Vinido svetainė patvirtina Gaurės g. 32 adresą, betono gamybą ir betono mazgą.</t>
+          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6570,22 +6574,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>santvara-kedainiai</t>
+          <t>medis-ir-betonas-naujoji-akmene</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>304915297</t>
+          <t>153074073</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>UAB Santvara</t>
+          <t>AB Medis ir betonas</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Santvara</t>
+          <t>Medis ir betonas</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6595,24 +6599,24 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Kėdainiai</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Kėdainių r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Aruodų g. 34, Kėdainiai</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>55.2634747</v>
+        <v>56.3143832</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>23.9440384</v>
+        <v>22.9130704</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -6641,7 +6645,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Santvara betono gamyba</t>
+          <t>Medis ir betonas gamyba</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -6655,24 +6659,16 @@
       <c r="U54" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
+      <c r="V54" s="2" t="inlineStr"/>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
-      <c r="X54" s="2" t="inlineStr">
-        <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr"/>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6684,22 +6680,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>medis-ir-betonas-naujoji-akmene</t>
+          <t>ekobetonas-marijampole</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>153074073</t>
+          <t>300636364</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>AB Medis ir betonas</t>
+          <t>UAB Ekobetonas</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas</t>
+          <t>Ekobetonas</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6709,24 +6705,24 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Gamyklų g. 3, Marijampolė</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>56.3143832</v>
+        <v>54.5750142</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>22.9130704</v>
+        <v>23.3796805</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -6755,7 +6751,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas gamyba</t>
+          <t>Ekobetonas betono gamyba</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -6769,16 +6765,24 @@
       <c r="U55" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>https://ekobetonas.lt/</t>
+        </is>
+      </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X55" s="2" t="inlineStr"/>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+        </is>
+      </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6790,22 +6794,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ekobetonas-marijampole</t>
+          <t>rokbetonis-rokiskis</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>300636364</t>
+          <t>304184091</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UAB Ekobetonas</t>
+          <t>MB Rokbetonis</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas</t>
+          <t>Rokbetonis</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6815,24 +6819,24 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Rokiškis</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Rokiškio r. sav.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Gamyklų g. 3, Marijampolė</t>
+          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>54.5750142</v>
+        <v>55.9525796</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>23.3796805</v>
+        <v>25.5624197</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -6861,7 +6865,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas betono gamyba</t>
+          <t>Rokbetonis betono gamyba</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -6873,26 +6877,18 @@
         </is>
       </c>
       <c r="U56" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>https://ekobetonas.lt/</t>
-        </is>
-      </c>
+        <v>0.72</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr"/>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
-        </is>
-      </c>
-      <c r="X56" s="2" t="inlineStr">
-        <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr"/>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
+          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -6904,22 +6900,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>rokbetonis-rokiskis</t>
+          <t>beton-eura-dovainonys</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>304184091</t>
+          <t>302745280</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>MB Rokbetonis</t>
+          <t>UAB Beton Eura</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis</t>
+          <t>Beton Eura</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6929,24 +6925,24 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Rokiškis</t>
+          <t>Dovainonys</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Rokiškio r. sav.</t>
+          <t>Kaišiadorių r. sav.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
+          <t>Žilvičių g. 2, Dovainonys, Kaišiadorių r.</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>55.9525796</v>
+        <v>54.8395918</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>25.5624197</v>
+        <v>24.2360193</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6975,7 +6971,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis betono gamyba</t>
+          <t>Beton Eura betono gamyba</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -6987,18 +6983,26 @@
         </is>
       </c>
       <c r="U57" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr"/>
+        <v>0.82</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.betoneura.lt/</t>
+        </is>
+      </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X57" s="2" t="inlineStr"/>
+          <t>https://www.betoneura.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.betoneura.lt/kontaktai/</t>
+        </is>
+      </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
+          <t>Oficialus Beton Eura kontaktų puslapis patvirtina Žilvičių g. 2 adresą ir rekvizitus.</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7010,22 +7014,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>beton-eura-dovainonys</t>
+          <t>silutes-betonas-silute</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>302745280</t>
+          <t>177392928</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>UAB Beton Eura</t>
+          <t>UAB Šilutės betonas</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Beton Eura</t>
+          <t>Šilutės betonas</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -7035,24 +7039,24 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Dovainonys</t>
+          <t>Šilutė</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Kaišiadorių r. sav.</t>
+          <t>Šilutės r. sav.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Žilvičių g. 2, Dovainonys, Kaišiadorių r.</t>
+          <t>Ramučių g. 1, Šilutė</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>54.8395918</v>
+        <v>55.3538641</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>24.2360193</v>
+        <v>21.4796635</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -7081,7 +7085,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Beton Eura betono gamyba</t>
+          <t>Šilutės betono gamyba</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -7095,24 +7099,20 @@
       <c r="U58" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.betoneura.lt/</t>
-        </is>
-      </c>
+      <c r="V58" s="2" t="inlineStr"/>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>https://www.betoneura.lt/kontaktai/</t>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>https://www.betoneura.lt/kontaktai/</t>
+          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Beton Eura kontaktų puslapis patvirtina Žilvičių g. 2 adresą ir rekvizitus.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7124,22 +7124,22 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>silutes-betonas-silute</t>
+          <t>kruszbet-lithuania-jure</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>177392928</t>
+          <t>305173596</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilutės betonas</t>
+          <t>UAB KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betonas</t>
+          <t>KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -7149,24 +7149,24 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Šilutė</t>
+          <t>Jūrė</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Šilutės r. sav.</t>
+          <t>Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Ramučių g. 1, Šilutė</t>
+          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>55.3538641</v>
+        <v>54.7706307</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>21.4796635</v>
+        <v>23.4998409</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betono gamyba</t>
+          <t>KRUSZBET Lithuania betono gamyba</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -7215,11 +7215,7 @@
           <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
         </is>
       </c>
-      <c r="X59" s="2" t="inlineStr">
-        <is>
-          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
-        </is>
-      </c>
+      <c r="X59" s="2" t="inlineStr"/>
       <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
@@ -7234,49 +7230,49 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>kruszbet-lithuania-jure</t>
+          <t>telsiu-keliai-telsiai</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>305173596</t>
+          <t>180200843</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>UAB KRUSZBET Lithuania</t>
+          <t>UAB Telšių keliai</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania</t>
+          <t>Telšių keliai</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Jūrė</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Kazlų Rūdos sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
+          <t>Mažeikių g. 18, Telšiai</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>54.7706307</v>
+        <v>56.0004158</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>23.4998409</v>
+        <v>22.2581129</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -7305,57 +7301,67 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania betono gamyba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
       <c r="R60" s="2" t="inlineStr"/>
-      <c r="S60" s="4" t="inlineStr"/>
+      <c r="S60" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
         </is>
       </c>
       <c r="U60" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr"/>
+        <v>0.86</v>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/</t>
+        </is>
+      </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X60" s="2" t="inlineStr"/>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+        </is>
+      </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>telsiu-keliai-telsiai</t>
+          <t>vpa-laistai</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>180200843</t>
+          <t>110185819</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>UAB Telšių keliai</t>
+          <t>UAB V. Paulius &amp; Associates</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Telšių keliai</t>
+          <t>VPA</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7365,38 +7371,38 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Laistai</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių g. 18, Telšiai</t>
+          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>56.0004158</v>
+        <v>55.636908</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>22.2581129</v>
+        <v>21.209254</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7411,108 +7417,116 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr"/>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
       <c r="S61" s="4" t="n">
         <v>2</v>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
+          <t>VPA betono mazgas Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U61" s="5" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/</t>
+          <t>https://www.vpa.lt/</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://www.vpa.lt/?Kontaktai=</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
+          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>vpa-laistai</t>
+          <t>c3-beton-baisogala</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>110185819</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>UAB V. Paulius &amp; Associates</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>VPA</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Laistai</t>
+          <t>Baisogala</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
+          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>55.636908</v>
+        <v>55.6372</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>21.209254</v>
+        <v>23.7183</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Google Maps nuoroda</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7527,60 +7541,62 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Liebherr</t>
+          <t>Baisiogala Plant</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>3 m³</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S62" s="4" t="n">
-        <v>2</v>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>VPA betono mazgas Klaipėdos rajone.</t>
+          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
         </is>
       </c>
       <c r="U62" s="5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/</t>
+          <t>https://c3beton.com/</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/?Kontaktai=</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-baisogala</t>
+          <t>c3-beton-martiniskis</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -7605,24 +7621,24 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Baisogala</t>
+          <t>Martiniškis</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
+          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>55.6372</v>
+        <v>55.1441659</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>23.7183</v>
+        <v>24.1869636</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -7651,27 +7667,27 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Baisiogala Plant</t>
+          <t>Martiniškis Plant</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>Ammann Elba Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>60–80 m³/val.</t>
         </is>
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>2x85 t</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
+          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U63" s="5" t="n">
@@ -7694,7 +7710,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7706,7 +7722,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-martiniskis</t>
+          <t>c3-beton-stasenai</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7731,38 +7747,38 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
+          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>55.1441659</v>
+        <v>54.6493094</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>24.1869636</v>
+        <v>25.3107972</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus adreso taškas pagal geokodavimą</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7777,12 +7793,12 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis Plant</t>
+          <t>Vilnius Ušos g. Plant</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
+          <t>Nissbau Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -7797,7 +7813,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U64" s="5" t="n">
@@ -7820,7 +7836,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -7832,7 +7848,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-stasenai</t>
+          <t>c3-beton-runeikiai</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -7857,38 +7873,38 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Runeikiai</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
+          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>54.6493094</v>
+        <v>55.3327393</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>25.3107972</v>
+        <v>24.3501308</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas pagal geokodavimą</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7903,12 +7919,12 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Vilnius Ušos g. Plant</t>
+          <t>Runeikiai Plant</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Nissbau Euromix C120, 3 m³</t>
+          <t>Ammann Elba Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -7923,7 +7939,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U65" s="5" t="n">
@@ -7946,7 +7962,7 @@
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -7958,22 +7974,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-runeikiai</t>
+          <t>reljef-rukla</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>301731961</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>UAB Reljef</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>Reljef</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -7983,38 +7999,38 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Runeikiai</t>
+          <t>Rukla</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Kėdainių r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
+          <t>Rukla, Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>55.3327393</v>
+        <v>55.05225</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>24.3501308</v>
+        <v>24.4064167</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>Naudotojo pateiktos koordinatės</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8029,77 +8045,77 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Runeikiai Plant</t>
+          <t>Ammann Elba</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
+          <t>Nenustatyta</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>60–80 m³/val.</t>
+          <t>Nenustatytas</t>
         </is>
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2x85 t</t>
+          <t>2x65 t</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
         </is>
       </c>
       <c r="U66" s="5" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>reljef-rukla</t>
+          <t>ponas-betonas-paraudondvariai</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>301731961</t>
+          <t>306676006</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>UAB Reljef</t>
+          <t>UAB Ponas betonas</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Reljef</t>
+          <t>Ponas betonas</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8109,38 +8125,38 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Rukla</t>
+          <t>Paraudondvariai</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Rukla, Jonavos r. sav.</t>
+          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
-        <v>55.05225</v>
+        <v>54.8321418</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>24.4064167</v>
+        <v>25.2755596</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos koordinatės</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8155,186 +8171,60 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Nenustatyta</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>Nenustatytas</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2x65 t</t>
+          <t>2 matomi oficialioje nuotraukoje</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
+          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
         </is>
       </c>
       <c r="U67" s="5" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.ponasbetonas.lt/#Apiemus</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
+          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>ponas-betonas-paraudondvariai</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>306676006</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>UAB Ponas betonas</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Ponas betonas</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Paraudondvariai</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Vilniaus r. sav.</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>54.8321418</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>25.2755596</v>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
-      <c r="S68" s="4" t="inlineStr">
-        <is>
-          <t>2 matomi oficialioje nuotraukoje</t>
-        </is>
-      </c>
-      <c r="T68" s="2" t="inlineStr">
-        <is>
-          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
-        </is>
-      </c>
-      <c r="U68" s="5" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="V68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ponasbetonas.lt/</t>
-        </is>
-      </c>
-      <c r="W68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ponasbetonas.lt/#Apiemus</t>
-        </is>
-      </c>
-      <c r="X68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ponasbetonas.lt/</t>
-        </is>
-      </c>
-      <c r="Y68" s="2" t="inlineStr">
-        <is>
-          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
-        </is>
-      </c>
-      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z68"/>
+  <autoFilter ref="A1:Z67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8423,7 +8313,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T09:09:43.196745+00:00</t>
+          <t>2026-09-23T09:23:09.140754+00:00</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8368,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T09:09:43.197882+00:00</t>
+          <t>2026-09-23T09:23:09.140754+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8492,7 +8382,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z67" headerRowCount="1">
-  <autoFilter ref="A1:Z67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z68" headerRowCount="1">
+  <autoFilter ref="A1:Z68"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Įrašo ID"/>
     <tableColumn id="2" name="Įmonės kodas"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z67"/>
+  <dimension ref="A1:Z68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -8223,8 +8223,134 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>pabrades-betonas-pabrade</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>306177188</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>UAB Pabradės betonas</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Pabradės betonas</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Konkurentas</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Pabradė</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Švenčionių r. sav.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus g. 161, Pabradė, LT-18177 Švenčionių r.</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>54.9758768</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>25.7373849</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Tikslus oficialioje svetainėje pateiktos Google Maps nuorodos taškas</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Oficiali Pabradės betono Google Maps nuoroda</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/TQBCVR8DczDRvQaeA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr (tikėtina)</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/val.</t>
+        </is>
+      </c>
+      <c r="S68" s="4" t="inlineStr">
+        <is>
+          <t>3x65 t</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>UAB Pabradės betonas Vilniaus g. 161, Pabradėje, gamina sertifikuotą normalųjį betoną ir oficialiai nurodo dirbanti 50 km spinduliu aplink Pabradę. Oficialios galerijos nuotraukose matoma stacionari gamybos bazė su trimis cemento silosais. Mazgo gamintojas tikėtinai Liebherr pagal oficialiose nuotraukose matomą Liebherr įrangą ir gamyklos konstrukcijos vizualinius požymius; gamintojo lentelė viešai neparodyta.</t>
+        </is>
+      </c>
+      <c r="U68" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pabradesbetonas.lt/</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pabradesbetonas.lt/</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pabradesbetonas.lt/galerija/</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>Adresas, įmonės kodas ir betono gamyba patvirtinti oficialioje svetainėje bei viešame gamybos kontrolės sertifikate. Koordinatės paimtos iš oficialioje svetainėje pateiktos Google Maps nuorodos. Maišyklės tūris 3 m³, realus našumas 60 m³/val. ir silosai 3x65 t įrašyti pagal naudotojo pateiktą informaciją. Gamintojas Liebherr nurodytas kaip tikėtinas pagal oficialios galerijos nuotraukas; viešo gamintojo ženklinimo ant paties mazgo nerasta.</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z67"/>
+  <autoFilter ref="A1:Z68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8313,7 +8439,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T09:23:09.140754+00:00</t>
+          <t>2026-09-23T09:44:17.027476+00:00</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T09:23:09.140754+00:00</t>
+          <t>2026-09-23T09:44:17.028490+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8382,7 +8508,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -2047,19 +2047,31 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus betono gamykla, Sandėlių g.</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
+          <t>Wiggert</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Wiggertmixer MO80</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>30 m³/val.</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>3x75 t</t>
+        </is>
+      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas Heidelberg Materials betono gamyklų tinklo taškas Vilniuje.</t>
+          <t>Sandėlių g. 16 veikiantis mobilus Wiggert betono mazgas su Wiggertmixer MO80 priverstinio maišymo maišykle. Oficialus PAV dokumentas nurodo 30 m³/val. našumą, tris po 75 t cemento silosus ir iki 20 000 m³ metinę gamybą.</t>
         </is>
       </c>
       <c r="U13" s="5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
@@ -2073,17 +2085,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>https://www.betonas.heidelbergmaterials.lt/lt/kontaktine-informacija-0</t>
+          <t>https://old.gamta.lt/files/PAV%20atranka_0905.docx</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Heidelberg Materials Lietuva Betonas kontaktų puslapis patvirtina betono užsakymų padalinius Lietuvoje.</t>
+          <t>Padalinio adresas patvirtintas oficialiame Heidelberg Materials kontaktų puslapyje. Gamintojas, maišyklės modelis, našumas ir silosų talpa paimti iš oficialaus 2016 m. Aplinkos apsaugos agentūros PAV dokumento Sandėlių g. 16 mazgui. Naudotojo pateikta nuotrauka atitinka dokumente aprašytą mobilų mazgą.</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8451,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T09:44:17.027476+00:00</t>
+          <t>2026-09-23T15:17:04.691715+00:00</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T09:44:17.028490+00:00</t>
+          <t>2026-09-23T15:17:04.691715+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z68" headerRowCount="1">
-  <autoFilter ref="A1:Z68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z67" headerRowCount="1">
+  <autoFilter ref="A1:Z67"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Įrašo ID"/>
     <tableColumn id="2" name="Įmonės kodas"/>
@@ -492,13 +492,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z68"/>
+  <dimension ref="A1:Z67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -5038,18 +5038,18 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>vilniaus-betono-gaminiai-vilnius</t>
+          <t>pamario-grupe-kalnuvenai</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>UAB Vilniaus betono gaminiai</t>
+          <t>UAB Pamario grupė</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>HAUS / Vilniaus betono gaminiai</t>
+          <t>Pamario grupė</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5059,24 +5059,24 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Kalnuvėnai</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>A. Jakšto g. 5, Vilnius</t>
+          <t>Kaukėnų g. 12, Kalnuvėnai, Klaipėdos r.</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>54.6888177</v>
+        <v>55.7905468</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>25.2756813</v>
+        <v>21.1471136</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -5095,17 +5095,17 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus betono gaminiai</t>
+          <t>Pamario grupės betono mazgas</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -5113,30 +5113,30 @@
       <c r="S40" s="4" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas HAUS blokelių ir betono gaminių gamintojas.</t>
+          <t>Viešai skelbiama betono mišinių veikla Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U40" s="5" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>https://www.vbg.lt/</t>
+          <t>https://pamariogrupe.lt/</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>Žemėlapyje naudotas viešai skelbiamas įmonės adresas; gamybos vietą reikia patikslinti.</t>
+          <t>Reikia patikslinti našumą ir gamybos režimą.</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5148,18 +5148,18 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>pamario-grupe-kalnuvenai</t>
+          <t>betono-zona-klaipeda</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>UAB Pamario grupė</t>
+          <t>UAB Betono zona</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupė</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5169,24 +5169,24 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Kalnuvėnai</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Kaukėnų g. 12, Kalnuvėnai, Klaipėdos r.</t>
+          <t>Dvaro g. 6, Klaipėda</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>55.7905468</v>
+        <v>55.7549809</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>21.1471136</v>
+        <v>21.150509</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -5205,17 +5205,17 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupės betono mazgas</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -5223,30 +5223,30 @@
       <c r="S41" s="4" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Klaipėdos rajone.</t>
+          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
         </is>
       </c>
       <c r="U41" s="5" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą ir gamybos režimą.</t>
+          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5258,18 +5258,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>betono-zona-klaipeda</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr"/>
+          <t>topbeton-panevezys</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>307083610</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono zona</t>
+          <t>UAB Topbeton</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Topbeton</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5279,24 +5283,24 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g. 6, Klaipėda</t>
+          <t>Beržų g. 5C, Panevėžys</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>55.7549809</v>
+        <v>55.7168572</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>21.150509</v>
+        <v>24.3617863</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -5315,17 +5319,17 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Topbeton betono mazgas</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -5333,30 +5337,30 @@
       <c r="S42" s="4" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
+          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U42" s="5" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://topbeton.lt/</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5368,22 +5372,18 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>topbeton-panevezys</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>307083610</t>
-        </is>
-      </c>
+          <t>gelzbetonio-gamyba-panevezys</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>UAB Topbeton</t>
+          <t>MB Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Topbeton</t>
+          <t>Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5403,14 +5403,14 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Beržų g. 5C, Panevėžys</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>55.7168572</v>
+        <v>55.7409491</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>24.3617863</v>
+        <v>24.3803541</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -5429,17 +5429,17 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Topbeton betono mazgas</t>
+          <t>Gelžbetonio gamyba Panevėžyje</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -5447,30 +5447,30 @@
       <c r="S43" s="4" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U43" s="5" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>https://topbeton.lt/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
+          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5482,18 +5482,18 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>gelzbetonio-gamyba-panevezys</t>
+          <t>inroma-pakruojis</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>MB Gelžbetonio gamyba</t>
+          <t>UAB Inroma</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba</t>
+          <t>Inroma</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5503,24 +5503,24 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Pakruojis</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Pakruojo r. sav.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Pramonės g. 5B, Pakruojis</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.9763263</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>24.3803541</v>
+        <v>23.8584712</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -5539,17 +5539,17 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba Panevėžyje</t>
+          <t>Inroma betono mazgas</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -5557,7 +5557,7 @@
       <c r="S44" s="4" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
         </is>
       </c>
       <c r="U44" s="5" t="n">
@@ -5565,22 +5565,22 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
+          <t>Reikia patikslinti našumą.</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5592,18 +5592,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>inroma-pakruojis</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr"/>
+          <t>utenos-betonas-utena</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>300904691</t>
+        </is>
+      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>UAB Inroma</t>
+          <t>UAB Utenos betonas</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Inroma</t>
+          <t>Utenos betonas</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5613,24 +5617,24 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Pakruojis</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Pakruojo r. sav.</t>
+          <t>Utenos r. sav.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Pramonės g. 5B, Pakruojis</t>
+          <t>Metalo g. 9B, Utena</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>55.9763263</v>
+        <v>55.4947607</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>23.8584712</v>
+        <v>25.6225075</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -5659,7 +5663,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Inroma betono mazgas</t>
+          <t>Utenos betono mazgas</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -5667,30 +5671,30 @@
       <c r="S45" s="4" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
         </is>
       </c>
       <c r="U45" s="5" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://utenosbetonas.lt/</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5702,22 +5706,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>utenos-betonas-utena</t>
+          <t>sbetonas-jonava</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>300904691</t>
+          <t>300902683</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>UAB Utenos betonas</t>
+          <t>UAB Sbetonas</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Utenos betonas</t>
+          <t>Sbetonas</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5727,24 +5731,24 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Jonava</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Utenos r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Metalo g. 9B, Utena</t>
+          <t>Skarulių g. 58, Jonava</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>55.4947607</v>
+        <v>55.0786452</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>25.6225075</v>
+        <v>24.3199072</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5773,7 +5777,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Utenos betono mazgas</t>
+          <t>Sbetonas betono mazgas</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -5781,7 +5785,7 @@
       <c r="S46" s="4" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
+          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
         </is>
       </c>
       <c r="U46" s="5" t="n">
@@ -5789,22 +5793,22 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>https://utenosbetonas.lt/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
+          <t>Papildomai rasta pagal prekinio betono požymį.</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5816,22 +5820,18 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>sbetonas-jonava</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>300902683</t>
-        </is>
-      </c>
+          <t>kalcitas-naujoji-akmene</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>UAB Sbetonas</t>
+          <t>AB Kalcitas</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas</t>
+          <t>Kalcitas</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5841,24 +5841,24 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Jonava</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Skarulių g. 58, Jonava</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>55.0786452</v>
+        <v>56.3143832</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>24.3199072</v>
+        <v>22.9130704</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas betono mazgas</t>
+          <t>Kalcitas betono mišinių gamybos linija</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -5895,30 +5895,26 @@
       <c r="S47" s="4" t="inlineStr"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
+          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
         </is>
       </c>
       <c r="U47" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="V47" s="2" t="inlineStr">
-        <is>
-          <t>https://sbetonas.lt/</t>
-        </is>
-      </c>
+      <c r="V47" s="2" t="inlineStr"/>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta pagal prekinio betono požymį.</t>
+          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -5930,18 +5926,18 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>kalcitas-naujoji-akmene</t>
+          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>AB Kalcitas</t>
+          <t>UAB Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas</t>
+          <t>Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5951,24 +5947,24 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Gelgaudiškis</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Šakių r. sav.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>56.3143832</v>
+        <v>55.07067</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>22.9130704</v>
+        <v>22.976723</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5977,27 +5973,27 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>GLG kontaktų puslapis</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono mišiniai ir gelžbetonis</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas betono mišinių gamybos linija</t>
+          <t>Gelgaudiškio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -6005,26 +6001,30 @@
       <c r="S48" s="4" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
+          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
         </is>
       </c>
       <c r="U48" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>https://glg.lt/</t>
+        </is>
+      </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://glg.lt/betonas/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
+          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6036,45 +6036,49 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr"/>
+          <t>ginfa-kutiskiai</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>302680943</t>
+        </is>
+      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelgaudiškio gelžbetonis</t>
+          <t>UAB GinFa</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonis</t>
+          <t>GinFa</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta</t>
+          <t>Papildomai rasta EVRK 23.63</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškis</t>
+          <t>Kutiškiai</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Šakių r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
+          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>55.07067</v>
+        <v>55.8326273</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>22.976723</v>
+        <v>23.4995317</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -6083,27 +6087,27 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>GLG kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai ir gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonio gamykla</t>
+          <t>GinFa betono gamyba</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -6111,30 +6115,22 @@
       <c r="S49" s="4" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
+          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U49" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/</t>
-        </is>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr"/>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="X49" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/betonas/betono-misiniai/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr"/>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6146,22 +6142,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ginfa-kutiskiai</t>
+          <t>antano-gribino-imone-prienai</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>302680943</t>
+          <t>170687267</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>UAB GinFa</t>
+          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>GinFa</t>
+          <t>Antano Gribino įmonė</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -6171,24 +6167,24 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Kutiškiai</t>
+          <t>Prienai</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Prienų r. sav.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
+          <t>Kęstučio g. 95A, Prienai</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>55.8326273</v>
+        <v>54.6523184</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>23.4995317</v>
+        <v>23.9696591</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -6217,7 +6213,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>GinFa betono gamyba</t>
+          <t>Antano Gribino įmonės betono gamyba</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -6252,22 +6248,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>antano-gribino-imone-prienai</t>
+          <t>vinido-taurage</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>170687267</t>
+          <t>306258220</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
+          <t>UAB Vinido</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonė</t>
+          <t>Vinido</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6277,24 +6273,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Prienai</t>
+          <t>Tauragė</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Prienų r. sav.</t>
+          <t>Tauragės r. sav.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Kęstučio g. 95A, Prienai</t>
+          <t>Gaurės g. 32, Tauragė</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>54.6523184</v>
+        <v>55.2492204</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>23.9696591</v>
+        <v>22.3185845</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -6323,7 +6319,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonės betono gamyba</t>
+          <t>Vinido betono gamyba</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -6337,16 +6333,24 @@
       <c r="U51" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/</t>
+        </is>
+      </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X51" s="2" t="inlineStr"/>
+          <t>https://betonastaurageje.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/betonas/</t>
+        </is>
+      </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Oficiali Vinido svetainė patvirtina Gaurės g. 32 adresą, betono gamybą ir betono mazgą.</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6358,22 +6362,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>vinido-taurage</t>
+          <t>santvara-kedainiai</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>306258220</t>
+          <t>304915297</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>UAB Vinido</t>
+          <t>UAB Santvara</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Vinido</t>
+          <t>Santvara</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6383,24 +6387,24 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tauragė</t>
+          <t>Kėdainiai</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Tauragės r. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Gaurės g. 32, Tauragė</t>
+          <t>Aruodų g. 34, Kėdainiai</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>55.2492204</v>
+        <v>55.2634747</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>22.3185845</v>
+        <v>23.9440384</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -6429,7 +6433,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Vinido betono gamyba</t>
+          <t>Santvara betono gamyba</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -6445,22 +6449,22 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/kontaktai/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/betonas/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Vinido svetainė patvirtina Gaurės g. 32 adresą, betono gamybą ir betono mazgą.</t>
+          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6472,22 +6476,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>santvara-kedainiai</t>
+          <t>medis-ir-betonas-naujoji-akmene</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>304915297</t>
+          <t>153074073</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>UAB Santvara</t>
+          <t>AB Medis ir betonas</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Santvara</t>
+          <t>Medis ir betonas</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6497,24 +6501,24 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Kėdainiai</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Kėdainių r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Aruodų g. 34, Kėdainiai</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>55.2634747</v>
+        <v>56.3143832</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>23.9440384</v>
+        <v>22.9130704</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -6543,7 +6547,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Santvara betono gamyba</t>
+          <t>Medis ir betonas gamyba</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -6557,24 +6561,16 @@
       <c r="U53" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
+      <c r="V53" s="2" t="inlineStr"/>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
-      <c r="X53" s="2" t="inlineStr">
-        <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr"/>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6586,22 +6582,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>medis-ir-betonas-naujoji-akmene</t>
+          <t>ekobetonas-marijampole</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>153074073</t>
+          <t>300636364</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>AB Medis ir betonas</t>
+          <t>UAB Ekobetonas</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas</t>
+          <t>Ekobetonas</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6611,24 +6607,24 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Gamyklų g. 3, Marijampolė</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>56.3143832</v>
+        <v>54.5750142</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>22.9130704</v>
+        <v>23.3796805</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -6657,7 +6653,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas gamyba</t>
+          <t>Ekobetonas betono gamyba</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -6671,16 +6667,24 @@
       <c r="U54" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>https://ekobetonas.lt/</t>
+        </is>
+      </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X54" s="2" t="inlineStr"/>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+        </is>
+      </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6692,22 +6696,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ekobetonas-marijampole</t>
+          <t>rokbetonis-rokiskis</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>300636364</t>
+          <t>304184091</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>UAB Ekobetonas</t>
+          <t>MB Rokbetonis</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas</t>
+          <t>Rokbetonis</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6717,24 +6721,24 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Rokiškis</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Rokiškio r. sav.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Gamyklų g. 3, Marijampolė</t>
+          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>54.5750142</v>
+        <v>55.9525796</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>23.3796805</v>
+        <v>25.5624197</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -6763,7 +6767,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas betono gamyba</t>
+          <t>Rokbetonis betono gamyba</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -6775,26 +6779,18 @@
         </is>
       </c>
       <c r="U55" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>https://ekobetonas.lt/</t>
-        </is>
-      </c>
+        <v>0.72</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr"/>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
-        </is>
-      </c>
-      <c r="X55" s="2" t="inlineStr">
-        <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr"/>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
+          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6806,22 +6802,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>rokbetonis-rokiskis</t>
+          <t>beton-eura-dovainonys</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>304184091</t>
+          <t>302745280</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>MB Rokbetonis</t>
+          <t>UAB Beton Eura</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis</t>
+          <t>Beton Eura</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6831,24 +6827,24 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Rokiškis</t>
+          <t>Dovainonys</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Rokiškio r. sav.</t>
+          <t>Kaišiadorių r. sav.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
+          <t>Žilvičių g. 2, Dovainonys, Kaišiadorių r.</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>55.9525796</v>
+        <v>54.8395918</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>25.5624197</v>
+        <v>24.2360193</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -6877,7 +6873,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis betono gamyba</t>
+          <t>Beton Eura betono gamyba</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -6889,18 +6885,26 @@
         </is>
       </c>
       <c r="U56" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr"/>
+        <v>0.82</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.betoneura.lt/</t>
+        </is>
+      </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X56" s="2" t="inlineStr"/>
+          <t>https://www.betoneura.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.betoneura.lt/kontaktai/</t>
+        </is>
+      </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
+          <t>Oficialus Beton Eura kontaktų puslapis patvirtina Žilvičių g. 2 adresą ir rekvizitus.</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -6912,22 +6916,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>beton-eura-dovainonys</t>
+          <t>silutes-betonas-silute</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>302745280</t>
+          <t>177392928</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>UAB Beton Eura</t>
+          <t>UAB Šilutės betonas</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Beton Eura</t>
+          <t>Šilutės betonas</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6937,24 +6941,24 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Dovainonys</t>
+          <t>Šilutė</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Kaišiadorių r. sav.</t>
+          <t>Šilutės r. sav.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Žilvičių g. 2, Dovainonys, Kaišiadorių r.</t>
+          <t>Ramučių g. 1, Šilutė</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>54.8395918</v>
+        <v>55.3538641</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>24.2360193</v>
+        <v>21.4796635</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6983,7 +6987,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Beton Eura betono gamyba</t>
+          <t>Šilutės betono gamyba</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -6997,24 +7001,20 @@
       <c r="U57" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.betoneura.lt/</t>
-        </is>
-      </c>
+      <c r="V57" s="2" t="inlineStr"/>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>https://www.betoneura.lt/kontaktai/</t>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>https://www.betoneura.lt/kontaktai/</t>
+          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Beton Eura kontaktų puslapis patvirtina Žilvičių g. 2 adresą ir rekvizitus.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7026,22 +7026,22 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>silutes-betonas-silute</t>
+          <t>kruszbet-lithuania-jure</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>177392928</t>
+          <t>305173596</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilutės betonas</t>
+          <t>UAB KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betonas</t>
+          <t>KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -7051,24 +7051,24 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Šilutė</t>
+          <t>Jūrė</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Šilutės r. sav.</t>
+          <t>Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Ramučių g. 1, Šilutė</t>
+          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>55.3538641</v>
+        <v>54.7706307</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>21.4796635</v>
+        <v>23.4998409</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betono gamyba</t>
+          <t>KRUSZBET Lithuania betono gamyba</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -7117,11 +7117,7 @@
           <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
-        <is>
-          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
-        </is>
-      </c>
+      <c r="X58" s="2" t="inlineStr"/>
       <c r="Y58" s="2" t="inlineStr">
         <is>
           <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
@@ -7136,49 +7132,49 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>kruszbet-lithuania-jure</t>
+          <t>telsiu-keliai-telsiai</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>305173596</t>
+          <t>180200843</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>UAB KRUSZBET Lithuania</t>
+          <t>UAB Telšių keliai</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania</t>
+          <t>Telšių keliai</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Jūrė</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Kazlų Rūdos sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
+          <t>Mažeikių g. 18, Telšiai</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>54.7706307</v>
+        <v>56.0004158</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>23.4998409</v>
+        <v>22.2581129</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -7207,57 +7203,67 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania betono gamyba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
       <c r="R59" s="2" t="inlineStr"/>
-      <c r="S59" s="4" t="inlineStr"/>
+      <c r="S59" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
         </is>
       </c>
       <c r="U59" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V59" s="2" t="inlineStr"/>
+        <v>0.86</v>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/</t>
+        </is>
+      </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X59" s="2" t="inlineStr"/>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+        </is>
+      </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>telsiu-keliai-telsiai</t>
+          <t>vpa-laistai</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>180200843</t>
+          <t>110185819</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>UAB Telšių keliai</t>
+          <t>UAB V. Paulius &amp; Associates</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Telšių keliai</t>
+          <t>VPA</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7267,38 +7273,38 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Laistai</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių g. 18, Telšiai</t>
+          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>56.0004158</v>
+        <v>55.636908</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>22.2581129</v>
+        <v>21.209254</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7313,108 +7319,116 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr"/>
-      <c r="R60" s="2" t="inlineStr"/>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
       <c r="S60" s="4" t="n">
         <v>2</v>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
+          <t>VPA betono mazgas Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U60" s="5" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/</t>
+          <t>https://www.vpa.lt/</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://www.vpa.lt/?Kontaktai=</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
+          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>vpa-laistai</t>
+          <t>c3-beton-baisogala</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>110185819</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>UAB V. Paulius &amp; Associates</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>VPA</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Laistai</t>
+          <t>Baisogala</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
+          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>55.636908</v>
+        <v>55.6372</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>21.209254</v>
+        <v>23.7183</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Google Maps nuoroda</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7429,60 +7443,62 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Liebherr</t>
+          <t>Baisiogala Plant</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>3 m³</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S61" s="4" t="n">
-        <v>2</v>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>VPA betono mazgas Klaipėdos rajone.</t>
+          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
         </is>
       </c>
       <c r="U61" s="5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/</t>
+          <t>https://c3beton.com/</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/?Kontaktai=</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-baisogala</t>
+          <t>c3-beton-martiniskis</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7507,24 +7523,24 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Baisogala</t>
+          <t>Martiniškis</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
+          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>55.6372</v>
+        <v>55.1441659</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>23.7183</v>
+        <v>24.1869636</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -7553,27 +7569,27 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Baisiogala Plant</t>
+          <t>Martiniškis Plant</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>Ammann Elba Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>60–80 m³/val.</t>
         </is>
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>2x85 t</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
+          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U62" s="5" t="n">
@@ -7596,7 +7612,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7608,7 +7624,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-martiniskis</t>
+          <t>c3-beton-stasenai</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -7633,38 +7649,38 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
+          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>55.1441659</v>
+        <v>54.6493094</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>24.1869636</v>
+        <v>25.3107972</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus adreso taškas pagal geokodavimą</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7679,12 +7695,12 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis Plant</t>
+          <t>Vilnius Ušos g. Plant</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
+          <t>Nissbau Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -7699,7 +7715,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U63" s="5" t="n">
@@ -7722,7 +7738,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7734,7 +7750,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-stasenai</t>
+          <t>c3-beton-runeikiai</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -7759,38 +7775,38 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Runeikiai</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
+          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>54.6493094</v>
+        <v>55.3327393</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>25.3107972</v>
+        <v>24.3501308</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas pagal geokodavimą</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7805,12 +7821,12 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Vilnius Ušos g. Plant</t>
+          <t>Runeikiai Plant</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Nissbau Euromix C120, 3 m³</t>
+          <t>Ammann Elba Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
@@ -7825,7 +7841,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U64" s="5" t="n">
@@ -7848,7 +7864,7 @@
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -7860,22 +7876,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-runeikiai</t>
+          <t>reljef-rukla</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>301731961</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>UAB Reljef</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>Reljef</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -7885,38 +7901,38 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Runeikiai</t>
+          <t>Rukla</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Kėdainių r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
+          <t>Rukla, Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>55.3327393</v>
+        <v>55.05225</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>24.3501308</v>
+        <v>24.4064167</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>Naudotojo pateiktos koordinatės</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7931,77 +7947,77 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Runeikiai Plant</t>
+          <t>Ammann Elba</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
+          <t>Nenustatyta</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>60–80 m³/val.</t>
+          <t>Nenustatytas</t>
         </is>
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2x85 t</t>
+          <t>2x65 t</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
         </is>
       </c>
       <c r="U65" s="5" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>reljef-rukla</t>
+          <t>ponas-betonas-paraudondvariai</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>301731961</t>
+          <t>306676006</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>UAB Reljef</t>
+          <t>UAB Ponas betonas</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Reljef</t>
+          <t>Ponas betonas</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -8011,38 +8027,38 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Rukla</t>
+          <t>Paraudondvariai</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Rukla, Jonavos r. sav.</t>
+          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>55.05225</v>
+        <v>54.8321418</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>24.4064167</v>
+        <v>25.2755596</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos koordinatės</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8057,77 +8073,77 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Nenustatyta</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Nenustatytas</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2x65 t</t>
+          <t>2 matomi oficialioje nuotraukoje</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
+          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
         </is>
       </c>
       <c r="U66" s="5" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.ponasbetonas.lt/#Apiemus</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
+          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ponas-betonas-paraudondvariai</t>
+          <t>pabrades-betonas-pabrade</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>306676006</t>
+          <t>306177188</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>UAB Ponas betonas</t>
+          <t>UAB Pabradės betonas</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Ponas betonas</t>
+          <t>Pabradės betonas</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8137,38 +8153,38 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Paraudondvariai</t>
+          <t>Pabradė</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Švenčionių r. sav.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
+          <t>Vilniaus g. 161, Pabradė, LT-18177 Švenčionių r.</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
-        <v>54.8321418</v>
+        <v>54.9758768</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>25.2755596</v>
+        <v>25.7373849</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
+          <t>Tikslus oficialioje svetainėje pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
+          <t>Oficiali Pabradės betono Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
+          <t>https://maps.app.goo.gl/TQBCVR8DczDRvQaeA</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8183,186 +8199,60 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
+          <t>Liebherr (tikėtina)</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>3 m³</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>60 m³/val.</t>
         </is>
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>2 matomi oficialioje nuotraukoje</t>
+          <t>3x65 t</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
+          <t>UAB Pabradės betonas Vilniaus g. 161, Pabradėje, gamina sertifikuotą normalųjį betoną ir oficialiai nurodo dirbanti 50 km spinduliu aplink Pabradę. Oficialios galerijos nuotraukose matoma stacionari gamybos bazė su trimis cemento silosais. Mazgo gamintojas tikėtinai Liebherr pagal oficialiose nuotraukose matomą Liebherr įrangą ir gamyklos konstrukcijos vizualinius požymius; gamintojo lentelė viešai neparodyta.</t>
         </is>
       </c>
       <c r="U67" s="5" t="n">
-        <v>0.98</v>
+        <v>0.72</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/</t>
+          <t>https://www.pabradesbetonas.lt/</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/#Apiemus</t>
+          <t>https://www.pabradesbetonas.lt/</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/</t>
+          <t>https://www.pabradesbetonas.lt/galerija/</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
+          <t>Adresas, įmonės kodas ir betono gamyba patvirtinti oficialioje svetainėje bei viešame gamybos kontrolės sertifikate. Koordinatės paimtos iš oficialioje svetainėje pateiktos Google Maps nuorodos. Maišyklės tūris 3 m³, realus našumas 60 m³/val. ir silosai 3x65 t įrašyti pagal naudotojo pateiktą informaciją. Gamintojas Liebherr nurodytas kaip tikėtinas pagal oficialios galerijos nuotraukas; viešo gamintojo ženklinimo ant paties mazgo nerasta.</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>pabrades-betonas-pabrade</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>306177188</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>UAB Pabradės betonas</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Pabradės betonas</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Pabradė</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Švenčionių r. sav.</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Vilniaus g. 161, Pabradė, LT-18177 Švenčionių r.</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>54.9758768</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>25.7373849</v>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Tikslus oficialioje svetainėje pateiktos Google Maps nuorodos taškas</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Oficiali Pabradės betono Google Maps nuoroda</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/TQBCVR8DczDRvQaeA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>Liebherr (tikėtina)</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/val.</t>
-        </is>
-      </c>
-      <c r="S68" s="4" t="inlineStr">
-        <is>
-          <t>3x65 t</t>
-        </is>
-      </c>
-      <c r="T68" s="2" t="inlineStr">
-        <is>
-          <t>UAB Pabradės betonas Vilniaus g. 161, Pabradėje, gamina sertifikuotą normalųjį betoną ir oficialiai nurodo dirbanti 50 km spinduliu aplink Pabradę. Oficialios galerijos nuotraukose matoma stacionari gamybos bazė su trimis cemento silosais. Mazgo gamintojas tikėtinai Liebherr pagal oficialiose nuotraukose matomą Liebherr įrangą ir gamyklos konstrukcijos vizualinius požymius; gamintojo lentelė viešai neparodyta.</t>
-        </is>
-      </c>
-      <c r="U68" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="V68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pabradesbetonas.lt/</t>
-        </is>
-      </c>
-      <c r="W68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pabradesbetonas.lt/</t>
-        </is>
-      </c>
-      <c r="X68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.pabradesbetonas.lt/galerija/</t>
-        </is>
-      </c>
-      <c r="Y68" s="2" t="inlineStr">
-        <is>
-          <t>Adresas, įmonės kodas ir betono gamyba patvirtinti oficialioje svetainėje bei viešame gamybos kontrolės sertifikate. Koordinatės paimtos iš oficialioje svetainėje pateiktos Google Maps nuorodos. Maišyklės tūris 3 m³, realus našumas 60 m³/val. ir silosai 3x65 t įrašyti pagal naudotojo pateiktą informaciją. Gamintojas Liebherr nurodytas kaip tikėtinas pagal oficialios galerijos nuotraukas; viešo gamintojo ženklinimo ant paties mazgo nerasta.</t>
-        </is>
-      </c>
-      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z68"/>
+  <autoFilter ref="A1:Z67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8451,7 +8341,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T15:17:04.691715+00:00</t>
+          <t>2026-09-23T15:24:19.634207+00:00</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:17:04.691715+00:00</t>
+          <t>2026-09-23T15:24:19.635205+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8520,7 +8410,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z67" headerRowCount="1">
-  <autoFilter ref="A1:Z67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z70" headerRowCount="1">
+  <autoFilter ref="A1:Z70"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Įrašo ID"/>
     <tableColumn id="2" name="Įmonės kodas"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z67"/>
+  <dimension ref="A1:Z70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -8251,8 +8251,382 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>alkesta-marijampole-vasaros</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>249672710</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>UAB Alkesta</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Alkesta</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Konkurentas</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Marijampolė</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Marijampolės sav.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Vasaros g. 14, Marijampolė, LT-68111</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>54.5686121</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>23.3895157</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Elba</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>0,5 m³</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>10 m³/val.</t>
+        </is>
+      </c>
+      <c r="S68" s="4" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>UAB Alkesta Marijampolės betono mazgas Vasaros g. 14. Mazgo gamintojas Elba, maišyklė 0,5 m³, našumas 10 m³/val.</t>
+        </is>
+      </c>
+      <c r="U68" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>https://alkesta.lt/</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>https://spsc.lt/registrai/regsapp/ser_produktai_view.php?editid1=13061</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>Oficialus SPSC sertifikatų registras patvirtina UAB Alkesta betono gamybą ir gamybos vietą Vasaros g. 14, Marijampolėje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris ir našumas įrašyti pagal naudotojo pateiktą informaciją.</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>gevalda-visincia</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>302592895</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>UAB Gevalda</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Gevalda</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Konkurentas</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Visinčia</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Šalčininkų r. sav.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Visinčia, Pabarės sen., Šalčininkų r. sav.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>54.4122467</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>25.1449142</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Elkon</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/val.</t>
+        </is>
+      </c>
+      <c r="S69" s="4" t="inlineStr">
+        <is>
+          <t>2x85 t</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>UAB Gevalda mobilus betono mazgas Visinčioje. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
+        </is>
+      </c>
+      <c r="U69" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gevalda.lt/</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris, našumas ir silosai įrašyti pagal naudotojo pateiktą informaciją.</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>gevalda-kaunas-palemonas</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>302592895</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>UAB Gevalda</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Gevalda</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Konkurentas</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Kaunas</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Kauno m. sav.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Kražantės g., Palemonas, Kaunas</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>54.918</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>24.063</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Elkon</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>60 m³/val.</t>
+        </is>
+      </c>
+      <c r="S70" s="4" t="inlineStr">
+        <is>
+          <t>2x85 t</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>UAB Gevalda mobilus betono mazgas Palemone, Kaune. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
+        </is>
+      </c>
+      <c r="U70" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gevalda.lt/</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija ir analogiški techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z67"/>
+  <autoFilter ref="A1:Z70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8341,7 +8715,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T15:24:19.634207+00:00</t>
+          <t>2026-09-23T15:50:11.921774+00:00</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8770,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:24:19.635205+00:00</t>
+          <t>2026-09-23T15:50:11.921774+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8410,7 +8784,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z70" headerRowCount="1">
-  <autoFilter ref="A1:Z70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z69" headerRowCount="1">
+  <autoFilter ref="A1:Z69"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Įrašo ID"/>
     <tableColumn id="2" name="Įmonės kodas"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z70"/>
+  <dimension ref="A1:Z69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -6802,22 +6802,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>beton-eura-dovainonys</t>
+          <t>silutes-betonas-silute</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>302745280</t>
+          <t>177392928</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UAB Beton Eura</t>
+          <t>UAB Šilutės betonas</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Beton Eura</t>
+          <t>Šilutės betonas</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6827,24 +6827,24 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Dovainonys</t>
+          <t>Šilutė</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Kaišiadorių r. sav.</t>
+          <t>Šilutės r. sav.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Žilvičių g. 2, Dovainonys, Kaišiadorių r.</t>
+          <t>Ramučių g. 1, Šilutė</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>54.8395918</v>
+        <v>55.3538641</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>24.2360193</v>
+        <v>21.4796635</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Beton Eura betono gamyba</t>
+          <t>Šilutės betono gamyba</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -6887,24 +6887,20 @@
       <c r="U56" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.betoneura.lt/</t>
-        </is>
-      </c>
+      <c r="V56" s="2" t="inlineStr"/>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>https://www.betoneura.lt/kontaktai/</t>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>https://www.betoneura.lt/kontaktai/</t>
+          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Beton Eura kontaktų puslapis patvirtina Žilvičių g. 2 adresą ir rekvizitus.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -6916,22 +6912,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>silutes-betonas-silute</t>
+          <t>kruszbet-lithuania-jure</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>177392928</t>
+          <t>305173596</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilutės betonas</t>
+          <t>UAB KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betonas</t>
+          <t>KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -6941,24 +6937,24 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Šilutė</t>
+          <t>Jūrė</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Šilutės r. sav.</t>
+          <t>Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Ramučių g. 1, Šilutė</t>
+          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>55.3538641</v>
+        <v>54.7706307</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>21.4796635</v>
+        <v>23.4998409</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6987,7 +6983,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betono gamyba</t>
+          <t>KRUSZBET Lithuania betono gamyba</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -7007,11 +7003,7 @@
           <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
         </is>
       </c>
-      <c r="X57" s="2" t="inlineStr">
-        <is>
-          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
-        </is>
-      </c>
+      <c r="X57" s="2" t="inlineStr"/>
       <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
@@ -7026,49 +7018,49 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>kruszbet-lithuania-jure</t>
+          <t>telsiu-keliai-telsiai</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>305173596</t>
+          <t>180200843</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>UAB KRUSZBET Lithuania</t>
+          <t>UAB Telšių keliai</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania</t>
+          <t>Telšių keliai</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Jūrė</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Kazlų Rūdos sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
+          <t>Mažeikių g. 18, Telšiai</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>54.7706307</v>
+        <v>56.0004158</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>23.4998409</v>
+        <v>22.2581129</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -7097,57 +7089,67 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania betono gamyba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
       <c r="R58" s="2" t="inlineStr"/>
-      <c r="S58" s="4" t="inlineStr"/>
+      <c r="S58" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
         </is>
       </c>
       <c r="U58" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V58" s="2" t="inlineStr"/>
+        <v>0.86</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/</t>
+        </is>
+      </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X58" s="2" t="inlineStr"/>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+        </is>
+      </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>telsiu-keliai-telsiai</t>
+          <t>vpa-laistai</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>180200843</t>
+          <t>110185819</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>UAB Telšių keliai</t>
+          <t>UAB V. Paulius &amp; Associates</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Telšių keliai</t>
+          <t>VPA</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -7157,38 +7159,38 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Laistai</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių g. 18, Telšiai</t>
+          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>56.0004158</v>
+        <v>55.636908</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>22.2581129</v>
+        <v>21.209254</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7203,108 +7205,116 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr"/>
-      <c r="R59" s="2" t="inlineStr"/>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
       <c r="S59" s="4" t="n">
         <v>2</v>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
+          <t>VPA betono mazgas Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U59" s="5" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/</t>
+          <t>https://www.vpa.lt/</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://www.vpa.lt/?Kontaktai=</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
+          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>vpa-laistai</t>
+          <t>c3-beton-baisogala</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>110185819</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>UAB V. Paulius &amp; Associates</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>VPA</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Laistai</t>
+          <t>Baisogala</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
+          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>55.636908</v>
+        <v>55.6372</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>21.209254</v>
+        <v>23.7183</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Google Maps nuoroda</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7319,60 +7329,62 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Liebherr</t>
+          <t>Baisiogala Plant</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>3 m³</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S60" s="4" t="n">
-        <v>2</v>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="S60" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>VPA betono mazgas Klaipėdos rajone.</t>
+          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
         </is>
       </c>
       <c r="U60" s="5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/</t>
+          <t>https://c3beton.com/</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/?Kontaktai=</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-baisogala</t>
+          <t>c3-beton-martiniskis</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -7397,24 +7409,24 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Baisogala</t>
+          <t>Martiniškis</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
+          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>55.6372</v>
+        <v>55.1441659</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>23.7183</v>
+        <v>24.1869636</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -7443,27 +7455,27 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Baisiogala Plant</t>
+          <t>Martiniškis Plant</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>Ammann Elba Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>60–80 m³/val.</t>
         </is>
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>2x85 t</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
+          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U61" s="5" t="n">
@@ -7486,7 +7498,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7498,7 +7510,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-martiniskis</t>
+          <t>c3-beton-stasenai</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -7523,38 +7535,38 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
+          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>55.1441659</v>
+        <v>54.6493094</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>24.1869636</v>
+        <v>25.3107972</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus adreso taškas pagal geokodavimą</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7569,12 +7581,12 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis Plant</t>
+          <t>Vilnius Ušos g. Plant</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
+          <t>Nissbau Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
@@ -7589,7 +7601,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U62" s="5" t="n">
@@ -7612,7 +7624,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7624,7 +7636,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-stasenai</t>
+          <t>c3-beton-runeikiai</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -7649,38 +7661,38 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Runeikiai</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
+          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>54.6493094</v>
+        <v>55.3327393</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>25.3107972</v>
+        <v>24.3501308</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas pagal geokodavimą</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7695,12 +7707,12 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Vilnius Ušos g. Plant</t>
+          <t>Runeikiai Plant</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Nissbau Euromix C120, 3 m³</t>
+          <t>Ammann Elba Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
@@ -7715,7 +7727,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U63" s="5" t="n">
@@ -7738,7 +7750,7 @@
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7750,22 +7762,22 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-runeikiai</t>
+          <t>reljef-rukla</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>301731961</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>UAB Reljef</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>Reljef</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7775,38 +7787,38 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Runeikiai</t>
+          <t>Rukla</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Kėdainių r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
+          <t>Rukla, Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>55.3327393</v>
+        <v>55.05225</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>24.3501308</v>
+        <v>24.4064167</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>Naudotojo pateiktos koordinatės</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7821,77 +7833,77 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Runeikiai Plant</t>
+          <t>Ammann Elba</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
+          <t>Nenustatyta</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>60–80 m³/val.</t>
+          <t>Nenustatytas</t>
         </is>
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2x85 t</t>
+          <t>2x65 t</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
         </is>
       </c>
       <c r="U64" s="5" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>reljef-rukla</t>
+          <t>ponas-betonas-paraudondvariai</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>301731961</t>
+          <t>306676006</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>UAB Reljef</t>
+          <t>UAB Ponas betonas</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Reljef</t>
+          <t>Ponas betonas</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -7901,38 +7913,38 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Rukla</t>
+          <t>Paraudondvariai</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Rukla, Jonavos r. sav.</t>
+          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>55.05225</v>
+        <v>54.8321418</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>24.4064167</v>
+        <v>25.2755596</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos koordinatės</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7947,77 +7959,77 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Nenustatyta</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>Nenustatytas</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>2x65 t</t>
+          <t>2 matomi oficialioje nuotraukoje</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
+          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
         </is>
       </c>
       <c r="U65" s="5" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.ponasbetonas.lt/#Apiemus</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
+          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ponas-betonas-paraudondvariai</t>
+          <t>pabrades-betonas-pabrade</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>306676006</t>
+          <t>306177188</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>UAB Ponas betonas</t>
+          <t>UAB Pabradės betonas</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Ponas betonas</t>
+          <t>Pabradės betonas</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -8027,38 +8039,38 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Paraudondvariai</t>
+          <t>Pabradė</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Švenčionių r. sav.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
+          <t>Vilniaus g. 161, Pabradė, LT-18177 Švenčionių r.</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>54.8321418</v>
+        <v>54.9758768</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>25.2755596</v>
+        <v>25.7373849</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
+          <t>Tikslus oficialioje svetainėje pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
+          <t>Oficiali Pabradės betono Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
+          <t>https://maps.app.goo.gl/TQBCVR8DczDRvQaeA</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8073,77 +8085,77 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
+          <t>Liebherr (tikėtina)</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>3 m³</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>60 m³/val.</t>
         </is>
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>2 matomi oficialioje nuotraukoje</t>
+          <t>3x65 t</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
+          <t>UAB Pabradės betonas Vilniaus g. 161, Pabradėje, gamina sertifikuotą normalųjį betoną ir oficialiai nurodo dirbanti 50 km spinduliu aplink Pabradę. Oficialios galerijos nuotraukose matoma stacionari gamybos bazė su trimis cemento silosais. Mazgo gamintojas tikėtinai Liebherr pagal oficialiose nuotraukose matomą Liebherr įrangą ir gamyklos konstrukcijos vizualinius požymius; gamintojo lentelė viešai neparodyta.</t>
         </is>
       </c>
       <c r="U66" s="5" t="n">
-        <v>0.98</v>
+        <v>0.72</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/</t>
+          <t>https://www.pabradesbetonas.lt/</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/#Apiemus</t>
+          <t>https://www.pabradesbetonas.lt/</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/</t>
+          <t>https://www.pabradesbetonas.lt/galerija/</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
+          <t>Adresas, įmonės kodas ir betono gamyba patvirtinti oficialioje svetainėje bei viešame gamybos kontrolės sertifikate. Koordinatės paimtos iš oficialioje svetainėje pateiktos Google Maps nuorodos. Maišyklės tūris 3 m³, realus našumas 60 m³/val. ir silosai 3x65 t įrašyti pagal naudotojo pateiktą informaciją. Gamintojas Liebherr nurodytas kaip tikėtinas pagal oficialios galerijos nuotraukas; viešo gamintojo ženklinimo ant paties mazgo nerasta.</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>pabrades-betonas-pabrade</t>
+          <t>alkesta-marijampole-vasaros</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>306177188</t>
+          <t>249672710</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>UAB Pabradės betonas</t>
+          <t>UAB Alkesta</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Pabradės betonas</t>
+          <t>Alkesta</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8153,38 +8165,38 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Pabradė</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Švenčionių r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus g. 161, Pabradė, LT-18177 Švenčionių r.</t>
+          <t>Vasaros g. 14, Marijampolė, LT-68111</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
-        <v>54.9758768</v>
+        <v>54.5686121</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>25.7373849</v>
+        <v>23.3895157</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Tikslus oficialioje svetainėje pateiktos Google Maps nuorodos taškas</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Pabradės betono Google Maps nuoroda</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/TQBCVR8DczDRvQaeA</t>
+          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8199,50 +8211,46 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Liebherr (tikėtina)</t>
+          <t>Elba</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>3 m³</t>
+          <t>0,5 m³</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>60 m³/val.</t>
-        </is>
-      </c>
-      <c r="S67" s="4" t="inlineStr">
-        <is>
-          <t>3x65 t</t>
-        </is>
-      </c>
+          <t>10 m³/val.</t>
+        </is>
+      </c>
+      <c r="S67" s="4" t="inlineStr"/>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>UAB Pabradės betonas Vilniaus g. 161, Pabradėje, gamina sertifikuotą normalųjį betoną ir oficialiai nurodo dirbanti 50 km spinduliu aplink Pabradę. Oficialios galerijos nuotraukose matoma stacionari gamybos bazė su trimis cemento silosais. Mazgo gamintojas tikėtinai Liebherr pagal oficialiose nuotraukose matomą Liebherr įrangą ir gamyklos konstrukcijos vizualinius požymius; gamintojo lentelė viešai neparodyta.</t>
+          <t>UAB Alkesta Marijampolės betono mazgas Vasaros g. 14. Mazgo gamintojas Elba, maišyklė 0,5 m³, našumas 10 m³/val.</t>
         </is>
       </c>
       <c r="U67" s="5" t="n">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>https://www.pabradesbetonas.lt/</t>
+          <t>https://alkesta.lt/</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>https://www.pabradesbetonas.lt/</t>
+          <t>https://spsc.lt/registrai/regsapp/ser_produktai_view.php?editid1=13061</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>https://www.pabradesbetonas.lt/galerija/</t>
+          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>Adresas, įmonės kodas ir betono gamyba patvirtinti oficialioje svetainėje bei viešame gamybos kontrolės sertifikate. Koordinatės paimtos iš oficialioje svetainėje pateiktos Google Maps nuorodos. Maišyklės tūris 3 m³, realus našumas 60 m³/val. ir silosai 3x65 t įrašyti pagal naudotojo pateiktą informaciją. Gamintojas Liebherr nurodytas kaip tikėtinas pagal oficialios galerijos nuotraukas; viešo gamintojo ženklinimo ant paties mazgo nerasta.</t>
+          <t>Oficialus SPSC sertifikatų registras patvirtina UAB Alkesta betono gamybą ir gamybos vietą Vasaros g. 14, Marijampolėje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris ir našumas įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8254,22 +8262,22 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>alkesta-marijampole-vasaros</t>
+          <t>gevalda-visincia</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>249672710</t>
+          <t>302592895</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>UAB Alkesta</t>
+          <t>UAB Gevalda</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Alkesta</t>
+          <t>Gevalda</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -8279,24 +8287,24 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Visinčia</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Šalčininkų r. sav.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Vasaros g. 14, Marijampolė, LT-68111</t>
+          <t>Visinčia, Pabarės sen., Šalčininkų r. sav.</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>54.5686121</v>
+        <v>54.4122467</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>23.3895157</v>
+        <v>25.1449142</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -8310,7 +8318,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
+          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8325,23 +8333,27 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Elba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>0,5 m³</t>
+          <t>3 m³</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>10 m³/val.</t>
-        </is>
-      </c>
-      <c r="S68" s="4" t="inlineStr"/>
+          <t>60 m³/val.</t>
+        </is>
+      </c>
+      <c r="S68" s="4" t="inlineStr">
+        <is>
+          <t>2x85 t</t>
+        </is>
+      </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>UAB Alkesta Marijampolės betono mazgas Vasaros g. 14. Mazgo gamintojas Elba, maišyklė 0,5 m³, našumas 10 m³/val.</t>
+          <t>UAB Gevalda mobilus betono mazgas Visinčioje. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U68" s="5" t="n">
@@ -8349,22 +8361,22 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>https://alkesta.lt/</t>
+          <t>https://www.gevalda.lt/</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>https://spsc.lt/registrai/regsapp/ser_produktai_view.php?editid1=13061</t>
+          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
+          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>Oficialus SPSC sertifikatų registras patvirtina UAB Alkesta betono gamybą ir gamybos vietą Vasaros g. 14, Marijampolėje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris ir našumas įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris, našumas ir silosai įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8376,7 +8388,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>gevalda-visincia</t>
+          <t>gevalda-kaunas-palemonas</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -8401,24 +8413,24 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Visinčia</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Šalčininkų r. sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Visinčia, Pabarės sen., Šalčininkų r. sav.</t>
+          <t>Kražantės g., Palemonas, Kaunas</t>
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>54.4122467</v>
+        <v>54.918</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>25.1449142</v>
+        <v>24.063</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -8432,7 +8444,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
+          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8467,7 +8479,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>UAB Gevalda mobilus betono mazgas Visinčioje. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
+          <t>UAB Gevalda mobilus betono mazgas Palemone, Kaune. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U69" s="5" t="n">
@@ -8485,148 +8497,22 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
+          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris, našumas ir silosai įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija ir analogiški techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>gevalda-kaunas-palemonas</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>302592895</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>UAB Gevalda</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Gevalda</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Kaunas</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Kauno m. sav.</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Kražantės g., Palemonas, Kaunas</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>54.918</v>
-      </c>
-      <c r="J70" s="3" t="n">
-        <v>24.063</v>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/val.</t>
-        </is>
-      </c>
-      <c r="S70" s="4" t="inlineStr">
-        <is>
-          <t>2x85 t</t>
-        </is>
-      </c>
-      <c r="T70" s="2" t="inlineStr">
-        <is>
-          <t>UAB Gevalda mobilus betono mazgas Palemone, Kaune. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
-        </is>
-      </c>
-      <c r="U70" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="V70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gevalda.lt/</t>
-        </is>
-      </c>
-      <c r="W70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
-        </is>
-      </c>
-      <c r="X70" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
-        </is>
-      </c>
-      <c r="Y70" s="2" t="inlineStr">
-        <is>
-          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija ir analogiški techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
-        </is>
-      </c>
-      <c r="Z70" s="2" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z70"/>
+  <autoFilter ref="A1:Z69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8715,7 +8601,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T15:50:11.921774+00:00</t>
+          <t>2026-09-23T15:57:21.399333+00:00</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8656,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:50:11.921774+00:00</t>
+          <t>2026-09-23T15:57:21.399333+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8784,7 +8670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -4112,16 +4112,28 @@
           <t>Betono bazė</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="4" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>1 m³</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>20-30 m³/val.</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>2x50 t (horizontalūs)</t>
+        </is>
+      </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>Viešuose šaltiniuose minima betono mišinių veikla; tikslų mazgo adresą reikia patikslinti.</t>
+          <t>UAB Betono bazė betono mazgas Elektrinės g. 11, Drūkšinių k. Maišyklė 1 m³, našumas 20-30 m³/val., du horizontalūs po 50 t silosai.</t>
         </is>
       </c>
       <c r="U31" s="5" t="n">
-        <v>0.65</v>
+        <v>0.95</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
@@ -4140,12 +4152,12 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Elektrinės g. 11 adresą ir betono bazės veiklą.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Elektrinės g. 11 adresą ir betono bazės veiklą. Maišyklės tūris, našumas ir horizontalių silosų skaičius bei talpa įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23T15:57:21.399333+00:00</t>
+          <t>2026-09-24T04:22:17.382218+00:00</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8668,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23T15:57:21.399333+00:00</t>
+          <t>2026-09-24T04:22:17.383221+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z69" headerRowCount="1">
-  <autoFilter ref="A1:Z69"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z67" headerRowCount="1">
+  <autoFilter ref="A1:Z67"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Įrašo ID"/>
     <tableColumn id="2" name="Įmonės kodas"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z69"/>
+  <dimension ref="A1:Z67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -4618,18 +4618,18 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>re-betono-konstrukcijos-kretinga</t>
+          <t>silales-statyba-vingininkai</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>UAB RE Betono konstrukcijos</t>
+          <t>UAB Šilalės statyba</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>RE Betono konstrukcijos</t>
+          <t>Šilalės statyba</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4639,24 +4639,24 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Kretinga</t>
+          <t>Vingininkai</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Kretingos r. sav.</t>
+          <t>Šilalės r. sav.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Tiekėjų g. 27B, Kretinga</t>
+          <t>Lauryno Ivinskio g. 7, Vingininkai, Šilalės r.</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>55.87963</v>
+        <v>55.4808479</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>21.220888</v>
+        <v>22.1937399</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>RE Betono konstrukcijų gamyba</t>
+          <t>Šilalės statybos betono gaminių gamyba</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -4693,26 +4693,30 @@
       <c r="S36" s="4" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, cemento gaminiai, betono siurblys ir pamatų blokai Kretingoje.</t>
+          <t>Viešai skelbiama betono gaminių ir statybinių konstrukcijų veikla Šilalės rajone.</t>
         </is>
       </c>
       <c r="U36" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr"/>
+        <v>0.72</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.silalesstatyba.lt/</t>
+        </is>
+      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
+          <t>https://www.silalesstatyba.lt/</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/re-betono-konstrukcijos-uab-betonas-cementas-betono-siurblys-pamatu-blokai-kretingoje-104253/</t>
+          <t>https://www.silalesstatyba.lt/</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>Katalogo šaltinis, reikia patikslinti gamybos apimtį.</t>
+          <t>Reikia patikslinti tikslų gaminių asortimentą.</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4724,18 +4728,18 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>silales-statyba-vingininkai</t>
+          <t>panevezio-gelzbetonis-panevezys</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilalės statyba</t>
+          <t>UAB Panevėžio gelžbetonis</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Šilalės statyba</t>
+          <t>Panevėžio gelžbetonis</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4745,24 +4749,24 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Vingininkai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Šilalės r. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Lauryno Ivinskio g. 7, Vingininkai, Šilalės r.</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>55.4808479</v>
+        <v>55.7409491</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>22.1937399</v>
+        <v>24.3803541</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4786,12 +4790,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Šilalės statybos betono gaminių gamyba</t>
+          <t>Panevėžio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -4799,30 +4803,26 @@
       <c r="S37" s="4" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių ir statybinių konstrukcijų veikla Šilalės rajone.</t>
+          <t>Viešame įmonių kataloge nurodomas gelžbetonio gaminių profilis Panevėžyje.</t>
         </is>
       </c>
       <c r="U37" s="5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.silalesstatyba.lt/</t>
-        </is>
-      </c>
+        <v>0.78</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr"/>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>https://www.silalesstatyba.lt/</t>
+          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>https://www.silalesstatyba.lt/</t>
+          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti tikslų gaminių asortimentą.</t>
+          <t>Reikia patikrinti veiklos aktyvumą ir produkcijos apimtį.</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4834,18 +4834,18 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>panevezio-gelzbetonis-panevezys</t>
+          <t>pamatas-telsiai</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>UAB Panevėžio gelžbetonis</t>
+          <t>UAB Pamatas</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio gelžbetonis</t>
+          <t>Pamatas</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4855,24 +4855,24 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Tryškių g. 46, Dimaičių k., Telšių r.</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.9874536</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>24.3803541</v>
+        <v>22.287162</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4896,12 +4896,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono gaminiai</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio gelžbetonio gamykla</t>
+          <t>Pamatas betono gaminių gamyba</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -4909,26 +4909,30 @@
       <c r="S38" s="4" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>Viešame įmonių kataloge nurodomas gelžbetonio gaminių profilis Panevėžyje.</t>
+          <t>Viešai skelbiami pamatų ir kiti betono gaminiai Telšių rajone.</t>
         </is>
       </c>
       <c r="U38" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V38" s="2" t="inlineStr"/>
+        <v>0.72</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>https://pamatas.lt/</t>
+        </is>
+      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>https://www.spec.lt/imone/panevezio-gelzbetonis-uab</t>
+          <t>https://pamatas.lt/</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikrinti veiklos aktyvumą ir produkcijos apimtį.</t>
+          <t>Adresas patikslintas pagal lietuvišką įmonės puslapį; koordinatės nustatytos Lietuvos geolokatoriumi.</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4940,18 +4944,18 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>pamatas-telsiai</t>
+          <t>betono-zona-klaipeda</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>UAB Pamatas</t>
+          <t>UAB Betono zona</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Pamatas</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4961,24 +4965,24 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Klaipėda</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Klaipėdos m. sav.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Tryškių g. 46, Dimaičių k., Telšių r.</t>
+          <t>Dvaro g. 6, Klaipėda</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.9874536</v>
+        <v>55.7549809</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>22.287162</v>
+        <v>21.150509</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -5007,7 +5011,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Pamatas betono gaminių gamyba</t>
+          <t>Betono zona</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -5015,30 +5019,30 @@
       <c r="S39" s="4" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiami pamatų ir kiti betono gaminiai Telšių rajone.</t>
+          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
         </is>
       </c>
       <c r="U39" s="5" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>https://pamatas.lt/</t>
+          <t>https://betonozona.lt/</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>Adresas patikslintas pagal lietuvišką įmonės puslapį; koordinatės nustatytos Lietuvos geolokatoriumi.</t>
+          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5050,18 +5054,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>pamario-grupe-kalnuvenai</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr"/>
+          <t>topbeton-panevezys</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>307083610</t>
+        </is>
+      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>UAB Pamario grupė</t>
+          <t>UAB Topbeton</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupė</t>
+          <t>Topbeton</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5071,24 +5079,24 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Kalnuvėnai</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Kaukėnų g. 12, Kalnuvėnai, Klaipėdos r.</t>
+          <t>Beržų g. 5C, Panevėžys</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>55.7905468</v>
+        <v>55.7168572</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>21.1471136</v>
+        <v>24.3617863</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -5117,7 +5125,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Pamario grupės betono mazgas</t>
+          <t>Topbeton betono mazgas</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -5125,30 +5133,30 @@
       <c r="S40" s="4" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Klaipėdos rajone.</t>
+          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U40" s="5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://topbeton.lt/</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>https://pamariogrupe.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą ir gamybos režimą.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5160,18 +5168,18 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>betono-zona-klaipeda</t>
+          <t>gelzbetonio-gamyba-panevezys</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono zona</t>
+          <t>MB Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5181,24 +5189,24 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g. 6, Klaipėda</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>55.7549809</v>
+        <v>55.7409491</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>21.150509</v>
+        <v>24.3803541</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -5222,12 +5230,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Gelžbetonio gamyba Panevėžyje</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -5235,30 +5243,30 @@
       <c r="S41" s="4" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
+          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U41" s="5" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
+          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5270,22 +5278,18 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>topbeton-panevezys</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>307083610</t>
-        </is>
-      </c>
+          <t>inroma-pakruojis</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>UAB Topbeton</t>
+          <t>UAB Inroma</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Topbeton</t>
+          <t>Inroma</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5295,24 +5299,24 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Pakruojis</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Pakruojo r. sav.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Beržų g. 5C, Panevėžys</t>
+          <t>Pramonės g. 5B, Pakruojis</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>55.7168572</v>
+        <v>55.9763263</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>24.3617863</v>
+        <v>23.8584712</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -5341,7 +5345,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Topbeton betono mazgas</t>
+          <t>Inroma betono mazgas</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -5349,30 +5353,30 @@
       <c r="S42" s="4" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
         </is>
       </c>
       <c r="U42" s="5" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>https://topbeton.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
+          <t>Reikia patikslinti našumą.</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5384,18 +5388,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>gelzbetonio-gamyba-panevezys</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr"/>
+          <t>utenos-betonas-utena</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>300904691</t>
+        </is>
+      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>MB Gelžbetonio gamyba</t>
+          <t>UAB Utenos betonas</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba</t>
+          <t>Utenos betonas</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5405,24 +5413,24 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Utenos r. sav.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Metalo g. 9B, Utena</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.4947607</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>24.3803541</v>
+        <v>25.6225075</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -5441,17 +5449,17 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba Panevėžyje</t>
+          <t>Utenos betono mazgas</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -5459,30 +5467,30 @@
       <c r="S43" s="4" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
         </is>
       </c>
       <c r="U43" s="5" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://utenosbetonas.lt/</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5494,18 +5502,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>inroma-pakruojis</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr"/>
+          <t>sbetonas-jonava</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>300902683</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>UAB Inroma</t>
+          <t>UAB Sbetonas</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Inroma</t>
+          <t>Sbetonas</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5515,24 +5527,24 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Pakruojis</t>
+          <t>Jonava</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Pakruojo r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Pramonės g. 5B, Pakruojis</t>
+          <t>Skarulių g. 58, Jonava</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>55.9763263</v>
+        <v>55.0786452</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>23.8584712</v>
+        <v>24.3199072</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -5561,7 +5573,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Inroma betono mazgas</t>
+          <t>Sbetonas betono mazgas</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -5569,30 +5581,30 @@
       <c r="S44" s="4" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
+          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
         </is>
       </c>
       <c r="U44" s="5" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą.</t>
+          <t>Papildomai rasta pagal prekinio betono požymį.</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5604,22 +5616,18 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>utenos-betonas-utena</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>300904691</t>
-        </is>
-      </c>
+          <t>kalcitas-naujoji-akmene</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>UAB Utenos betonas</t>
+          <t>AB Kalcitas</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Utenos betonas</t>
+          <t>Kalcitas</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5629,24 +5637,24 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Utenos r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Metalo g. 9B, Utena</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>55.4947607</v>
+        <v>56.3143832</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>25.6225075</v>
+        <v>22.9130704</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -5675,7 +5683,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Utenos betono mazgas</t>
+          <t>Kalcitas betono mišinių gamybos linija</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -5683,30 +5691,26 @@
       <c r="S45" s="4" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
+          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
         </is>
       </c>
       <c r="U45" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>https://utenosbetonas.lt/</t>
-        </is>
-      </c>
+      <c r="V45" s="2" t="inlineStr"/>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
+          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5718,22 +5722,18 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>sbetonas-jonava</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>300902683</t>
-        </is>
-      </c>
+          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>UAB Sbetonas</t>
+          <t>UAB Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas</t>
+          <t>Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5743,24 +5743,24 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Jonava</t>
+          <t>Gelgaudiškis</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Šakių r. sav.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Skarulių g. 58, Jonava</t>
+          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>55.0786452</v>
+        <v>55.07067</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>24.3199072</v>
+        <v>22.976723</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5769,27 +5769,27 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>GLG kontaktų puslapis</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono mišiniai ir gelžbetonis</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas betono mazgas</t>
+          <t>Gelgaudiškio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -5797,30 +5797,30 @@
       <c r="S46" s="4" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
+          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
         </is>
       </c>
       <c r="U46" s="5" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://glg.lt/</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://glg.lt/betonas/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta pagal prekinio betono požymį.</t>
+          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5832,45 +5832,49 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>kalcitas-naujoji-akmene</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr"/>
+          <t>ginfa-kutiskiai</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>302680943</t>
+        </is>
+      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>AB Kalcitas</t>
+          <t>UAB GinFa</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas</t>
+          <t>GinFa</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta</t>
+          <t>Papildomai rasta EVRK 23.63</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Kutiškiai</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>56.3143832</v>
+        <v>55.8326273</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>22.9130704</v>
+        <v>23.4995317</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5903,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas betono mišinių gamybos linija</t>
+          <t>GinFa betono gamyba</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -5907,26 +5911,22 @@
       <c r="S47" s="4" t="inlineStr"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
+          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U47" s="5" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="V47" s="2" t="inlineStr"/>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
-        </is>
-      </c>
-      <c r="X47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr"/>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -5938,45 +5938,49 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr"/>
+          <t>antano-gribino-imone-prienai</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>170687267</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelgaudiškio gelžbetonis</t>
+          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonis</t>
+          <t>Antano Gribino įmonė</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta</t>
+          <t>Papildomai rasta EVRK 23.63</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškis</t>
+          <t>Prienai</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Šakių r. sav.</t>
+          <t>Prienų r. sav.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
+          <t>Kęstučio g. 95A, Prienai</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>55.07067</v>
+        <v>54.6523184</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>22.976723</v>
+        <v>23.9696591</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5985,27 +5989,27 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>GLG kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai ir gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonio gamykla</t>
+          <t>Antano Gribino įmonės betono gamyba</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -6013,30 +6017,22 @@
       <c r="S48" s="4" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
+          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U48" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/</t>
-        </is>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr"/>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="X48" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/betonas/betono-misiniai/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr"/>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6048,22 +6044,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>ginfa-kutiskiai</t>
+          <t>vinido-taurage</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>302680943</t>
+          <t>306258220</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>UAB GinFa</t>
+          <t>UAB Vinido</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>GinFa</t>
+          <t>Vinido</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -6073,24 +6069,24 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Kutiškiai</t>
+          <t>Tauragė</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Tauragės r. sav.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
+          <t>Gaurės g. 32, Tauragė</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>55.8326273</v>
+        <v>55.2492204</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>23.4995317</v>
+        <v>22.3185845</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -6119,7 +6115,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>GinFa betono gamyba</t>
+          <t>Vinido betono gamyba</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -6133,16 +6129,24 @@
       <c r="U49" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/</t>
+        </is>
+      </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X49" s="2" t="inlineStr"/>
+          <t>https://betonastaurageje.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/betonas/</t>
+        </is>
+      </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Oficiali Vinido svetainė patvirtina Gaurės g. 32 adresą, betono gamybą ir betono mazgą.</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6154,22 +6158,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>antano-gribino-imone-prienai</t>
+          <t>santvara-kedainiai</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>170687267</t>
+          <t>304915297</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
+          <t>UAB Santvara</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonė</t>
+          <t>Santvara</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -6179,24 +6183,24 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Prienai</t>
+          <t>Kėdainiai</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Prienų r. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Kęstučio g. 95A, Prienai</t>
+          <t>Aruodų g. 34, Kėdainiai</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>54.6523184</v>
+        <v>55.2634747</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>23.9696591</v>
+        <v>23.9440384</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -6225,7 +6229,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonės betono gamyba</t>
+          <t>Santvara betono gamyba</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -6239,16 +6243,24 @@
       <c r="U50" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>https://santvara.eu/</t>
+        </is>
+      </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X50" s="2" t="inlineStr"/>
+          <t>https://santvara.eu/</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>https://santvara.eu/</t>
+        </is>
+      </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6260,22 +6272,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>vinido-taurage</t>
+          <t>medis-ir-betonas-naujoji-akmene</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>306258220</t>
+          <t>153074073</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>UAB Vinido</t>
+          <t>AB Medis ir betonas</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Vinido</t>
+          <t>Medis ir betonas</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6285,24 +6297,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Tauragė</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Tauragės r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Gaurės g. 32, Tauragė</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>55.2492204</v>
+        <v>56.3143832</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>22.3185845</v>
+        <v>22.9130704</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -6331,7 +6343,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Vinido betono gamyba</t>
+          <t>Medis ir betonas gamyba</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -6345,24 +6357,16 @@
       <c r="U51" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>https://betonastaurageje.lt/</t>
-        </is>
-      </c>
+      <c r="V51" s="2" t="inlineStr"/>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="X51" s="2" t="inlineStr">
-        <is>
-          <t>https://betonastaurageje.lt/betonas/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr"/>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Vinido svetainė patvirtina Gaurės g. 32 adresą, betono gamybą ir betono mazgą.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6374,22 +6378,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>santvara-kedainiai</t>
+          <t>ekobetonas-marijampole</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>304915297</t>
+          <t>300636364</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>UAB Santvara</t>
+          <t>UAB Ekobetonas</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Santvara</t>
+          <t>Ekobetonas</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6399,24 +6403,24 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Kėdainiai</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Kėdainių r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Aruodų g. 34, Kėdainiai</t>
+          <t>Gamyklų g. 3, Marijampolė</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>55.2634747</v>
+        <v>54.5750142</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>23.9440384</v>
+        <v>23.3796805</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -6445,7 +6449,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Santvara betono gamyba</t>
+          <t>Ekobetonas betono gamyba</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -6461,22 +6465,22 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>https://santvara.eu/</t>
+          <t>https://ekobetonas.lt/</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>https://santvara.eu/</t>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>https://santvara.eu/</t>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
+          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6488,22 +6492,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>medis-ir-betonas-naujoji-akmene</t>
+          <t>rokbetonis-rokiskis</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>153074073</t>
+          <t>304184091</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>AB Medis ir betonas</t>
+          <t>MB Rokbetonis</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas</t>
+          <t>Rokbetonis</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6513,24 +6517,24 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Rokiškis</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Rokiškio r. sav.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>56.3143832</v>
+        <v>55.9525796</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>22.9130704</v>
+        <v>25.5624197</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -6559,7 +6563,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas gamyba</t>
+          <t>Rokbetonis betono gamyba</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -6571,7 +6575,7 @@
         </is>
       </c>
       <c r="U53" s="5" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="V53" s="2" t="inlineStr"/>
       <c r="W53" s="2" t="inlineStr">
@@ -6582,7 +6586,7 @@
       <c r="X53" s="2" t="inlineStr"/>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6594,22 +6598,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ekobetonas-marijampole</t>
+          <t>silutes-betonas-silute</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>300636364</t>
+          <t>177392928</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>UAB Ekobetonas</t>
+          <t>UAB Šilutės betonas</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas</t>
+          <t>Šilutės betonas</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6619,24 +6623,24 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Šilutė</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Šilutės r. sav.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Gamyklų g. 3, Marijampolė</t>
+          <t>Ramučių g. 1, Šilutė</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>54.5750142</v>
+        <v>55.3538641</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>23.3796805</v>
+        <v>21.4796635</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -6665,7 +6669,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas betono gamyba</t>
+          <t>Šilutės betono gamyba (Nebeaktyvus mazgas)</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -6673,57 +6677,53 @@
       <c r="S54" s="4" t="inlineStr"/>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Nebeaktyvus mazgas. Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U54" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>https://ekobetonas.lt/</t>
-        </is>
-      </c>
+      <c r="V54" s="2" t="inlineStr"/>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą. Mazgas pažymėtas nebeaktyviu pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>rokbetonis-rokiskis</t>
+          <t>kruszbet-lithuania-jure</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>304184091</t>
+          <t>305173596</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>MB Rokbetonis</t>
+          <t>UAB KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis</t>
+          <t>KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6733,24 +6733,24 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Rokiškis</t>
+          <t>Jūrė</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Rokiškio r. sav.</t>
+          <t>Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
+          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>55.9525796</v>
+        <v>54.7706307</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>25.5624197</v>
+        <v>23.4998409</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis betono gamyba</t>
+          <t>KRUSZBET Lithuania betono gamyba</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="U55" s="5" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="V55" s="2" t="inlineStr"/>
       <c r="W55" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       <c r="X55" s="2" t="inlineStr"/>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6814,49 +6814,49 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>silutes-betonas-silute</t>
+          <t>telsiu-keliai-telsiai</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>177392928</t>
+          <t>180200843</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilutės betonas</t>
+          <t>UAB Telšių keliai</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betonas</t>
+          <t>Telšių keliai</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Šilutė</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Šilutės r. sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Ramučių g. 1, Šilutė</t>
+          <t>Mažeikių g. 18, Telšiai</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>55.3538641</v>
+        <v>56.0004158</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>21.4796635</v>
+        <v>22.2581129</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -6885,102 +6885,108 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betono gamyba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
       <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="4" t="inlineStr"/>
+      <c r="S56" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
         </is>
       </c>
       <c r="U56" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V56" s="2" t="inlineStr"/>
+        <v>0.86</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/</t>
+        </is>
+      </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>kruszbet-lithuania-jure</t>
+          <t>vpa-laistai</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>305173596</t>
+          <t>110185819</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>UAB KRUSZBET Lithuania</t>
+          <t>UAB V. Paulius &amp; Associates</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania</t>
+          <t>VPA</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Jūrė</t>
+          <t>Laistai</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Kazlų Rūdos sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
+          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>54.7706307</v>
+        <v>55.636908</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>23.4998409</v>
+        <v>21.209254</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6995,98 +7001,116 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania betono gamyba</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="4" t="inlineStr"/>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>VPA betono mazgas Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U57" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vpa.lt/</t>
+        </is>
+      </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X57" s="2" t="inlineStr"/>
+          <t>https://www.vpa.lt/?Kontaktai=</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+        </is>
+      </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>telsiu-keliai-telsiai</t>
+          <t>c3-beton-baisogala</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>180200843</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>UAB Telšių keliai</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Telšių keliai</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Baisogala</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių g. 18, Telšiai</t>
+          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>56.0004158</v>
+        <v>55.6372</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>22.2581129</v>
+        <v>23.7183</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7101,108 +7125,118 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr"/>
-      <c r="R58" s="2" t="inlineStr"/>
-      <c r="S58" s="4" t="n">
-        <v>2</v>
+          <t>Baisiogala Plant</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="S58" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
+          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
         </is>
       </c>
       <c r="U58" s="5" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/</t>
+          <t>https://c3beton.com/</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>vpa-laistai</t>
+          <t>c3-beton-martiniskis</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>110185819</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>UAB V. Paulius &amp; Associates</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>VPA</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Laistai</t>
+          <t>Martiniškis</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
+          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>55.636908</v>
+        <v>55.1441659</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>21.209254</v>
+        <v>24.1869636</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Google Maps nuoroda</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7217,60 +7251,62 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Liebherr</t>
+          <t>Martiniškis Plant</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>3 m³</t>
+          <t>Ammann Elba Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S59" s="4" t="n">
-        <v>2</v>
+          <t>60–80 m³/val.</t>
+        </is>
+      </c>
+      <c r="S59" s="4" t="inlineStr">
+        <is>
+          <t>2x85 t</t>
+        </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>VPA betono mazgas Klaipėdos rajone.</t>
+          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U59" s="5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/</t>
+          <t>https://c3beton.com/</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/?Kontaktai=</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-baisogala</t>
+          <t>c3-beton-stasenai</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -7295,38 +7331,38 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Baisogala</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
+          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>55.6372</v>
+        <v>54.6493094</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>23.7183</v>
+        <v>25.3107972</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus adreso taškas pagal geokodavimą</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7341,27 +7377,27 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Baisiogala Plant</t>
+          <t>Vilnius Ušos g. Plant</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>Nissbau Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>60–80 m³/val.</t>
         </is>
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>2x85 t</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
+          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U60" s="5" t="n">
@@ -7384,7 +7420,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
+          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7396,7 +7432,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-martiniskis</t>
+          <t>c3-beton-runeikiai</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -7421,24 +7457,24 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis</t>
+          <t>Runeikiai</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
+          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>55.1441659</v>
+        <v>55.3327393</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>24.1869636</v>
+        <v>24.3501308</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -7467,7 +7503,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis Plant</t>
+          <t>Runeikiai Plant</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7522,22 +7558,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-stasenai</t>
+          <t>reljef-rukla</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>301731961</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>UAB Reljef</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>Reljef</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7547,38 +7583,38 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Rukla</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
+          <t>Rukla, Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>54.6493094</v>
+        <v>55.05225</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>25.3107972</v>
+        <v>24.4064167</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas pagal geokodavimą</t>
+          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
+          <t>Naudotojo pateiktos koordinatės</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7593,203 +7629,203 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Vilnius Ušos g. Plant</t>
+          <t>Ammann Elba</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Nissbau Euromix C120, 3 m³</t>
+          <t>Nenustatyta</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>60–80 m³/val.</t>
+          <t>Nenustatytas</t>
         </is>
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2x85 t</t>
+          <t>2x65 t</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
         </is>
       </c>
       <c r="U62" s="5" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
+          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-runeikiai</t>
+          <t>ponas-betonas-paraudondvariai</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
+          <t>306676006</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>UAB Ponas betonas</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Ponas betonas</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Konkurentas</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Paraudondvariai</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus r. sav.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>54.8321418</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>25.2755596</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Elkon</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
           <t>Nenurodyta viešai</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>C3 Betonas</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>C3 Betonas</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Runeikiai</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Kėdainių r. sav.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>55.3327393</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>24.3501308</v>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>C3 Betonas oficialus puslapis</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>https://c3beton.com/lt/betonas</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>Runeikiai Plant</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
-        </is>
-      </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>60–80 m³/val.</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>2x85 t</t>
+          <t>2 matomi oficialioje nuotraukoje</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
         </is>
       </c>
       <c r="U63" s="5" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.ponasbetonas.lt/#Apiemus</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>reljef-rukla</t>
+          <t>pabrades-betonas-pabrade</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>301731961</t>
+          <t>306177188</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>UAB Reljef</t>
+          <t>UAB Pabradės betonas</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Reljef</t>
+          <t>Pabradės betonas</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7799,38 +7835,38 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Rukla</t>
+          <t>Pabradė</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Švenčionių r. sav.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Rukla, Jonavos r. sav.</t>
+          <t>Vilniaus g. 161, Pabradė, LT-18177 Švenčionių r.</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>55.05225</v>
+        <v>54.9758768</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>24.4064167</v>
+        <v>25.7373849</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
+          <t>Tikslus oficialioje svetainėje pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos koordinatės</t>
+          <t>Oficiali Pabradės betono Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://maps.app.goo.gl/TQBCVR8DczDRvQaeA</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7845,77 +7881,77 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba</t>
+          <t>Liebherr (tikėtina)</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Nenustatyta</t>
+          <t>3 m³</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>Nenustatytas</t>
+          <t>60 m³/val.</t>
         </is>
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>2x65 t</t>
+          <t>3x65 t</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
+          <t>UAB Pabradės betonas Vilniaus g. 161, Pabradėje, gamina sertifikuotą normalųjį betoną ir oficialiai nurodo dirbanti 50 km spinduliu aplink Pabradę. Oficialios galerijos nuotraukose matoma stacionari gamybos bazė su trimis cemento silosais. Mazgo gamintojas tikėtinai Liebherr pagal oficialiose nuotraukose matomą Liebherr įrangą ir gamyklos konstrukcijos vizualinius požymius; gamintojo lentelė viešai neparodyta.</t>
         </is>
       </c>
       <c r="U64" s="5" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.pabradesbetonas.lt/</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.pabradesbetonas.lt/</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://www.pabradesbetonas.lt/galerija/</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
+          <t>Adresas, įmonės kodas ir betono gamyba patvirtinti oficialioje svetainėje bei viešame gamybos kontrolės sertifikate. Koordinatės paimtos iš oficialioje svetainėje pateiktos Google Maps nuorodos. Maišyklės tūris 3 m³, realus našumas 60 m³/val. ir silosai 3x65 t įrašyti pagal naudotojo pateiktą informaciją. Gamintojas Liebherr nurodytas kaip tikėtinas pagal oficialios galerijos nuotraukas; viešo gamintojo ženklinimo ant paties mazgo nerasta.</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ponas-betonas-paraudondvariai</t>
+          <t>alkesta-marijampole-vasaros</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>306676006</t>
+          <t>249672710</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>UAB Ponas betonas</t>
+          <t>UAB Alkesta</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Ponas betonas</t>
+          <t>Alkesta</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -7925,24 +7961,24 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Paraudondvariai</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
+          <t>Vasaros g. 14, Marijampolė, LT-68111</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>54.8321418</v>
+        <v>54.5686121</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>25.2755596</v>
+        <v>23.3895157</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -7956,7 +7992,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
+          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7971,77 +8007,73 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
+          <t>Elba</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>0,5 m³</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
-      <c r="S65" s="4" t="inlineStr">
-        <is>
-          <t>2 matomi oficialioje nuotraukoje</t>
-        </is>
-      </c>
+          <t>10 m³/val.</t>
+        </is>
+      </c>
+      <c r="S65" s="4" t="inlineStr"/>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
+          <t>UAB Alkesta Marijampolės betono mazgas Vasaros g. 14. Mazgo gamintojas Elba, maišyklė 0,5 m³, našumas 10 m³/val.</t>
         </is>
       </c>
       <c r="U65" s="5" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/</t>
+          <t>https://alkesta.lt/</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/#Apiemus</t>
+          <t>https://spsc.lt/registrai/regsapp/ser_produktai_view.php?editid1=13061</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/</t>
+          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
+          <t>Oficialus SPSC sertifikatų registras patvirtina UAB Alkesta betono gamybą ir gamybos vietą Vasaros g. 14, Marijampolėje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris ir našumas įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>pabrades-betonas-pabrade</t>
+          <t>gevalda-visincia</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>306177188</t>
+          <t>302592895</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>UAB Pabradės betonas</t>
+          <t>UAB Gevalda</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Pabradės betonas</t>
+          <t>Gevalda</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -8051,38 +8083,38 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Pabradė</t>
+          <t>Visinčia</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Švenčionių r. sav.</t>
+          <t>Šalčininkų r. sav.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus g. 161, Pabradė, LT-18177 Švenčionių r.</t>
+          <t>Visinčia, Pabarės sen., Šalčininkų r. sav.</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>54.9758768</v>
+        <v>54.4122467</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>25.7373849</v>
+        <v>25.1449142</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Tikslus oficialioje svetainėje pateiktos Google Maps nuorodos taškas</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Pabradės betono Google Maps nuoroda</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/TQBCVR8DczDRvQaeA</t>
+          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8097,7 +8129,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Liebherr (tikėtina)</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8112,35 +8144,35 @@
       </c>
       <c r="S66" s="4" t="inlineStr">
         <is>
-          <t>3x65 t</t>
+          <t>2x85 t</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>UAB Pabradės betonas Vilniaus g. 161, Pabradėje, gamina sertifikuotą normalųjį betoną ir oficialiai nurodo dirbanti 50 km spinduliu aplink Pabradę. Oficialios galerijos nuotraukose matoma stacionari gamybos bazė su trimis cemento silosais. Mazgo gamintojas tikėtinai Liebherr pagal oficialiose nuotraukose matomą Liebherr įrangą ir gamyklos konstrukcijos vizualinius požymius; gamintojo lentelė viešai neparodyta.</t>
+          <t>UAB Gevalda mobilus betono mazgas Visinčioje. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U66" s="5" t="n">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>https://www.pabradesbetonas.lt/</t>
+          <t>https://www.gevalda.lt/</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>https://www.pabradesbetonas.lt/</t>
+          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>https://www.pabradesbetonas.lt/galerija/</t>
+          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>Adresas, įmonės kodas ir betono gamyba patvirtinti oficialioje svetainėje bei viešame gamybos kontrolės sertifikate. Koordinatės paimtos iš oficialioje svetainėje pateiktos Google Maps nuorodos. Maišyklės tūris 3 m³, realus našumas 60 m³/val. ir silosai 3x65 t įrašyti pagal naudotojo pateiktą informaciją. Gamintojas Liebherr nurodytas kaip tikėtinas pagal oficialios galerijos nuotraukas; viešo gamintojo ženklinimo ant paties mazgo nerasta.</t>
+          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris, našumas ir silosai įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8152,22 +8184,22 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>alkesta-marijampole-vasaros</t>
+          <t>gevalda-kaunas-palemonas</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>249672710</t>
+          <t>302592895</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>UAB Alkesta</t>
+          <t>UAB Gevalda</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Alkesta</t>
+          <t>Gevalda</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8177,24 +8209,24 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Vasaros g. 14, Marijampolė, LT-68111</t>
+          <t>Kražantės g., Palemonas, Kaunas</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
-        <v>54.5686121</v>
+        <v>54.918</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>23.3895157</v>
+        <v>24.063</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8240,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
+          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8223,23 +8255,27 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Elba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>0,5 m³</t>
+          <t>3 m³</t>
         </is>
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>10 m³/val.</t>
-        </is>
-      </c>
-      <c r="S67" s="4" t="inlineStr"/>
+          <t>60 m³/val.</t>
+        </is>
+      </c>
+      <c r="S67" s="4" t="inlineStr">
+        <is>
+          <t>2x85 t</t>
+        </is>
+      </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>UAB Alkesta Marijampolės betono mazgas Vasaros g. 14. Mazgo gamintojas Elba, maišyklė 0,5 m³, našumas 10 m³/val.</t>
+          <t>UAB Gevalda mobilus betono mazgas Palemone, Kaune. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U67" s="5" t="n">
@@ -8247,284 +8283,32 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>https://alkesta.lt/</t>
+          <t>https://www.gevalda.lt/</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>https://spsc.lt/registrai/regsapp/ser_produktai_view.php?editid1=13061</t>
+          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
+          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>Oficialus SPSC sertifikatų registras patvirtina UAB Alkesta betono gamybą ir gamybos vietą Vasaros g. 14, Marijampolėje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris ir našumas įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija ir analogiški techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>gevalda-visincia</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>302592895</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>UAB Gevalda</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Gevalda</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Visinčia</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Šalčininkų r. sav.</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Visinčia, Pabarės sen., Šalčininkų r. sav.</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>54.4122467</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>25.1449142</v>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/val.</t>
-        </is>
-      </c>
-      <c r="S68" s="4" t="inlineStr">
-        <is>
-          <t>2x85 t</t>
-        </is>
-      </c>
-      <c r="T68" s="2" t="inlineStr">
-        <is>
-          <t>UAB Gevalda mobilus betono mazgas Visinčioje. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
-        </is>
-      </c>
-      <c r="U68" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="V68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gevalda.lt/</t>
-        </is>
-      </c>
-      <c r="W68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
-        </is>
-      </c>
-      <c r="X68" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
-        </is>
-      </c>
-      <c r="Y68" s="2" t="inlineStr">
-        <is>
-          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris, našumas ir silosai įrašyti pagal naudotojo pateiktą informaciją.</t>
-        </is>
-      </c>
-      <c r="Z68" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>gevalda-kaunas-palemonas</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>302592895</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>UAB Gevalda</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Gevalda</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Kaunas</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Kauno m. sav.</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Kražantės g., Palemonas, Kaunas</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>54.918</v>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>24.063</v>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/val.</t>
-        </is>
-      </c>
-      <c r="S69" s="4" t="inlineStr">
-        <is>
-          <t>2x85 t</t>
-        </is>
-      </c>
-      <c r="T69" s="2" t="inlineStr">
-        <is>
-          <t>UAB Gevalda mobilus betono mazgas Palemone, Kaune. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
-        </is>
-      </c>
-      <c r="U69" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="V69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gevalda.lt/</t>
-        </is>
-      </c>
-      <c r="W69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
-        </is>
-      </c>
-      <c r="X69" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
-        </is>
-      </c>
-      <c r="Y69" s="2" t="inlineStr">
-        <is>
-          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija ir analogiški techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
-        </is>
-      </c>
-      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z69"/>
+  <autoFilter ref="A1:Z67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8613,7 +8397,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24T04:22:17.382218+00:00</t>
+          <t>2026-09-24T04:42:42.583222+00:00</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8452,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24T04:22:17.383221+00:00</t>
+          <t>2026-09-24T04:42:42.583222+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8682,7 +8466,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -3472,18 +3472,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>inhus-senieji-trakai</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr"/>
+          <t>betonika-senieji-trakai</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>135551936</t>
+        </is>
+      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>UAB INHUS Lietuva</t>
+          <t>Betonika UAB</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>INHUS</t>
+          <t>Betonika</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3503,7 +3507,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Plačioji g. 27, Senieji Trakai</t>
+          <t>Plačioji g. 27, Senųjų Trakų km., LT-21146</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
@@ -3539,7 +3543,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>INHUS gelžbetonio gamykla</t>
+          <t>Betonika Trakų gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -3547,31 +3551,35 @@
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiamas surenkamojo gelžbetonio konstrukcijų gamintojas.</t>
+          <t>Surenkamojo gelžbetonio gamykla. Gaminamos perdangos plokštės, kolonos, sijos, sienų elementai, laiptų ir stogo plokštės; įmonė nurodo, kad prekinio betono neparduoda.</t>
         </is>
       </c>
       <c r="U26" s="5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
+          <t>https://betonika.lt/</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
+          <t>https://betonika.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>https://inhus.eu/</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr"/>
+          <t>https://betonika.lt/apie-mus/</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>Oficialiame kontaktų puslapyje ši vieta įvardyta kaip Trakų gamykla; nurodyta „BETONO NEPARDUODAME“.</t>
+        </is>
+      </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -8397,7 +8405,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24T04:42:42.583222+00:00</t>
+          <t>2026-09-25T06:01:50.565312+00:00</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24T04:42:42.583222+00:00</t>
+          <t>2026-09-25T06:01:50.565312+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$67</definedName>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25T06:01:50.565312+00:00</t>
+          <t>2026-09-28T11:25:34.092109+00:00</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25T06:01:50.565312+00:00</t>
+          <t>2026-09-28T11:25:34.092537+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -8405,7 +8405,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28T11:25:34.092109+00:00</t>
+          <t>2026-10-05T12:01:10.504500+00:00</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28T11:25:34.092537+00:00</t>
+          <t>2026-10-05T12:01:10.504942+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -8405,7 +8405,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-05T12:01:10.504500+00:00</t>
+          <t>2026-10-12T12:42:52.334852+00:00</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05T12:01:10.504942+00:00</t>
+          <t>2026-10-12T12:42:52.335562+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -169,8 +169,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z67" headerRowCount="1">
-  <autoFilter ref="A1:Z67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ImonesTable" displayName="ImonesTable" ref="A1:Z66" headerRowCount="1">
+  <autoFilter ref="A1:Z66"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Įrašo ID"/>
     <tableColumn id="2" name="Įmonės kodas"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z67"/>
+  <dimension ref="A1:Z66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -509,10 +509,10 @@
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="42" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
+    <col width="41" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="32" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="33" customWidth="1" min="17" max="17"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
@@ -1470,7 +1470,11 @@
           <t>60 m³/h</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>4 vnt. (2×120 t, 2×60 t)</t>
+        </is>
+      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
           <t>Viešai skelbiamas Betono centro betono mazgas Klaipėdoje.</t>
@@ -1496,12 +1500,12 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame Betono centro kontaktų puslapyje patvirtintas Klaipėdos padalinys. Mazgo techniniai duomenys patikslinti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficialiame Betono centro kontaktų puslapyje patvirtintas Klaipėdos padalinys. Mazgo techniniai duomenys patikslinti pagal naudotojo pateiktą informaciją. Silosai: 4 vnt. (2×120 t, 2×60 t), pagal naudotojo 2026-10-14 pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4952,18 +4956,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>betono-zona-klaipeda</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr"/>
+          <t>topbeton-panevezys</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>307083610</t>
+        </is>
+      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>UAB Betono zona</t>
+          <t>UAB Topbeton</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Topbeton</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4973,24 +4981,24 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Klaipėda</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos m. sav.</t>
+          <t>Panevėžio m. sav.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g. 6, Klaipėda</t>
+          <t>Beržų g. 5C, Panevėžys</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.7549809</v>
+        <v>55.7168572</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>21.150509</v>
+        <v>24.3617863</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -5009,17 +5017,17 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Betono gaminiai</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Betono zona</t>
+          <t>Topbeton betono mazgas</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -5027,30 +5035,30 @@
       <c r="S39" s="4" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono gaminių veikla Klaipėdoje.</t>
+          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U39" s="5" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://topbeton.lt/</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>https://betonozona.lt/</t>
+          <t>https://www.topbeton.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>Patikrinti, ar įmonė pati gamina, ar tik prekiauja betono gaminiais.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5062,22 +5070,18 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>topbeton-panevezys</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>307083610</t>
-        </is>
-      </c>
+          <t>gelzbetonio-gamyba-panevezys</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>UAB Topbeton</t>
+          <t>MB Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Topbeton</t>
+          <t>Gelžbetonio gamyba</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5097,14 +5101,14 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Beržų g. 5C, Panevėžys</t>
+          <t>S. Kerbedžio g. 52, Panevėžys</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>55.7168572</v>
+        <v>55.7409491</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>24.3617863</v>
+        <v>24.3803541</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -5123,17 +5127,17 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Gelžbetonis</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Topbeton betono mazgas</t>
+          <t>Gelžbetonio gamyba Panevėžyje</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -5141,30 +5145,30 @@
       <c r="S40" s="4" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
         </is>
       </c>
       <c r="U40" s="5" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>https://topbeton.lt/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>https://www.topbeton.lt/kontaktai/</t>
+          <t>https://gelzbetoniogamyba.lt/</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Beržų g. 5C adresą.</t>
+          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5176,18 +5180,18 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>gelzbetonio-gamyba-panevezys</t>
+          <t>inroma-pakruojis</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>MB Gelžbetonio gamyba</t>
+          <t>UAB Inroma</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba</t>
+          <t>Inroma</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5197,24 +5201,24 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Pakruojis</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Panevėžio m. sav.</t>
+          <t>Pakruojo r. sav.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>S. Kerbedžio g. 52, Panevėžys</t>
+          <t>Pramonės g. 5B, Pakruojis</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>55.7409491</v>
+        <v>55.9763263</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>24.3803541</v>
+        <v>23.8584712</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -5233,17 +5237,17 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Gelžbetonio gamyba Panevėžyje</t>
+          <t>Inroma betono mazgas</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -5251,7 +5255,7 @@
       <c r="S41" s="4" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama gelžbetonio gaminių gamyba Panevėžyje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
         </is>
       </c>
       <c r="U41" s="5" t="n">
@@ -5259,22 +5263,22 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>https://gelzbetoniogamyba.lt/</t>
+          <t>https://inroma.lt/</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti ryšį su kitomis S. Kerbedžio g. 52 įmonėmis.</t>
+          <t>Reikia patikslinti našumą.</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5286,18 +5290,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>inroma-pakruojis</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr"/>
+          <t>utenos-betonas-utena</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>300904691</t>
+        </is>
+      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>UAB Inroma</t>
+          <t>UAB Utenos betonas</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Inroma</t>
+          <t>Utenos betonas</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5307,24 +5315,24 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Pakruojis</t>
+          <t>Utena</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Pakruojo r. sav.</t>
+          <t>Utenos r. sav.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Pramonės g. 5B, Pakruojis</t>
+          <t>Metalo g. 9B, Utena</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>55.9763263</v>
+        <v>55.4947607</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>23.8584712</v>
+        <v>25.6225075</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -5353,7 +5361,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Inroma betono mazgas</t>
+          <t>Utenos betono mazgas</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -5361,30 +5369,30 @@
       <c r="S42" s="4" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Pakruojyje.</t>
+          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
         </is>
       </c>
       <c r="U42" s="5" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://utenosbetonas.lt/</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>https://inroma.lt/</t>
+          <t>https://www.utenosbetonas.lt/kontaktai/</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti našumą.</t>
+          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5396,22 +5404,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>utenos-betonas-utena</t>
+          <t>sbetonas-jonava</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>300904691</t>
+          <t>300902683</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>UAB Utenos betonas</t>
+          <t>UAB Sbetonas</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Utenos betonas</t>
+          <t>Sbetonas</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5421,24 +5429,24 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Utena</t>
+          <t>Jonava</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Utenos r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Metalo g. 9B, Utena</t>
+          <t>Skarulių g. 58, Jonava</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>55.4947607</v>
+        <v>55.0786452</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>25.6225075</v>
+        <v>24.3199072</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5475,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Utenos betono mazgas</t>
+          <t>Sbetonas betono mazgas</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -5475,7 +5483,7 @@
       <c r="S43" s="4" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama betono mišinių veikla Utenoje.</t>
+          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
         </is>
       </c>
       <c r="U43" s="5" t="n">
@@ -5483,22 +5491,22 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>https://utenosbetonas.lt/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>https://www.utenosbetonas.lt/kontaktai/</t>
+          <t>https://sbetonas.lt/</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>Oficialus kontaktų puslapis patvirtina Metalo g. 9B adresą.</t>
+          <t>Papildomai rasta pagal prekinio betono požymį.</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5510,22 +5518,18 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>sbetonas-jonava</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>300902683</t>
-        </is>
-      </c>
+          <t>kalcitas-naujoji-akmene</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>UAB Sbetonas</t>
+          <t>AB Kalcitas</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas</t>
+          <t>Kalcitas</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5535,24 +5539,24 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Jonava</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Skarulių g. 58, Jonava</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>55.0786452</v>
+        <v>56.3143832</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>24.3199072</v>
+        <v>22.9130704</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -5581,7 +5585,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Sbetonas betono mazgas</t>
+          <t>Kalcitas betono mišinių gamybos linija</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -5589,30 +5593,26 @@
       <c r="S44" s="4" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>Viešai skelbiama prekinio betono gamyba Jonavoje.</t>
+          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
         </is>
       </c>
       <c r="U44" s="5" t="n">
         <v>0.78</v>
       </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>https://sbetonas.lt/</t>
-        </is>
-      </c>
+      <c r="V44" s="2" t="inlineStr"/>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>https://sbetonas.lt/</t>
+          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta pagal prekinio betono požymį.</t>
+          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5624,18 +5624,18 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>kalcitas-naujoji-akmene</t>
+          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>AB Kalcitas</t>
+          <t>UAB Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas</t>
+          <t>Gelgaudiškio gelžbetonis</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5645,24 +5645,24 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Gelgaudiškis</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Šakių r. sav.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>56.3143832</v>
+        <v>55.07067</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>22.9130704</v>
+        <v>22.976723</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -5671,27 +5671,27 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>GLG kontaktų puslapis</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
+          <t>Betono mišiniai ir gelžbetonis</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Kalcitas betono mišinių gamybos linija</t>
+          <t>Gelgaudiškio gelžbetonio gamykla</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
@@ -5699,26 +5699,30 @@
       <c r="S45" s="4" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>Viešame kataloge nurodomi betonas, betono mišiniai ir betono gamybos linija Naujojoje Akmenėje.</t>
+          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
         </is>
       </c>
       <c r="U45" s="5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>https://glg.lt/</t>
+        </is>
+      </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://glg.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>https://www.1551.lt/kalcitas-ab-betonas-betono-misiniai-betono-gamybos-linija-technikos-nuoma-naujojoje-akmeneje-59982/</t>
+          <t>https://glg.lt/betonas/betono-misiniai/</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>Reikia patikslinti, ar veikla yra nuolat aktyvi.</t>
+          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5730,45 +5734,49 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>gelgaudiskio-gelzbetonis-gelgaudiskis</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr"/>
+          <t>ginfa-kutiskiai</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>302680943</t>
+        </is>
+      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>UAB Gelgaudiškio gelžbetonis</t>
+          <t>UAB GinFa</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonis</t>
+          <t>GinFa</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta</t>
+          <t>Papildomai rasta EVRK 23.63</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškis</t>
+          <t>Kutiškiai</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Šakių r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Vakarų g. 33 D, 71431, Gelgaudiškis</t>
+          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>55.07067</v>
+        <v>55.8326273</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>22.976723</v>
+        <v>23.4995317</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5777,27 +5785,27 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>GLG kontaktų puslapis</t>
+          <t>Lietuvos geolokatorius</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
+          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>precast_concrete</t>
+          <t>ready_mix_concrete</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai ir gelžbetonis</t>
+          <t>Betono mišiniai</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Gelgaudiškio gelžbetonio gamykla</t>
+          <t>GinFa betono gamyba</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -5805,30 +5813,22 @@
       <c r="S46" s="4" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>Įmonė gamina gelžbetonio gaminius, prekinį ir hidrotechninį betoną bei smėlbetonio mišinius.</t>
+          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
         </is>
       </c>
       <c r="U46" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/</t>
-        </is>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr"/>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>https://glg.lt/kontaktai/</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t>https://glg.lt/betonas/betono-misiniai/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>Patikslinta pagal oficialų glg.lt kontaktų ir įmonės aprašymo puslapius.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5840,22 +5840,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ginfa-kutiskiai</t>
+          <t>antano-gribino-imone-prienai</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>302680943</t>
+          <t>170687267</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>UAB GinFa</t>
+          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>GinFa</t>
+          <t>Antano Gribino įmonė</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5865,24 +5865,24 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Kutiškiai</t>
+          <t>Prienai</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Prienų r. sav.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Alyvų g. 8, Kutiškiai, Radviliškio r.</t>
+          <t>Kęstučio g. 95A, Prienai</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>55.8326273</v>
+        <v>54.6523184</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>23.4995317</v>
+        <v>23.9696591</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>GinFa betono gamyba</t>
+          <t>Antano Gribino įmonės betono gamyba</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -5946,22 +5946,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>antano-gribino-imone-prienai</t>
+          <t>vinido-taurage</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>170687267</t>
+          <t>306258220</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>IĮ Antano Gribino gamybos ir komercinės veiklos įmonė</t>
+          <t>UAB Vinido</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Antano Gribino įmonė</t>
+          <t>Vinido</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5971,24 +5971,24 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Prienai</t>
+          <t>Tauragė</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Prienų r. sav.</t>
+          <t>Tauragės r. sav.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Kęstučio g. 95A, Prienai</t>
+          <t>Gaurės g. 32, Tauragė</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>54.6523184</v>
+        <v>55.2492204</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>23.9696591</v>
+        <v>22.3185845</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -6015,59 +6015,67 @@
           <t>Betono mišiniai</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>Antano Gribino įmonės betono gamyba</t>
-        </is>
-      </c>
+      <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>200–250 m³/dieną (gamyba ir pristatymas)</t>
+        </is>
+      </c>
       <c r="S48" s="4" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Nuosavas betono mazgas Tauragėje. Įmonė skelbia galinti pagaminti ir pristatyti iki 200–250 m³ betono per dieną; užsakius nuo 50 m³ dirba ir savaitgaliais. Teikia betono gamybos ir tiekimo, betono siurblio nuomos bei betono gaminių gamybos paslaugas.</t>
         </is>
       </c>
       <c r="U48" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/</t>
+        </is>
+      </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X48" s="2" t="inlineStr"/>
+          <t>https://betonastaurageje.lt/kontaktai/</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>https://betonastaurageje.lt/uab-vinido-betonas/</t>
+        </is>
+      </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Oficiali svetainė patvirtina įmonės kodą 306258220, Gaurės g. 32 adresą ir nuosavą betono mazgą. Kontaktai: +370 644 45799, info@uabvinido.lt. 200–250 m³/dieną yra skelbiama gamybos ir pristatymo apimtis, ne valandinis mazgo našumas. Mazgo gamintojas, maišyklė ir silosai viešai nenurodyti.</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>vinido-taurage</t>
+          <t>santvara-kedainiai</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>306258220</t>
+          <t>304915297</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>UAB Vinido</t>
+          <t>UAB Santvara</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Vinido</t>
+          <t>Santvara</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -6077,24 +6085,24 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Tauragė</t>
+          <t>Kėdainiai</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Tauragės r. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Gaurės g. 32, Tauragė</t>
+          <t>Aruodų g. 34, Kėdainiai</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>55.2492204</v>
+        <v>55.2634747</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>22.3185845</v>
+        <v>23.9440384</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -6123,7 +6131,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Vinido betono gamyba</t>
+          <t>Santvara betono gamyba</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -6139,22 +6147,22 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/kontaktai/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>https://betonastaurageje.lt/betonas/</t>
+          <t>https://santvara.eu/</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Vinido svetainė patvirtina Gaurės g. 32 adresą, betono gamybą ir betono mazgą.</t>
+          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6166,22 +6174,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>santvara-kedainiai</t>
+          <t>medis-ir-betonas-naujoji-akmene</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>304915297</t>
+          <t>153074073</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>UAB Santvara</t>
+          <t>AB Medis ir betonas</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Santvara</t>
+          <t>Medis ir betonas</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -6191,24 +6199,24 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Kėdainiai</t>
+          <t>Naujoji Akmenė</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Kėdainių r. sav.</t>
+          <t>Akmenės r. sav.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Aruodų g. 34, Kėdainiai</t>
+          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>55.2634747</v>
+        <v>56.3143832</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>23.9440384</v>
+        <v>22.9130704</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -6237,7 +6245,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Santvara betono gamyba</t>
+          <t>Medis ir betonas gamyba</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -6251,24 +6259,16 @@
       <c r="U50" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
+      <c r="V50" s="2" t="inlineStr"/>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
-      <c r="X50" s="2" t="inlineStr">
-        <is>
-          <t>https://santvara.eu/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr"/>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Santvara svetainė patvirtina Aruodų g. 34 adresą ir betono bei birių medžiagų veiklą.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6280,22 +6280,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>medis-ir-betonas-naujoji-akmene</t>
+          <t>ekobetonas-marijampole</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>153074073</t>
+          <t>300636364</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>AB Medis ir betonas</t>
+          <t>UAB Ekobetonas</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas</t>
+          <t>Ekobetonas</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6305,24 +6305,24 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Naujoji Akmenė</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Akmenės r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>J. Dalinkevičiaus g. 2, Naujoji Akmenė</t>
+          <t>Gamyklų g. 3, Marijampolė</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>56.3143832</v>
+        <v>54.5750142</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>22.9130704</v>
+        <v>23.3796805</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Medis ir betonas gamyba</t>
+          <t>Ekobetonas betono gamyba</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -6365,16 +6365,24 @@
       <c r="U51" s="5" t="n">
         <v>0.82</v>
       </c>
-      <c r="V51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>https://ekobetonas.lt/</t>
+        </is>
+      </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X51" s="2" t="inlineStr"/>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
+        </is>
+      </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6386,22 +6394,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ekobetonas-marijampole</t>
+          <t>rokbetonis-rokiskis</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>300636364</t>
+          <t>304184091</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>UAB Ekobetonas</t>
+          <t>MB Rokbetonis</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas</t>
+          <t>Rokbetonis</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6411,24 +6419,24 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Rokiškis</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Rokiškio r. sav.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Gamyklų g. 3, Marijampolė</t>
+          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>54.5750142</v>
+        <v>55.9525796</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>23.3796805</v>
+        <v>25.5624197</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -6457,7 +6465,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Ekobetonas betono gamyba</t>
+          <t>Rokbetonis betono gamyba</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -6469,26 +6477,18 @@
         </is>
       </c>
       <c r="U52" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>https://ekobetonas.lt/</t>
-        </is>
-      </c>
+        <v>0.72</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr"/>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
-        </is>
-      </c>
-      <c r="X52" s="2" t="inlineStr">
-        <is>
-          <t>https://ekobetonas.lt/kontaktai-betono-gamyba-armaturinis-plienas/</t>
-        </is>
-      </c>
+          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr"/>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>Oficialus Ekobetonas kontaktų puslapis patvirtina Gamyklų g. 3 adresą ir betono užsakymų kontaktus.</t>
+          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6500,22 +6500,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>rokbetonis-rokiskis</t>
+          <t>kruszbet-lithuania-jure</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>304184091</t>
+          <t>305173596</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>MB Rokbetonis</t>
+          <t>UAB KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis</t>
+          <t>KRUSZBET Lithuania</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -6525,24 +6525,24 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Rokiškis</t>
+          <t>Jūrė</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Rokiškio r. sav.</t>
+          <t>Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Vydūno g. 12A, Parokiškė, Rokiškio r.</t>
+          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>55.9525796</v>
+        <v>54.7706307</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>25.5624197</v>
+        <v>23.4998409</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Rokbetonis betono gamyba</t>
+          <t>KRUSZBET Lithuania betono gamyba</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="U53" s="5" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="V53" s="2" t="inlineStr"/>
       <c r="W53" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       <c r="X53" s="2" t="inlineStr"/>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>Adresas rastas viešuose kataloguose, bet geokoduotas tik iki Rokiškio miesto taško; reikia patikslinti tikslų betono mazgo GPS.</t>
+          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6606,49 +6606,49 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>silutes-betonas-silute</t>
+          <t>telsiu-keliai-telsiai</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>177392928</t>
+          <t>180200843</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>UAB Šilutės betonas</t>
+          <t>UAB Telšių keliai</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betonas</t>
+          <t>Telšių keliai</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Šilutė</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Šilutės r. sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Ramučių g. 1, Šilutė</t>
+          <t>Mažeikių g. 18, Telšiai</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>55.3538641</v>
+        <v>56.0004158</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>21.4796635</v>
+        <v>22.2581129</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -6677,102 +6677,108 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Šilutės betono gamyba (Nebeaktyvus mazgas)</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
       <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="4" t="inlineStr"/>
+      <c r="S54" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>Nebeaktyvus mazgas. Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
         </is>
       </c>
       <c r="U54" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V54" s="2" t="inlineStr"/>
+        <v>0.86</v>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tkeliai.lt/</t>
+        </is>
+      </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>https://fsaskaita.lt/imone/uzdaroji-akcine-bendrove-silutes-betonas-177392928</t>
+          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą. Mazgas pažymėtas nebeaktyviu pagal naudotojo pateiktą informaciją.</t>
+          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>kruszbet-lithuania-jure</t>
+          <t>vpa-laistai</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>305173596</t>
+          <t>110185819</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>UAB KRUSZBET Lithuania</t>
+          <t>UAB V. Paulius &amp; Associates</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania</t>
+          <t>VPA</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Papildomai rasta EVRK 23.63</t>
+          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Jūrė</t>
+          <t>Laistai</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Kazlų Rūdos sav.</t>
+          <t>Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Medelyno g. 30A, Jūrė, Kazlų Rūdos sav.</t>
+          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>54.7706307</v>
+        <v>55.636908</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>23.4998409</v>
+        <v>21.209254</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6787,98 +6793,116 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>KRUSZBET Lithuania betono gamyba</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="4" t="inlineStr"/>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>60-80 m³/h</t>
+        </is>
+      </c>
+      <c r="S55" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>Registrų centro/VDA atviruose duomenyse pagrindinė veikla nurodyta kaip prekinio betono mišinio gamyba (EVRK 23.63).</t>
+          <t>VPA betono mazgas Klaipėdos rajone.</t>
         </is>
       </c>
       <c r="U55" s="5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="V55" s="2" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vpa.lt/</t>
+        </is>
+      </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>https://data.gov.lt/dataset/juridiniu-asmenu-ekonomines-veiklos-rusys-ir-instituciniai-sektoriai/</t>
-        </is>
-      </c>
-      <c r="X55" s="2" t="inlineStr"/>
+          <t>https://www.vpa.lt/?Kontaktai=</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+        </is>
+      </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>Adresas geokoduotas pagal viešai randamą įmonės adresą; betono mazgo vietą verta patikslinti atskiru šaltiniu.</t>
+          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>telsiu-keliai-telsiai</t>
+          <t>c3-beton-baisogala</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>180200843</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UAB Telšių keliai</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Telšių keliai</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Telšiai</t>
+          <t>Baisogala</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Telšių r. sav.</t>
+          <t>Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Mažeikių g. 18, Telšiai</t>
+          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>56.0004158</v>
+        <v>55.6372</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>22.2581129</v>
+        <v>23.7183</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Lietuvos geolokatorius</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>https://hub.arcgis.com/content/b9e27b4266524b39bc651d6a26480b87</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6893,108 +6917,118 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="4" t="n">
-        <v>2</v>
+          <t>Baisiogala Plant</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
+      </c>
+      <c r="S56" s="4" t="inlineStr">
+        <is>
+          <t>Nenurodyta viešai</t>
+        </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame įmonės puslapyje skelbiama betono mišinių gamyba ir prekyba. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai.</t>
+          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
         </is>
       </c>
       <c r="U56" s="5" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/</t>
+          <t>https://c3beton.com/</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>https://www.tkeliai.lt/kitos-paslaugos/</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal naudotojo informaciją; veikla patvirtinta oficialiame lietuviškame įmonės puslapyje. Naudotojo duomenimis, betono mazgas vadinasi Elkon, yra 2 silosai. Koordinatės nustatytos Lietuvos geolokatoriumi pagal Mažeikių g. 18 adresą.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>vpa-laistai</t>
+          <t>c3-beton-martiniskis</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>110185819</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>UAB V. Paulius &amp; Associates</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>VPA</t>
+          <t>C3 Betonas</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Papildomai įtraukta pagal naudotojo informaciją</t>
+          <t>Konkurentas</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Laistai</t>
+          <t>Martiniškis</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Klaipėdos r. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Stariškės g. 9, Laistų k., Dovilų sen., Klaipėdos r. sav.</t>
+          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>55.636908</v>
+        <v>55.1441659</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>21.209254</v>
+        <v>24.1869636</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos Google Maps nuorodos taškas</t>
+          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Google Maps nuoroda</t>
+          <t>C3 Betonas oficialus puslapis</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7009,60 +7043,62 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Liebherr</t>
+          <t>Martiniškis Plant</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>3 m³</t>
+          <t>Ammann Elba Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>60-80 m³/h</t>
-        </is>
-      </c>
-      <c r="S57" s="4" t="n">
-        <v>2</v>
+          <t>60–80 m³/val.</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="inlineStr">
+        <is>
+          <t>2x85 t</t>
+        </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>VPA betono mazgas Klaipėdos rajone.</t>
+          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U57" s="5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/</t>
+          <t>https://c3beton.com/</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>https://www.vpa.lt/?Kontaktai=</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/2geTBr4zmdrmPY548</t>
+          <t>https://c3beton.com/lt/betonas</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>Vieta nustatyta pagal naudotojo pateiktą Google Maps nuorodą. VPA kontaktų puslapis nurodo Stariškės g. 9, Laistų k. adresą. Techniniai mazgo duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-baisogala</t>
+          <t>c3-beton-stasenai</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -7087,38 +7123,38 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Baisogala</t>
+          <t>Vilnius</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Radviliškio r. sav.</t>
+          <t>Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Dvaro g., Baisogala, Radviliškio r. sav.</t>
+          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>55.6372</v>
+        <v>54.6493094</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>23.7183</v>
+        <v>25.3107972</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
+          <t>Tikslus adreso taškas pagal geokodavimą</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas oficialus puslapis</t>
+          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7133,27 +7169,27 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Baisiogala Plant</t>
+          <t>Vilnius Ušos g. Plant</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>Nissbau Euromix C120, 3 m³</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>60–80 m³/val.</t>
         </is>
       </c>
       <c r="S58" s="4" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>2x85 t</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame C3 Betonas puslapyje ši vieta rodoma kaip C3 betono gamykla Lietuvos tinkle. C3 nurodo, kad aplink gamyklas taikomas 50 km pristatymo spindulys.</t>
+          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U58" s="5" t="n">
@@ -7176,7 +7212,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Įmonės kodas ir techniniai mazgo duomenys viešai nenurodyti.</t>
+          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7188,7 +7224,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-martiniskis</t>
+          <t>c3-beton-runeikiai</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -7213,24 +7249,24 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis</t>
+          <t>Runeikiai</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Vanagiškiai, Kulvos sen., Jonavos r. sav.</t>
+          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>55.1441659</v>
+        <v>55.3327393</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>24.1869636</v>
+        <v>24.3501308</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -7259,7 +7295,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Martiniškis Plant</t>
+          <t>Runeikiai Plant</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7314,22 +7350,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-stasenai</t>
+          <t>reljef-rukla</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>301731961</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>UAB Reljef</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>C3 Betonas</t>
+          <t>Reljef</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7339,38 +7375,38 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Vilnius</t>
+          <t>Rukla</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus m. sav.</t>
+          <t>Jonavos r. sav.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Ušos g. 21, Vilnius, 02121 Vilniaus m. sav.</t>
+          <t>Rukla, Jonavos r. sav.</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>54.6493094</v>
+        <v>55.05225</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>25.3107972</v>
+        <v>24.4064167</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Tikslus adreso taškas pagal geokodavimą</t>
+          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>ArcGIS geokodavimas pagal naudotojo pateiktą adresą</t>
+          <t>Naudotojo pateiktos koordinatės</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>https://geocode.arcgis.com/arcgis/rest/services/World/GeocodeServer/findAddressCandidates</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7385,203 +7421,203 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Vilnius Ušos g. Plant</t>
+          <t>Ammann Elba</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Nissbau Euromix C120, 3 m³</t>
+          <t>Nenustatyta</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>60–80 m³/val.</t>
+          <t>Nenustatytas</t>
         </is>
       </c>
       <c r="S60" s="4" t="inlineStr">
         <is>
-          <t>2x85 t</t>
+          <t>2x65 t</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Nissbau Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
         </is>
       </c>
       <c r="U60" s="5" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.reljef.lt/</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>Perkelta iš Stašėnų lokacijos į Ušos g. 21, Vilnius pagal naudotojo pateiktą informaciją. Maišyklė pervadinta į Nissbau Euromix C120, 3 m³. Koordinatės geokoduotos pagal naują adresą.</t>
+          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>c3-beton-runeikiai</t>
+          <t>ponas-betonas-paraudondvariai</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
+          <t>306676006</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>UAB Ponas betonas</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Ponas betonas</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Konkurentas</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Paraudondvariai</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus r. sav.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>54.8321418</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>25.2755596</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>ready_mix_concrete</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>Betono mišiniai</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Elkon</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
           <t>Nenurodyta viešai</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>C3 Betonas</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>C3 Betonas</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Runeikiai</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Kėdainių r. sav.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Paguiriai, Šėtos sen., Kėdainių r. sav.</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>55.3327393</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>24.3501308</v>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Oficialiame puslapyje pateiktas gamyklos taškas</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>C3 Betonas oficialus puslapis</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>https://c3beton.com/lt/betonas</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>Runeikiai Plant</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>Ammann Elba Euromix C120, 3 m³</t>
-        </is>
-      </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>60–80 m³/val.</t>
+          <t>Nenurodyta viešai</t>
         </is>
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>2x85 t</t>
+          <t>2 matomi oficialioje nuotraukoje</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>Betono mazgas Ammann Elba Euromix C120; maišyklė 3 m³; našumas 60–80 m³/val.; silosai 2x85 t.</t>
+          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
         </is>
       </c>
       <c r="U61" s="5" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.ponasbetonas.lt/#Apiemus</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>https://c3beton.com/lt/betonas</t>
+          <t>https://www.ponasbetonas.lt/</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>Įtraukta pagal oficialaus C3 Betonas puslapio žemėlapį. Koordinatės paimtos iš oficialaus puslapio programinio kodo; adresas patikslintas pagal koordinates. Techniniai duomenys papildyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>reljef-rukla</t>
+          <t>pabrades-betonas-pabrade</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>301731961</t>
+          <t>306177188</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>UAB Reljef</t>
+          <t>UAB Pabradės betonas</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Reljef</t>
+          <t>Pabradės betonas</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7591,38 +7627,38 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Rukla</t>
+          <t>Pabradė</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Jonavos r. sav.</t>
+          <t>Švenčionių r. sav.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Rukla, Jonavos r. sav.</t>
+          <t>Vilniaus g. 161, Pabradė, LT-18177 Švenčionių r.</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>55.05225</v>
+        <v>54.9758768</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>24.4064167</v>
+        <v>25.7373849</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktas taškas; adresas artimiausias pagal OpenStreetMap</t>
+          <t>Tikslus oficialioje svetainėje pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateiktos koordinatės</t>
+          <t>Oficiali Pabradės betono Google Maps nuoroda</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://maps.app.goo.gl/TQBCVR8DczDRvQaeA</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7637,77 +7673,77 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Ammann Elba</t>
+          <t>Liebherr (tikėtina)</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Nenustatyta</t>
+          <t>3 m³</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>Nenustatytas</t>
+          <t>60 m³/val.</t>
         </is>
       </c>
       <c r="S62" s="4" t="inlineStr">
         <is>
-          <t>2x65 t</t>
+          <t>3x65 t</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>Rukloje veikiantis UAB Reljef betono mazgas: Ammann Elba, 2x65 t silosai. Maišyklė ir našumas nenustatyti.</t>
+          <t>UAB Pabradės betonas Vilniaus g. 161, Pabradėje, gamina sertifikuotą normalųjį betoną ir oficialiai nurodo dirbanti 50 km spinduliu aplink Pabradę. Oficialios galerijos nuotraukose matoma stacionari gamybos bazė su trimis cemento silosais. Mazgo gamintojas tikėtinai Liebherr pagal oficialiose nuotraukose matomą Liebherr įrangą ir gamyklos konstrukcijos vizualinius požymius; gamintojo lentelė viešai neparodyta.</t>
         </is>
       </c>
       <c r="U62" s="5" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.pabradesbetonas.lt/</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>https://www.reljef.lt/</t>
+          <t>https://www.pabradesbetonas.lt/</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/?mlat=55.05225&amp;mlon=24.4064167#map=18/55.05225/24.4064167</t>
+          <t>https://www.pabradesbetonas.lt/galerija/</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>Įmonės rekvizitai paimti iš oficialaus UAB Reljef puslapio. Betono mazgo gamintojas, silosai ir lokacija įrašyti pagal naudotojo pateiktą informaciją. Artimiausias viešai geokoduotas adresas nustatytas pagal OpenStreetMap.</t>
+          <t>Adresas, įmonės kodas ir betono gamyba patvirtinti oficialioje svetainėje bei viešame gamybos kontrolės sertifikate. Koordinatės paimtos iš oficialioje svetainėje pateiktos Google Maps nuorodos. Maišyklės tūris 3 m³, realus našumas 60 m³/val. ir silosai 3x65 t įrašyti pagal naudotojo pateiktą informaciją. Gamintojas Liebherr nurodytas kaip tikėtinas pagal oficialios galerijos nuotraukas; viešo gamintojo ženklinimo ant paties mazgo nerasta.</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ponas-betonas-paraudondvariai</t>
+          <t>alkesta-marijampole-vasaros</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>306676006</t>
+          <t>249672710</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>UAB Ponas betonas</t>
+          <t>UAB Alkesta</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Ponas betonas</t>
+          <t>Alkesta</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -7717,24 +7753,24 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Paraudondvariai</t>
+          <t>Marijampolė</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus r. sav.</t>
+          <t>Marijampolės sav.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus g., Paraudondvariai, Riešės sen., Vilniaus r. sav.</t>
+          <t>Vasaros g. 14, Marijampolė, LT-68111</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>54.8321418</v>
+        <v>54.5686121</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>25.2755596</v>
+        <v>23.3895157</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -7748,7 +7784,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/NxQohpnzv1q9DA6CA?g_st=ac</t>
+          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7763,77 +7799,73 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Elkon</t>
+          <t>Elba</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
+          <t>0,5 m³</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>Nenurodyta viešai</t>
-        </is>
-      </c>
-      <c r="S63" s="4" t="inlineStr">
-        <is>
-          <t>2 matomi oficialioje nuotraukoje</t>
-        </is>
-      </c>
+          <t>10 m³/val.</t>
+        </is>
+      </c>
+      <c r="S63" s="4" t="inlineStr"/>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>Oficialiame UAB Ponas betonas puslapyje nurodoma, kad įmonė turi nuosavą betono mazgą, gamina prekinį betoną ir jį pristato. Puslapio hero nuotraukoje ant silosų matomas ELKON ženklinimas, todėl mazgo gamintojas identifikuotas kaip Elkon. Konkretus modelis, maišyklė ir našumas viešai nenurodyti; oficialioje nuotraukoje matomi 2 silosai.</t>
+          <t>UAB Alkesta Marijampolės betono mazgas Vasaros g. 14. Mazgo gamintojas Elba, maišyklė 0,5 m³, našumas 10 m³/val.</t>
         </is>
       </c>
       <c r="U63" s="5" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/</t>
+          <t>https://alkesta.lt/</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/#Apiemus</t>
+          <t>https://spsc.lt/registrai/regsapp/ser_produktai_view.php?editid1=13061</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>https://www.ponasbetonas.lt/</t>
+          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>Nuosavas betono mazgas ir prekinio betono gamyba patvirtinti oficialiame įmonės puslapyje. Mazgo gamintojas nustatytas pagal oficialaus puslapio hero nuotraukoje ant silosų matomą ELKON ženklinimą; modelis, maišyklė ir našumas viešai nenurodyti. Tiksli mazgo lokacija paimta iš naudotojo pateiktos Google Maps nuorodos; vietovė patikslinta pagal OpenStreetMap. Įmonės kodas patvirtintas Registrų centro viešame juridinio asmens pranešime.</t>
+          <t>Oficialus SPSC sertifikatų registras patvirtina UAB Alkesta betono gamybą ir gamybos vietą Vasaros g. 14, Marijampolėje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris ir našumas įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>pabrades-betonas-pabrade</t>
+          <t>gevalda-visincia</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>306177188</t>
+          <t>302592895</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>UAB Pabradės betonas</t>
+          <t>UAB Gevalda</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Pabradės betonas</t>
+          <t>Gevalda</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7843,38 +7875,38 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Pabradė</t>
+          <t>Visinčia</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Švenčionių r. sav.</t>
+          <t>Šalčininkų r. sav.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Vilniaus g. 161, Pabradė, LT-18177 Švenčionių r.</t>
+          <t>Visinčia, Pabarės sen., Šalčininkų r. sav.</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>54.9758768</v>
+        <v>54.4122467</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>25.7373849</v>
+        <v>25.1449142</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Tikslus oficialioje svetainėje pateiktos Google Maps nuorodos taškas</t>
+          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Oficiali Pabradės betono Google Maps nuoroda</t>
+          <t>Naudotojo pateikta Google Maps lokacija</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/TQBCVR8DczDRvQaeA</t>
+          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7889,7 +7921,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Liebherr (tikėtina)</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7904,35 +7936,35 @@
       </c>
       <c r="S64" s="4" t="inlineStr">
         <is>
-          <t>3x65 t</t>
+          <t>2x85 t</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>UAB Pabradės betonas Vilniaus g. 161, Pabradėje, gamina sertifikuotą normalųjį betoną ir oficialiai nurodo dirbanti 50 km spinduliu aplink Pabradę. Oficialios galerijos nuotraukose matoma stacionari gamybos bazė su trimis cemento silosais. Mazgo gamintojas tikėtinai Liebherr pagal oficialiose nuotraukose matomą Liebherr įrangą ir gamyklos konstrukcijos vizualinius požymius; gamintojo lentelė viešai neparodyta.</t>
+          <t>UAB Gevalda mobilus betono mazgas Visinčioje. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U64" s="5" t="n">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>https://www.pabradesbetonas.lt/</t>
+          <t>https://www.gevalda.lt/</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>https://www.pabradesbetonas.lt/</t>
+          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>https://www.pabradesbetonas.lt/galerija/</t>
+          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>Adresas, įmonės kodas ir betono gamyba patvirtinti oficialioje svetainėje bei viešame gamybos kontrolės sertifikate. Koordinatės paimtos iš oficialioje svetainėje pateiktos Google Maps nuorodos. Maišyklės tūris 3 m³, realus našumas 60 m³/val. ir silosai 3x65 t įrašyti pagal naudotojo pateiktą informaciją. Gamintojas Liebherr nurodytas kaip tikėtinas pagal oficialios galerijos nuotraukas; viešo gamintojo ženklinimo ant paties mazgo nerasta.</t>
+          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris, našumas ir silosai įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -7944,22 +7976,22 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>alkesta-marijampole-vasaros</t>
+          <t>gevalda-kaunas-palemonas</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>249672710</t>
+          <t>302592895</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>UAB Alkesta</t>
+          <t>UAB Gevalda</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Alkesta</t>
+          <t>Gevalda</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -7969,24 +8001,24 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Marijampolė</t>
+          <t>Kaunas</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Marijampolės sav.</t>
+          <t>Kauno m. sav.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Vasaros g. 14, Marijampolė, LT-68111</t>
+          <t>Kražantės g., Palemonas, Kaunas</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>54.5686121</v>
+        <v>54.918</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>23.3895157</v>
+        <v>24.063</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -8000,7 +8032,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
+          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8015,23 +8047,27 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Elba</t>
+          <t>Elkon</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>0,5 m³</t>
+          <t>3 m³</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>10 m³/val.</t>
-        </is>
-      </c>
-      <c r="S65" s="4" t="inlineStr"/>
+          <t>60 m³/val.</t>
+        </is>
+      </c>
+      <c r="S65" s="4" t="inlineStr">
+        <is>
+          <t>2x85 t</t>
+        </is>
+      </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>UAB Alkesta Marijampolės betono mazgas Vasaros g. 14. Mazgo gamintojas Elba, maišyklė 0,5 m³, našumas 10 m³/val.</t>
+          <t>UAB Gevalda mobilus betono mazgas Palemone, Kaune. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
         </is>
       </c>
       <c r="U65" s="5" t="n">
@@ -8039,22 +8075,22 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>https://alkesta.lt/</t>
+          <t>https://www.gevalda.lt/</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>https://spsc.lt/registrai/regsapp/ser_produktai_view.php?editid1=13061</t>
+          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xKhbiD3KQWzTBzhK9?g_st=ic</t>
+          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>Oficialus SPSC sertifikatų registras patvirtina UAB Alkesta betono gamybą ir gamybos vietą Vasaros g. 14, Marijampolėje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris ir našumas įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija ir analogiški techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8066,22 +8102,22 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>gevalda-visincia</t>
+          <t>telsiu-gelzbetonis-telsiai</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>302592895</t>
+          <t>180245532</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>UAB Gevalda</t>
+          <t>UAB Telšių gelžbetonis</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Gevalda</t>
+          <t>Telšių gelžbetonis</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -8091,73 +8127,61 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Visinčia</t>
+          <t>Telšiai</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Šalčininkų r. sav.</t>
+          <t>Telšių r. sav.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Visinčia, Pabarės sen., Šalčininkų r. sav.</t>
+          <t>Statybininkų g. 2-8, LT-87101 Telšiai</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>54.4122467</v>
+        <v>55.9947877</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>25.1449142</v>
+        <v>22.2517039</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
+          <t>Oficialios svetainės žemėlapio adreso taškas</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
+          <t>Google Maps (oficiali įmonės kontaktų nuoroda)</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
+          <t>https://maps.app.goo.gl/fJnDGN7yksUMAyQa9</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>ready_mix_concrete</t>
+          <t>precast_concrete</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>Elkon</t>
-        </is>
-      </c>
+          <t>Betono mišiniai ir gelžbetonio gaminiai</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/val.</t>
-        </is>
-      </c>
-      <c r="S66" s="4" t="inlineStr">
-        <is>
-          <t>2x85 t</t>
-        </is>
-      </c>
+          <t>Sicoma OMG planetarinė maišyklė</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="4" t="inlineStr"/>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>UAB Gevalda mobilus betono mazgas Visinčioje. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
+          <t>Gamintojas siūlo betoninius ir gelžbetoninius gaminius bei prekinį betoną C8/10–C35/45. Oficialioje įmonės istorijoje nurodytas betono mazgo automatizavimas (2016 m.) ir Sicoma OMG planetarinės maišyklės sumontavimas (2023 m.).</t>
         </is>
       </c>
       <c r="U66" s="5" t="n">
@@ -8165,158 +8189,32 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>https://www.gevalda.lt/</t>
+          <t>https://tgb.lt/</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
+          <t>https://tgb.lt/kontaktai/</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/xuuJfukn3ApaYNME6?g_st=ic</t>
+          <t>https://tgb.lt/apie-imone/</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija, mazgo gamintojas, maišyklės tūris, našumas ir silosai įrašyti pagal naudotojo pateiktą informaciją.</t>
+          <t>Adresas ir Google Maps nuoroda paimti iš oficialios svetainės kontaktų. Nuoroda rodo Statybininkų g. 2 adreso tašką; tai nėra atskirai patvirtinta mazgo vieta sklype. Prekinio betono šaltinis: https://tgb.lt/prekinis-betonas/. Kontaktai: +370 679 89333, info@tgb.lt. Įmonės kodas patvirtintas Registrų centro leidinyje: https://www.registrucentras.lt/jar/infleid/download.do?oid=252865. Maišyklės tūris, našumas ir silosai viešai nenurodyti.</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>gevalda-kaunas-palemonas</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>302592895</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>UAB Gevalda</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Gevalda</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Konkurentas</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Kaunas</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Kauno m. sav.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Kražantės g., Palemonas, Kaunas</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>54.918</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>24.063</v>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Tikslus naudotojo pateiktos Google Maps nuorodos taškas</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>Naudotojo pateikta Google Maps lokacija</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>ready_mix_concrete</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>Betono mišiniai</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>Elkon</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>3 m³</t>
-        </is>
-      </c>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>60 m³/val.</t>
-        </is>
-      </c>
-      <c r="S67" s="4" t="inlineStr">
-        <is>
-          <t>2x85 t</t>
-        </is>
-      </c>
-      <c r="T67" s="2" t="inlineStr">
-        <is>
-          <t>UAB Gevalda mobilus betono mazgas Palemone, Kaune. Mazgo gamintojas Elkon, maišyklė 3 m³, našumas 60 m³/val., silosai 2x85 t.</t>
-        </is>
-      </c>
-      <c r="U67" s="5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="V67" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gevalda.lt/</t>
-        </is>
-      </c>
-      <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gevalda.lt/paslaugos/gamyba</t>
-        </is>
-      </c>
-      <c r="X67" s="2" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/sKM8v9zqzZz9ZR8i8</t>
-        </is>
-      </c>
-      <c r="Y67" s="2" t="inlineStr">
-        <is>
-          <t>Oficiali UAB Gevalda svetainė patvirtina betono mišinių gamybą mobilioje gamykloje. Tiksli lokacija ir analogiški techniniai duomenys įrašyti pagal naudotojo pateiktą informaciją.</t>
-        </is>
-      </c>
-      <c r="Z67" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z67"/>
+  <autoFilter ref="A1:Z66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -8405,7 +8303,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-12T12:42:52.334852+00:00</t>
+          <t>2026-10-14T05:44:30.655552+00:00</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8358,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12T12:42:52.335562+00:00</t>
+          <t>2026-10-14T05:44:30.655552+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8474,7 +8372,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Įmonės" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metaduomenys" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Importo žurnalas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Įmonės'!$A$1:$Z$66</definedName>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14T05:44:30.655552+00:00</t>
+          <t>2026-10-19T10:29:43.005133+00:00</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14T05:44:30.655552+00:00</t>
+          <t>2026-10-19T10:29:43.005856+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/data/companies.xlsx
+++ b/data/companies.xlsx
@@ -8303,7 +8303,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-19T10:29:43.005133+00:00</t>
+          <t>2026-10-26T10:44:26.689991+00:00</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19T10:29:43.005856+00:00</t>
+          <t>2026-10-26T10:44:26.690503+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
